--- a/Ciclodeinstruccion (2).xlsx
+++ b/Ciclodeinstruccion (2).xlsx
@@ -14,125 +14,128 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="86">
   <si>
     <t>Intrucciones</t>
   </si>
   <si>
-    <t>LD AX, 20H</t>
+    <t>Hora</t>
+  </si>
+  <si>
+    <t>Ciclo / Estado</t>
+  </si>
+  <si>
+    <t>Acción Realizada</t>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>IR</t>
+  </si>
+  <si>
+    <t>MAR</t>
+  </si>
+  <si>
+    <t>MOV AX, 00H</t>
+  </si>
+  <si>
+    <t>MDR</t>
+  </si>
+  <si>
+    <t>AX</t>
+  </si>
+  <si>
+    <t>BX</t>
+  </si>
+  <si>
+    <t>ALU Operando 1</t>
+  </si>
+  <si>
+    <t>ALU Operando 2</t>
+  </si>
+  <si>
+    <t>ALU Operación</t>
+  </si>
+  <si>
+    <t>ALU Resultado</t>
+  </si>
+  <si>
+    <t>ZF (Zero)</t>
+  </si>
+  <si>
+    <t>CF (Carry)</t>
+  </si>
+  <si>
+    <t>MOV BX, 04H</t>
+  </si>
+  <si>
+    <t>SF (Sign)</t>
+  </si>
+  <si>
+    <t>READY</t>
+  </si>
+  <si>
+    <t>Programa cargado desde la hoja 'Programas'.</t>
+  </si>
+  <si>
+    <t>00H</t>
+  </si>
+  <si>
+    <t>MOV AX, 03H</t>
+  </si>
+  <si>
+    <t>MOV AX, 0AH</t>
+  </si>
+  <si>
+    <t>ADD AX, 03H</t>
+  </si>
+  <si>
+    <t>INC AX</t>
+  </si>
+  <si>
+    <t>MOV BX, 08H</t>
+  </si>
+  <si>
+    <t>LD BX, 10H</t>
+  </si>
+  <si>
+    <t>DEC BX</t>
+  </si>
+  <si>
+    <t>CMP AX, 05H</t>
+  </si>
+  <si>
+    <t>CMP AX, BX</t>
+  </si>
+  <si>
+    <t>JNZ 02H</t>
+  </si>
+  <si>
+    <t>JNZ 01H</t>
+  </si>
+  <si>
+    <t>ST 20H, AX</t>
+  </si>
+  <si>
+    <t>JZ 06H</t>
   </si>
   <si>
     <t>HLT</t>
   </si>
   <si>
-    <t>MOV AX, 00H</t>
-  </si>
-  <si>
-    <t>MOV AX, 03H</t>
-  </si>
-  <si>
-    <t>Hora</t>
-  </si>
-  <si>
-    <t>MOV AX, 0AH</t>
-  </si>
-  <si>
-    <t>MOV BX, 04H</t>
-  </si>
-  <si>
-    <t>INC AX</t>
-  </si>
-  <si>
-    <t>MOV BX, 08H</t>
-  </si>
-  <si>
-    <t>LD BX, 10H</t>
-  </si>
-  <si>
-    <t>ADD AX, 03H</t>
-  </si>
-  <si>
-    <t>CMP AX, 05H</t>
-  </si>
-  <si>
-    <t>CMP AX, BX</t>
-  </si>
-  <si>
-    <t>DEC BX</t>
-  </si>
-  <si>
-    <t>JNZ 01H</t>
-  </si>
-  <si>
-    <t>ST 20H, AX</t>
-  </si>
-  <si>
-    <t>JZ 06H</t>
-  </si>
-  <si>
-    <t>JNZ 02H</t>
-  </si>
-  <si>
     <t>ST 30H, 00H</t>
   </si>
   <si>
-    <t>Ciclo / Estado</t>
-  </si>
-  <si>
-    <t>Acción Realizada</t>
-  </si>
-  <si>
-    <t>PC</t>
-  </si>
-  <si>
-    <t>IR</t>
+    <t>Estado</t>
   </si>
   <si>
     <t>ST 30H, FFH</t>
   </si>
   <si>
-    <t>MAR</t>
-  </si>
-  <si>
-    <t>MDR</t>
-  </si>
-  <si>
-    <t>AX</t>
-  </si>
-  <si>
-    <t>BX</t>
-  </si>
-  <si>
-    <t>ALU Operando 1</t>
-  </si>
-  <si>
-    <t>ALU Operando 2</t>
-  </si>
-  <si>
-    <t>ALU Operación</t>
-  </si>
-  <si>
-    <t>ALU Resultado</t>
-  </si>
-  <si>
-    <t>ZF (Zero)</t>
-  </si>
-  <si>
-    <t>CF (Carry)</t>
-  </si>
-  <si>
-    <t>SF (Sign)</t>
-  </si>
-  <si>
-    <t>Estado</t>
-  </si>
-  <si>
     <t>CPU:</t>
   </si>
   <si>
-    <t>READY</t>
-  </si>
-  <si>
     <t>RAM</t>
   </si>
   <si>
@@ -187,9 +190,6 @@
     <t>"+F</t>
   </si>
   <si>
-    <t>00H</t>
-  </si>
-  <si>
     <t>10H</t>
   </si>
   <si>
@@ -238,7 +238,7 @@
     <t>F0H</t>
   </si>
   <si>
-    <t>Registros para Operaciones</t>
+    <t>Unidad Arimetica Logica</t>
   </si>
   <si>
     <t>Operador 1</t>
@@ -292,6 +292,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -300,12 +306,6 @@
       <b/>
       <sz val="20.0"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -862,40 +862,44 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="98">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="21" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="21" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="3" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="3" fillId="5" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="3" fillId="5" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -910,18 +914,18 @@
     </xf>
     <xf borderId="6" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="2" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="7" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="8" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="9" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="10" fillId="6" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="11" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="12" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="11" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="12" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="13" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="14" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="15" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="16" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="16" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="3" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -932,41 +936,41 @@
     <xf borderId="3" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="17" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="18" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="17" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="18" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="5" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="19" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="19" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="13" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="20" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="21" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="22" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="20" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="21" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="22" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="23" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="23" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="3" fillId="2" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="18" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="3" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="24" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="18" fillId="2" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="3" fillId="2" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="24" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="23" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="23" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="25" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -979,23 +983,23 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="27" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="27" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="28" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="27" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="28" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="29" fillId="0" fontId="13" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="30" fillId="0" fontId="13" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="31" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="5" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="32" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="33" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="34" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="31" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="32" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="33" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="34" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="9" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="9" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="10" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="35" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="9" fontId="3" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="10" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="35" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="4" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -1013,7 +1017,7 @@
     <xf borderId="29" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="24" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -1024,21 +1028,21 @@
     <xf borderId="3" fillId="10" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="18" fillId="7" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="37" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="18" fillId="7" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="37" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="38" fillId="0" fontId="17" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="15" fillId="0" fontId="17" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="7" fillId="0" fontId="17" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="38" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="15" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="39" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="38" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="15" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="39" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="40" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="40" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -2329,110 +2333,149 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
+      <c r="B1" s="3"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="s">
-        <v>1</v>
+      <c r="A2" s="4" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>6</v>
+      <c r="A3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="4">
-      <c r="H4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="R4" s="3" t="s">
-        <v>10</v>
+      <c r="A4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="5">
-      <c r="H5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="R5" s="3" t="s">
-        <v>13</v>
+      <c r="A5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="5" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="6">
-      <c r="H6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="R6" s="3" t="s">
-        <v>17</v>
+      <c r="A6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="9"/>
+      <c r="R6" s="5" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="7">
-      <c r="H7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="R7" s="3" t="s">
-        <v>19</v>
+      <c r="A7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="5" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="8">
-      <c r="H8" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>2</v>
+      <c r="A8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="9"/>
+      <c r="R8" s="5" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6"/>
-      <c r="H9" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>24</v>
+      <c r="A9" s="10"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="9"/>
+      <c r="R9" s="5" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4"/>
-      <c r="R10" s="3" t="s">
-        <v>2</v>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="9"/>
+      <c r="O10" s="9"/>
+      <c r="P10" s="9"/>
+      <c r="Q10" s="9"/>
+      <c r="R10" s="5" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="11">
@@ -2442,22 +2485,22 @@
       <c r="A12" s="4"/>
     </row>
     <row r="13">
-      <c r="A13" s="7"/>
+      <c r="A13" s="12"/>
     </row>
     <row r="14">
-      <c r="A14" s="7"/>
+      <c r="A14" s="12"/>
     </row>
     <row r="15">
-      <c r="A15" s="7"/>
+      <c r="A15" s="12"/>
     </row>
     <row r="16">
-      <c r="A16" s="7"/>
+      <c r="A16" s="12"/>
     </row>
     <row r="17">
-      <c r="A17" s="7"/>
+      <c r="A17" s="12"/>
     </row>
     <row r="18">
-      <c r="A18" s="7"/>
+      <c r="A18" s="12"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -2473,1182 +2516,1196 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
+      <c r="A1" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="s">
-        <v>37</v>
+      <c r="A2" s="11" t="s">
+        <v>39</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-      <c r="L2" s="20"/>
+        <v>19</v>
+      </c>
+      <c r="C2" s="18"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="22"/>
     </row>
     <row r="3">
-      <c r="A3" s="21"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="22"/>
-      <c r="L3" s="23"/>
+      <c r="A3" s="23"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="24"/>
+      <c r="L3" s="25"/>
     </row>
     <row r="4">
-      <c r="E4" s="22"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="N4" s="25"/>
-      <c r="O4" s="25"/>
-      <c r="P4" s="25"/>
-      <c r="Q4" s="25"/>
-      <c r="R4" s="25"/>
-      <c r="S4" s="25"/>
-      <c r="T4" s="25"/>
-      <c r="U4" s="25"/>
-      <c r="V4" s="25"/>
-      <c r="W4" s="25"/>
-      <c r="X4" s="25"/>
-      <c r="Y4" s="25"/>
-      <c r="Z4" s="25"/>
-      <c r="AA4" s="25"/>
-      <c r="AB4" s="25"/>
-      <c r="AC4" s="25"/>
-      <c r="AD4" s="25"/>
-      <c r="AE4" s="26"/>
+      <c r="E4" s="24"/>
+      <c r="L4" s="25"/>
+      <c r="M4" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="N4" s="27"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="27"/>
+      <c r="S4" s="27"/>
+      <c r="T4" s="27"/>
+      <c r="U4" s="27"/>
+      <c r="V4" s="27"/>
+      <c r="W4" s="27"/>
+      <c r="X4" s="27"/>
+      <c r="Y4" s="27"/>
+      <c r="Z4" s="27"/>
+      <c r="AA4" s="27"/>
+      <c r="AB4" s="27"/>
+      <c r="AC4" s="27"/>
+      <c r="AD4" s="27"/>
+      <c r="AE4" s="28"/>
     </row>
     <row r="5">
-      <c r="E5" s="27"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="28"/>
-      <c r="K5" s="28"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="30"/>
-      <c r="O5" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q5" s="32"/>
-      <c r="R5" s="33"/>
-      <c r="S5" s="34"/>
-      <c r="T5" s="33"/>
-      <c r="U5" s="32"/>
-      <c r="V5" s="12"/>
-      <c r="W5" s="12"/>
-      <c r="X5" s="12"/>
-      <c r="Y5" s="12"/>
-      <c r="Z5" s="12"/>
-      <c r="AA5" s="12"/>
-      <c r="AB5" s="12"/>
-      <c r="AC5" s="12"/>
-      <c r="AE5" s="35"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="30"/>
+      <c r="K5" s="30"/>
+      <c r="L5" s="31"/>
+      <c r="M5" s="32"/>
+      <c r="O5" s="33" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q5" s="34"/>
+      <c r="R5" s="35"/>
+      <c r="S5" s="36"/>
+      <c r="T5" s="35"/>
+      <c r="U5" s="34"/>
+      <c r="V5" s="14"/>
+      <c r="W5" s="14"/>
+      <c r="X5" s="14"/>
+      <c r="Y5" s="14"/>
+      <c r="Z5" s="14"/>
+      <c r="AA5" s="14"/>
+      <c r="AB5" s="14"/>
+      <c r="AC5" s="14"/>
+      <c r="AE5" s="37"/>
     </row>
     <row r="6">
-      <c r="M6" s="30"/>
-      <c r="N6" s="12"/>
-      <c r="O6" s="36"/>
-      <c r="P6" s="12"/>
-      <c r="Q6" s="12"/>
-      <c r="R6" s="12"/>
-      <c r="S6" s="12"/>
-      <c r="T6" s="12"/>
-      <c r="U6" s="12"/>
-      <c r="V6" s="12"/>
-      <c r="W6" s="12"/>
-      <c r="X6" s="12"/>
-      <c r="Y6" s="12"/>
-      <c r="Z6" s="12"/>
-      <c r="AA6" s="12"/>
-      <c r="AB6" s="12"/>
-      <c r="AC6" s="12"/>
-      <c r="AD6" s="12"/>
-      <c r="AE6" s="35"/>
+      <c r="M6" s="32"/>
+      <c r="N6" s="14"/>
+      <c r="O6" s="38"/>
+      <c r="P6" s="14"/>
+      <c r="Q6" s="14"/>
+      <c r="R6" s="14"/>
+      <c r="S6" s="14"/>
+      <c r="T6" s="14"/>
+      <c r="U6" s="14"/>
+      <c r="V6" s="14"/>
+      <c r="W6" s="14"/>
+      <c r="X6" s="14"/>
+      <c r="Y6" s="14"/>
+      <c r="Z6" s="14"/>
+      <c r="AA6" s="14"/>
+      <c r="AB6" s="14"/>
+      <c r="AC6" s="14"/>
+      <c r="AD6" s="14"/>
+      <c r="AE6" s="37"/>
     </row>
     <row r="7">
-      <c r="M7" s="30"/>
-      <c r="N7" s="37"/>
-      <c r="O7" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="P7" s="38" t="s">
+      <c r="M7" s="32"/>
+      <c r="N7" s="39"/>
+      <c r="O7" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="Q7" s="38" t="s">
+      <c r="P7" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="R7" s="38" t="s">
+      <c r="Q7" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="S7" s="38" t="s">
+      <c r="R7" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="T7" s="38" t="s">
+      <c r="S7" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="U7" s="38" t="s">
+      <c r="T7" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="V7" s="38" t="s">
+      <c r="U7" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="W7" s="38" t="s">
+      <c r="V7" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="X7" s="38" t="s">
+      <c r="W7" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="Y7" s="38" t="s">
+      <c r="X7" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="Z7" s="38" t="s">
+      <c r="Y7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="AA7" s="38" t="s">
+      <c r="Z7" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AB7" s="38" t="s">
+      <c r="AA7" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="AC7" s="38" t="s">
+      <c r="AB7" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="AD7" s="38" t="s">
+      <c r="AC7" s="40" t="s">
         <v>56</v>
       </c>
-      <c r="AE7" s="35"/>
+      <c r="AD7" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="AE7" s="37"/>
     </row>
     <row r="8">
-      <c r="M8" s="39"/>
-      <c r="N8" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="O8" s="40"/>
-      <c r="P8" s="40"/>
-      <c r="Q8" s="40"/>
-      <c r="R8" s="40"/>
-      <c r="S8" s="40"/>
-      <c r="T8" s="40"/>
-      <c r="U8" s="40"/>
-      <c r="V8" s="40"/>
-      <c r="W8" s="40"/>
-      <c r="X8" s="40"/>
-      <c r="Y8" s="40"/>
-      <c r="Z8" s="41"/>
-      <c r="AA8" s="41"/>
-      <c r="AB8" s="41"/>
-      <c r="AC8" s="41"/>
-      <c r="AD8" s="41"/>
-      <c r="AE8" s="35"/>
+      <c r="M8" s="41"/>
+      <c r="N8" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="O8" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="P8" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q8" s="42" t="s">
+        <v>24</v>
+      </c>
+      <c r="R8" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="S8" s="42" t="s">
+        <v>31</v>
+      </c>
+      <c r="T8" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="U8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="V8" s="42"/>
+      <c r="W8" s="42"/>
+      <c r="X8" s="42"/>
+      <c r="Y8" s="42"/>
+      <c r="Z8" s="43"/>
+      <c r="AA8" s="43"/>
+      <c r="AB8" s="43"/>
+      <c r="AC8" s="43"/>
+      <c r="AD8" s="43"/>
+      <c r="AE8" s="37"/>
     </row>
     <row r="9">
-      <c r="M9" s="30"/>
-      <c r="N9" s="38" t="s">
+      <c r="M9" s="32"/>
+      <c r="N9" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="O9" s="41"/>
-      <c r="P9" s="41"/>
-      <c r="Q9" s="41"/>
-      <c r="R9" s="41"/>
-      <c r="S9" s="41"/>
-      <c r="T9" s="41"/>
-      <c r="U9" s="41"/>
-      <c r="V9" s="41"/>
-      <c r="W9" s="41"/>
-      <c r="X9" s="41"/>
-      <c r="Y9" s="41"/>
-      <c r="Z9" s="41"/>
-      <c r="AA9" s="41"/>
-      <c r="AB9" s="41"/>
-      <c r="AC9" s="41"/>
-      <c r="AD9" s="41"/>
-      <c r="AE9" s="35"/>
+      <c r="O9" s="43"/>
+      <c r="P9" s="43"/>
+      <c r="Q9" s="43"/>
+      <c r="R9" s="43"/>
+      <c r="S9" s="43"/>
+      <c r="T9" s="43"/>
+      <c r="U9" s="43"/>
+      <c r="V9" s="43"/>
+      <c r="W9" s="43"/>
+      <c r="X9" s="43"/>
+      <c r="Y9" s="43"/>
+      <c r="Z9" s="43"/>
+      <c r="AA9" s="43"/>
+      <c r="AB9" s="43"/>
+      <c r="AC9" s="43"/>
+      <c r="AD9" s="43"/>
+      <c r="AE9" s="37"/>
     </row>
     <row r="10">
-      <c r="M10" s="30"/>
-      <c r="N10" s="38" t="s">
+      <c r="M10" s="32"/>
+      <c r="N10" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="O10" s="40"/>
-      <c r="P10" s="40"/>
-      <c r="Q10" s="40"/>
-      <c r="R10" s="41"/>
-      <c r="S10" s="41"/>
-      <c r="T10" s="41"/>
-      <c r="U10" s="41"/>
-      <c r="V10" s="41"/>
-      <c r="W10" s="41"/>
-      <c r="X10" s="41"/>
-      <c r="Y10" s="41"/>
-      <c r="Z10" s="41"/>
-      <c r="AA10" s="41"/>
-      <c r="AB10" s="41"/>
-      <c r="AC10" s="41"/>
-      <c r="AD10" s="41"/>
-      <c r="AE10" s="35"/>
+      <c r="O10" s="42"/>
+      <c r="P10" s="42"/>
+      <c r="Q10" s="42"/>
+      <c r="R10" s="43"/>
+      <c r="S10" s="43"/>
+      <c r="T10" s="43"/>
+      <c r="U10" s="43"/>
+      <c r="V10" s="43"/>
+      <c r="W10" s="43"/>
+      <c r="X10" s="43"/>
+      <c r="Y10" s="43"/>
+      <c r="Z10" s="43"/>
+      <c r="AA10" s="43"/>
+      <c r="AB10" s="43"/>
+      <c r="AC10" s="43"/>
+      <c r="AD10" s="43"/>
+      <c r="AE10" s="37"/>
     </row>
     <row r="11">
-      <c r="A11" s="42"/>
-      <c r="B11" s="43"/>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="26"/>
-      <c r="H11" s="3"/>
-      <c r="M11" s="30"/>
-      <c r="N11" s="38" t="s">
+      <c r="A11" s="44"/>
+      <c r="B11" s="45"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="45"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="28"/>
+      <c r="H11" s="7"/>
+      <c r="M11" s="32"/>
+      <c r="N11" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="O11" s="41"/>
-      <c r="P11" s="41"/>
-      <c r="Q11" s="41"/>
-      <c r="R11" s="41"/>
-      <c r="S11" s="41"/>
-      <c r="T11" s="41"/>
-      <c r="U11" s="41"/>
-      <c r="V11" s="41"/>
-      <c r="W11" s="41"/>
-      <c r="X11" s="41"/>
-      <c r="Y11" s="41"/>
-      <c r="Z11" s="41"/>
-      <c r="AA11" s="41"/>
-      <c r="AB11" s="41"/>
-      <c r="AC11" s="41"/>
-      <c r="AD11" s="41"/>
-      <c r="AE11" s="35"/>
+      <c r="O11" s="43"/>
+      <c r="P11" s="43"/>
+      <c r="Q11" s="43"/>
+      <c r="R11" s="43"/>
+      <c r="S11" s="43"/>
+      <c r="T11" s="43"/>
+      <c r="U11" s="43"/>
+      <c r="V11" s="43"/>
+      <c r="W11" s="43"/>
+      <c r="X11" s="43"/>
+      <c r="Y11" s="43"/>
+      <c r="Z11" s="43"/>
+      <c r="AA11" s="43"/>
+      <c r="AB11" s="43"/>
+      <c r="AC11" s="43"/>
+      <c r="AD11" s="43"/>
+      <c r="AE11" s="37"/>
     </row>
     <row r="12">
-      <c r="A12" s="44"/>
-      <c r="B12" s="45"/>
-      <c r="D12" s="45"/>
-      <c r="F12" s="46"/>
-      <c r="H12" s="3"/>
-      <c r="M12" s="30"/>
-      <c r="N12" s="38" t="s">
+      <c r="A12" s="46"/>
+      <c r="B12" s="47"/>
+      <c r="D12" s="47"/>
+      <c r="F12" s="48"/>
+      <c r="H12" s="7"/>
+      <c r="M12" s="32"/>
+      <c r="N12" s="40" t="s">
         <v>61</v>
       </c>
-      <c r="O12" s="40"/>
-      <c r="P12" s="41"/>
-      <c r="Q12" s="41"/>
-      <c r="R12" s="41"/>
-      <c r="S12" s="41"/>
-      <c r="T12" s="41"/>
-      <c r="U12" s="41"/>
-      <c r="V12" s="41"/>
-      <c r="W12" s="41"/>
-      <c r="X12" s="41"/>
-      <c r="Y12" s="41"/>
-      <c r="Z12" s="41"/>
-      <c r="AA12" s="41"/>
-      <c r="AB12" s="41"/>
-      <c r="AC12" s="41"/>
-      <c r="AD12" s="41"/>
-      <c r="AE12" s="35"/>
+      <c r="O12" s="42"/>
+      <c r="P12" s="43"/>
+      <c r="Q12" s="43"/>
+      <c r="R12" s="43"/>
+      <c r="S12" s="43"/>
+      <c r="T12" s="43"/>
+      <c r="U12" s="43"/>
+      <c r="V12" s="43"/>
+      <c r="W12" s="43"/>
+      <c r="X12" s="43"/>
+      <c r="Y12" s="43"/>
+      <c r="Z12" s="43"/>
+      <c r="AA12" s="43"/>
+      <c r="AB12" s="43"/>
+      <c r="AC12" s="43"/>
+      <c r="AD12" s="43"/>
+      <c r="AE12" s="37"/>
     </row>
     <row r="13">
-      <c r="A13" s="44"/>
-      <c r="F13" s="46"/>
-      <c r="H13" s="3"/>
-      <c r="M13" s="30"/>
-      <c r="N13" s="38" t="s">
+      <c r="A13" s="46"/>
+      <c r="F13" s="48"/>
+      <c r="H13" s="7"/>
+      <c r="M13" s="32"/>
+      <c r="N13" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="O13" s="41"/>
-      <c r="P13" s="41"/>
-      <c r="Q13" s="41"/>
-      <c r="R13" s="41"/>
-      <c r="S13" s="41"/>
-      <c r="T13" s="41"/>
-      <c r="U13" s="41"/>
-      <c r="V13" s="41"/>
-      <c r="W13" s="41"/>
-      <c r="X13" s="41"/>
-      <c r="Y13" s="41"/>
-      <c r="Z13" s="41"/>
-      <c r="AA13" s="41"/>
-      <c r="AB13" s="41"/>
-      <c r="AC13" s="41"/>
-      <c r="AD13" s="41"/>
-      <c r="AE13" s="35"/>
+      <c r="O13" s="43"/>
+      <c r="P13" s="43"/>
+      <c r="Q13" s="43"/>
+      <c r="R13" s="43"/>
+      <c r="S13" s="43"/>
+      <c r="T13" s="43"/>
+      <c r="U13" s="43"/>
+      <c r="V13" s="43"/>
+      <c r="W13" s="43"/>
+      <c r="X13" s="43"/>
+      <c r="Y13" s="43"/>
+      <c r="Z13" s="43"/>
+      <c r="AA13" s="43"/>
+      <c r="AB13" s="43"/>
+      <c r="AC13" s="43"/>
+      <c r="AD13" s="43"/>
+      <c r="AE13" s="37"/>
     </row>
     <row r="14">
-      <c r="A14" s="44"/>
-      <c r="F14" s="46"/>
-      <c r="H14" s="3"/>
-      <c r="M14" s="30"/>
-      <c r="N14" s="38" t="s">
+      <c r="A14" s="46"/>
+      <c r="F14" s="48"/>
+      <c r="H14" s="7"/>
+      <c r="M14" s="32"/>
+      <c r="N14" s="40" t="s">
         <v>63</v>
       </c>
-      <c r="O14" s="41"/>
-      <c r="P14" s="41"/>
-      <c r="Q14" s="41"/>
-      <c r="R14" s="41"/>
-      <c r="S14" s="41"/>
-      <c r="T14" s="41"/>
-      <c r="U14" s="41"/>
-      <c r="V14" s="41"/>
-      <c r="W14" s="41"/>
-      <c r="X14" s="41"/>
-      <c r="Y14" s="41"/>
-      <c r="Z14" s="41"/>
-      <c r="AA14" s="41"/>
-      <c r="AB14" s="41"/>
-      <c r="AC14" s="41"/>
-      <c r="AD14" s="41"/>
-      <c r="AE14" s="35"/>
+      <c r="O14" s="43"/>
+      <c r="P14" s="43"/>
+      <c r="Q14" s="43"/>
+      <c r="R14" s="43"/>
+      <c r="S14" s="43"/>
+      <c r="T14" s="43"/>
+      <c r="U14" s="43"/>
+      <c r="V14" s="43"/>
+      <c r="W14" s="43"/>
+      <c r="X14" s="43"/>
+      <c r="Y14" s="43"/>
+      <c r="Z14" s="43"/>
+      <c r="AA14" s="43"/>
+      <c r="AB14" s="43"/>
+      <c r="AC14" s="43"/>
+      <c r="AD14" s="43"/>
+      <c r="AE14" s="37"/>
     </row>
     <row r="15">
-      <c r="A15" s="44"/>
-      <c r="B15" s="47" t="s">
+      <c r="A15" s="46"/>
+      <c r="B15" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="C15" s="48"/>
-      <c r="D15" s="48"/>
-      <c r="E15" s="49"/>
-      <c r="F15" s="46"/>
-      <c r="H15" s="3"/>
-      <c r="M15" s="30"/>
-      <c r="N15" s="38" t="s">
+      <c r="C15" s="50"/>
+      <c r="D15" s="50"/>
+      <c r="E15" s="51"/>
+      <c r="F15" s="48"/>
+      <c r="H15" s="7"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="40" t="s">
         <v>65</v>
       </c>
-      <c r="O15" s="41"/>
-      <c r="P15" s="41"/>
-      <c r="Q15" s="41"/>
-      <c r="R15" s="41"/>
-      <c r="S15" s="41"/>
-      <c r="T15" s="41"/>
-      <c r="U15" s="41"/>
-      <c r="V15" s="41"/>
-      <c r="W15" s="41"/>
-      <c r="X15" s="41"/>
-      <c r="Y15" s="41"/>
-      <c r="Z15" s="41"/>
-      <c r="AA15" s="41"/>
-      <c r="AB15" s="41"/>
-      <c r="AC15" s="41"/>
-      <c r="AD15" s="41"/>
-      <c r="AE15" s="35"/>
+      <c r="O15" s="43"/>
+      <c r="P15" s="43"/>
+      <c r="Q15" s="43"/>
+      <c r="R15" s="43"/>
+      <c r="S15" s="43"/>
+      <c r="T15" s="43"/>
+      <c r="U15" s="43"/>
+      <c r="V15" s="43"/>
+      <c r="W15" s="43"/>
+      <c r="X15" s="43"/>
+      <c r="Y15" s="43"/>
+      <c r="Z15" s="43"/>
+      <c r="AA15" s="43"/>
+      <c r="AB15" s="43"/>
+      <c r="AC15" s="43"/>
+      <c r="AD15" s="43"/>
+      <c r="AE15" s="37"/>
     </row>
     <row r="16">
-      <c r="A16" s="44"/>
-      <c r="B16" s="50"/>
-      <c r="C16" s="51" t="s">
-        <v>57</v>
-      </c>
-      <c r="D16" s="52" t="s">
-        <v>22</v>
-      </c>
-      <c r="E16" s="53"/>
-      <c r="F16" s="46"/>
-      <c r="H16" s="3"/>
-      <c r="M16" s="30"/>
-      <c r="N16" s="54" t="s">
+      <c r="A16" s="46"/>
+      <c r="B16" s="52"/>
+      <c r="C16" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="54" t="s">
+        <v>4</v>
+      </c>
+      <c r="E16" s="55"/>
+      <c r="F16" s="48"/>
+      <c r="H16" s="7"/>
+      <c r="M16" s="32"/>
+      <c r="N16" s="56" t="s">
         <v>66</v>
       </c>
-      <c r="O16" s="41"/>
-      <c r="P16" s="41"/>
-      <c r="Q16" s="41"/>
-      <c r="R16" s="41"/>
-      <c r="S16" s="41"/>
-      <c r="T16" s="41"/>
-      <c r="U16" s="41"/>
-      <c r="V16" s="41"/>
-      <c r="W16" s="41"/>
-      <c r="X16" s="41"/>
-      <c r="Y16" s="41"/>
-      <c r="Z16" s="41"/>
-      <c r="AA16" s="41"/>
-      <c r="AB16" s="41"/>
-      <c r="AC16" s="41"/>
-      <c r="AD16" s="41"/>
-      <c r="AE16" s="35"/>
+      <c r="O16" s="43"/>
+      <c r="P16" s="43"/>
+      <c r="Q16" s="43"/>
+      <c r="R16" s="43"/>
+      <c r="S16" s="43"/>
+      <c r="T16" s="43"/>
+      <c r="U16" s="43"/>
+      <c r="V16" s="43"/>
+      <c r="W16" s="43"/>
+      <c r="X16" s="43"/>
+      <c r="Y16" s="43"/>
+      <c r="Z16" s="43"/>
+      <c r="AA16" s="43"/>
+      <c r="AB16" s="43"/>
+      <c r="AC16" s="43"/>
+      <c r="AD16" s="43"/>
+      <c r="AE16" s="37"/>
     </row>
     <row r="17">
-      <c r="A17" s="44"/>
-      <c r="B17" s="50"/>
-      <c r="C17" s="51" t="s">
-        <v>57</v>
-      </c>
-      <c r="D17" s="52" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" s="53"/>
-      <c r="F17" s="46"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="M17" s="30"/>
-      <c r="N17" s="54" t="s">
+      <c r="A17" s="46"/>
+      <c r="B17" s="52"/>
+      <c r="C17" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="54" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" s="55"/>
+      <c r="F17" s="48"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="M17" s="32"/>
+      <c r="N17" s="56" t="s">
         <v>67</v>
       </c>
-      <c r="O17" s="41"/>
-      <c r="P17" s="41"/>
-      <c r="Q17" s="41"/>
-      <c r="R17" s="41"/>
-      <c r="S17" s="41"/>
-      <c r="T17" s="41"/>
-      <c r="U17" s="41"/>
-      <c r="V17" s="41"/>
-      <c r="W17" s="41"/>
-      <c r="X17" s="41"/>
-      <c r="Y17" s="41"/>
-      <c r="Z17" s="41"/>
-      <c r="AA17" s="41"/>
-      <c r="AB17" s="41"/>
-      <c r="AC17" s="41"/>
-      <c r="AD17" s="41"/>
-      <c r="AE17" s="35"/>
+      <c r="O17" s="43"/>
+      <c r="P17" s="43"/>
+      <c r="Q17" s="43"/>
+      <c r="R17" s="43"/>
+      <c r="S17" s="43"/>
+      <c r="T17" s="43"/>
+      <c r="U17" s="43"/>
+      <c r="V17" s="43"/>
+      <c r="W17" s="43"/>
+      <c r="X17" s="43"/>
+      <c r="Y17" s="43"/>
+      <c r="Z17" s="43"/>
+      <c r="AA17" s="43"/>
+      <c r="AB17" s="43"/>
+      <c r="AC17" s="43"/>
+      <c r="AD17" s="43"/>
+      <c r="AE17" s="37"/>
     </row>
     <row r="18">
-      <c r="A18" s="44"/>
-      <c r="B18" s="50"/>
-      <c r="C18" s="51" t="s">
-        <v>57</v>
-      </c>
-      <c r="D18" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="53"/>
-      <c r="F18" s="55"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="M18" s="30"/>
-      <c r="N18" s="54" t="s">
+      <c r="A18" s="46"/>
+      <c r="B18" s="52"/>
+      <c r="C18" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" s="54" t="s">
+        <v>6</v>
+      </c>
+      <c r="E18" s="55"/>
+      <c r="F18" s="57"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="M18" s="32"/>
+      <c r="N18" s="56" t="s">
         <v>68</v>
       </c>
-      <c r="O18" s="41"/>
-      <c r="P18" s="41"/>
-      <c r="Q18" s="41"/>
-      <c r="R18" s="41"/>
-      <c r="S18" s="41"/>
-      <c r="T18" s="41"/>
-      <c r="U18" s="41"/>
-      <c r="V18" s="41"/>
-      <c r="W18" s="41"/>
-      <c r="X18" s="41"/>
-      <c r="Y18" s="41"/>
-      <c r="Z18" s="41"/>
-      <c r="AA18" s="41"/>
-      <c r="AB18" s="41"/>
-      <c r="AC18" s="41"/>
-      <c r="AD18" s="41"/>
-      <c r="AE18" s="35"/>
+      <c r="O18" s="43"/>
+      <c r="P18" s="43"/>
+      <c r="Q18" s="43"/>
+      <c r="R18" s="43"/>
+      <c r="S18" s="43"/>
+      <c r="T18" s="43"/>
+      <c r="U18" s="43"/>
+      <c r="V18" s="43"/>
+      <c r="W18" s="43"/>
+      <c r="X18" s="43"/>
+      <c r="Y18" s="43"/>
+      <c r="Z18" s="43"/>
+      <c r="AA18" s="43"/>
+      <c r="AB18" s="43"/>
+      <c r="AC18" s="43"/>
+      <c r="AD18" s="43"/>
+      <c r="AE18" s="37"/>
     </row>
     <row r="19">
-      <c r="A19" s="44"/>
-      <c r="B19" s="50"/>
-      <c r="C19" s="51" t="s">
-        <v>57</v>
-      </c>
-      <c r="D19" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="E19" s="53"/>
-      <c r="F19" s="55"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="M19" s="30"/>
-      <c r="N19" s="54" t="s">
+      <c r="A19" s="46"/>
+      <c r="B19" s="52"/>
+      <c r="C19" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" s="54" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="55"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="M19" s="32"/>
+      <c r="N19" s="56" t="s">
         <v>69</v>
       </c>
-      <c r="O19" s="41"/>
-      <c r="P19" s="41"/>
-      <c r="Q19" s="41"/>
-      <c r="R19" s="41"/>
-      <c r="S19" s="41"/>
-      <c r="T19" s="41"/>
-      <c r="U19" s="41"/>
-      <c r="V19" s="41"/>
-      <c r="W19" s="41"/>
-      <c r="X19" s="41"/>
-      <c r="Y19" s="41"/>
-      <c r="Z19" s="41"/>
-      <c r="AA19" s="41"/>
-      <c r="AB19" s="41"/>
-      <c r="AC19" s="41"/>
-      <c r="AD19" s="41"/>
-      <c r="AE19" s="35"/>
+      <c r="O19" s="43"/>
+      <c r="P19" s="43"/>
+      <c r="Q19" s="43"/>
+      <c r="R19" s="43"/>
+      <c r="S19" s="43"/>
+      <c r="T19" s="43"/>
+      <c r="U19" s="43"/>
+      <c r="V19" s="43"/>
+      <c r="W19" s="43"/>
+      <c r="X19" s="43"/>
+      <c r="Y19" s="43"/>
+      <c r="Z19" s="43"/>
+      <c r="AA19" s="43"/>
+      <c r="AB19" s="43"/>
+      <c r="AC19" s="43"/>
+      <c r="AD19" s="43"/>
+      <c r="AE19" s="37"/>
     </row>
     <row r="20">
-      <c r="A20" s="44"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="51" t="s">
-        <v>57</v>
-      </c>
-      <c r="D20" s="56" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" s="12"/>
-      <c r="F20" s="57"/>
-      <c r="G20" s="15"/>
-      <c r="M20" s="30"/>
-      <c r="N20" s="54" t="s">
+      <c r="A20" s="46"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="14"/>
+      <c r="F20" s="59"/>
+      <c r="G20" s="17"/>
+      <c r="M20" s="32"/>
+      <c r="N20" s="56" t="s">
         <v>70</v>
       </c>
-      <c r="O20" s="41"/>
-      <c r="P20" s="41"/>
-      <c r="Q20" s="41"/>
-      <c r="R20" s="41"/>
-      <c r="S20" s="41"/>
-      <c r="T20" s="41"/>
-      <c r="U20" s="41"/>
-      <c r="V20" s="41"/>
-      <c r="W20" s="41"/>
-      <c r="X20" s="41"/>
-      <c r="Y20" s="41"/>
-      <c r="Z20" s="41"/>
-      <c r="AA20" s="41"/>
-      <c r="AB20" s="41"/>
-      <c r="AC20" s="41"/>
-      <c r="AD20" s="41"/>
-      <c r="AE20" s="35"/>
+      <c r="O20" s="43"/>
+      <c r="P20" s="43"/>
+      <c r="Q20" s="43"/>
+      <c r="R20" s="43"/>
+      <c r="S20" s="43"/>
+      <c r="T20" s="43"/>
+      <c r="U20" s="43"/>
+      <c r="V20" s="43"/>
+      <c r="W20" s="43"/>
+      <c r="X20" s="43"/>
+      <c r="Y20" s="43"/>
+      <c r="Z20" s="43"/>
+      <c r="AA20" s="43"/>
+      <c r="AB20" s="43"/>
+      <c r="AC20" s="43"/>
+      <c r="AD20" s="43"/>
+      <c r="AE20" s="37"/>
     </row>
     <row r="21">
-      <c r="A21" s="44"/>
-      <c r="C21" s="51" t="s">
-        <v>57</v>
-      </c>
-      <c r="D21" s="56" t="s">
-        <v>28</v>
-      </c>
-      <c r="F21" s="46"/>
-      <c r="G21" s="15"/>
-      <c r="M21" s="30"/>
-      <c r="N21" s="54" t="s">
+      <c r="A21" s="46"/>
+      <c r="C21" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" s="48"/>
+      <c r="G21" s="17"/>
+      <c r="M21" s="32"/>
+      <c r="N21" s="56" t="s">
         <v>71</v>
       </c>
-      <c r="O21" s="41"/>
-      <c r="P21" s="41"/>
-      <c r="Q21" s="41"/>
-      <c r="R21" s="41"/>
-      <c r="S21" s="41"/>
-      <c r="T21" s="41"/>
-      <c r="U21" s="41"/>
-      <c r="V21" s="41"/>
-      <c r="W21" s="41"/>
-      <c r="X21" s="41"/>
-      <c r="Y21" s="41"/>
-      <c r="Z21" s="41"/>
-      <c r="AA21" s="41"/>
-      <c r="AB21" s="41"/>
-      <c r="AC21" s="41"/>
-      <c r="AD21" s="41"/>
-      <c r="AE21" s="35"/>
+      <c r="O21" s="43"/>
+      <c r="P21" s="43"/>
+      <c r="Q21" s="43"/>
+      <c r="R21" s="43"/>
+      <c r="S21" s="43"/>
+      <c r="T21" s="43"/>
+      <c r="U21" s="43"/>
+      <c r="V21" s="43"/>
+      <c r="W21" s="43"/>
+      <c r="X21" s="43"/>
+      <c r="Y21" s="43"/>
+      <c r="Z21" s="43"/>
+      <c r="AA21" s="43"/>
+      <c r="AB21" s="43"/>
+      <c r="AC21" s="43"/>
+      <c r="AD21" s="43"/>
+      <c r="AE21" s="37"/>
     </row>
     <row r="22">
-      <c r="A22" s="58"/>
-      <c r="B22" s="59"/>
-      <c r="C22" s="60"/>
-      <c r="D22" s="60"/>
-      <c r="E22" s="60"/>
-      <c r="F22" s="61"/>
-      <c r="G22" s="15"/>
-      <c r="M22" s="30"/>
-      <c r="N22" s="54" t="s">
+      <c r="A22" s="60"/>
+      <c r="B22" s="61"/>
+      <c r="C22" s="62"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="62"/>
+      <c r="F22" s="63"/>
+      <c r="G22" s="17"/>
+      <c r="M22" s="32"/>
+      <c r="N22" s="56" t="s">
         <v>72</v>
       </c>
-      <c r="O22" s="41"/>
-      <c r="P22" s="41"/>
-      <c r="Q22" s="41"/>
-      <c r="R22" s="41"/>
-      <c r="S22" s="41"/>
-      <c r="T22" s="41"/>
-      <c r="U22" s="41"/>
-      <c r="V22" s="41"/>
-      <c r="W22" s="41"/>
-      <c r="X22" s="41"/>
-      <c r="Y22" s="41"/>
-      <c r="Z22" s="41"/>
-      <c r="AA22" s="41"/>
-      <c r="AB22" s="41"/>
-      <c r="AC22" s="41"/>
-      <c r="AD22" s="62"/>
-      <c r="AE22" s="35"/>
+      <c r="O22" s="43"/>
+      <c r="P22" s="43"/>
+      <c r="Q22" s="43"/>
+      <c r="R22" s="43"/>
+      <c r="S22" s="43"/>
+      <c r="T22" s="43"/>
+      <c r="U22" s="43"/>
+      <c r="V22" s="43"/>
+      <c r="W22" s="43"/>
+      <c r="X22" s="43"/>
+      <c r="Y22" s="43"/>
+      <c r="Z22" s="43"/>
+      <c r="AA22" s="43"/>
+      <c r="AB22" s="43"/>
+      <c r="AC22" s="43"/>
+      <c r="AD22" s="64"/>
+      <c r="AE22" s="37"/>
     </row>
     <row r="23">
-      <c r="A23" s="15"/>
-      <c r="B23" s="63"/>
-      <c r="G23" s="15"/>
-      <c r="M23" s="30"/>
-      <c r="N23" s="54" t="s">
+      <c r="A23" s="17"/>
+      <c r="B23" s="65"/>
+      <c r="G23" s="17"/>
+      <c r="M23" s="32"/>
+      <c r="N23" s="56" t="s">
         <v>73</v>
       </c>
-      <c r="O23" s="41"/>
-      <c r="P23" s="41"/>
-      <c r="Q23" s="41"/>
-      <c r="R23" s="41"/>
-      <c r="S23" s="41"/>
-      <c r="T23" s="41"/>
-      <c r="U23" s="41"/>
-      <c r="V23" s="41"/>
-      <c r="W23" s="41"/>
-      <c r="X23" s="41"/>
-      <c r="Y23" s="41"/>
-      <c r="Z23" s="41"/>
-      <c r="AA23" s="41"/>
-      <c r="AB23" s="41"/>
-      <c r="AC23" s="64"/>
-      <c r="AD23" s="41"/>
-      <c r="AE23" s="65"/>
+      <c r="O23" s="43"/>
+      <c r="P23" s="43"/>
+      <c r="Q23" s="43"/>
+      <c r="R23" s="43"/>
+      <c r="S23" s="43"/>
+      <c r="T23" s="43"/>
+      <c r="U23" s="43"/>
+      <c r="V23" s="43"/>
+      <c r="W23" s="43"/>
+      <c r="X23" s="43"/>
+      <c r="Y23" s="43"/>
+      <c r="Z23" s="43"/>
+      <c r="AA23" s="43"/>
+      <c r="AB23" s="43"/>
+      <c r="AC23" s="66"/>
+      <c r="AD23" s="43"/>
+      <c r="AE23" s="67"/>
     </row>
     <row r="24">
-      <c r="A24" s="15"/>
-      <c r="B24" s="63"/>
-      <c r="G24" s="15"/>
-      <c r="M24" s="30"/>
-      <c r="N24" s="12"/>
-      <c r="O24" s="12"/>
-      <c r="P24" s="12"/>
-      <c r="Q24" s="12"/>
-      <c r="R24" s="12"/>
-      <c r="S24" s="12"/>
-      <c r="T24" s="12"/>
-      <c r="U24" s="12"/>
-      <c r="V24" s="12"/>
-      <c r="W24" s="12"/>
-      <c r="X24" s="12"/>
-      <c r="Y24" s="12"/>
-      <c r="Z24" s="12"/>
-      <c r="AA24" s="12"/>
-      <c r="AB24" s="12"/>
-      <c r="AC24" s="12"/>
-      <c r="AD24" s="21"/>
-      <c r="AE24" s="65"/>
+      <c r="A24" s="17"/>
+      <c r="B24" s="65"/>
+      <c r="G24" s="17"/>
+      <c r="M24" s="32"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14"/>
+      <c r="P24" s="14"/>
+      <c r="Q24" s="14"/>
+      <c r="R24" s="14"/>
+      <c r="S24" s="14"/>
+      <c r="T24" s="14"/>
+      <c r="U24" s="14"/>
+      <c r="V24" s="14"/>
+      <c r="W24" s="14"/>
+      <c r="X24" s="14"/>
+      <c r="Y24" s="14"/>
+      <c r="Z24" s="14"/>
+      <c r="AA24" s="14"/>
+      <c r="AB24" s="14"/>
+      <c r="AC24" s="14"/>
+      <c r="AD24" s="23"/>
+      <c r="AE24" s="67"/>
     </row>
     <row r="25">
-      <c r="A25" s="15"/>
-      <c r="B25" s="63"/>
-      <c r="G25" s="15"/>
-      <c r="K25" s="66"/>
-      <c r="M25" s="67"/>
-      <c r="N25" s="60"/>
-      <c r="O25" s="60"/>
-      <c r="P25" s="60"/>
-      <c r="Q25" s="60"/>
-      <c r="R25" s="60"/>
-      <c r="S25" s="60"/>
-      <c r="T25" s="60"/>
-      <c r="U25" s="60"/>
-      <c r="V25" s="60"/>
-      <c r="W25" s="60"/>
-      <c r="X25" s="60"/>
-      <c r="Y25" s="60"/>
-      <c r="Z25" s="60"/>
-      <c r="AA25" s="60"/>
-      <c r="AB25" s="60"/>
-      <c r="AC25" s="60"/>
-      <c r="AD25" s="68"/>
-      <c r="AE25" s="69"/>
+      <c r="A25" s="17"/>
+      <c r="B25" s="65"/>
+      <c r="G25" s="17"/>
+      <c r="K25" s="68"/>
+      <c r="M25" s="69"/>
+      <c r="N25" s="62"/>
+      <c r="O25" s="62"/>
+      <c r="P25" s="62"/>
+      <c r="Q25" s="62"/>
+      <c r="R25" s="62"/>
+      <c r="S25" s="62"/>
+      <c r="T25" s="62"/>
+      <c r="U25" s="62"/>
+      <c r="V25" s="62"/>
+      <c r="W25" s="62"/>
+      <c r="X25" s="62"/>
+      <c r="Y25" s="62"/>
+      <c r="Z25" s="62"/>
+      <c r="AA25" s="62"/>
+      <c r="AB25" s="62"/>
+      <c r="AC25" s="62"/>
+      <c r="AD25" s="70"/>
+      <c r="AE25" s="71"/>
     </row>
     <row r="26">
-      <c r="A26" s="15"/>
-      <c r="B26" s="63"/>
-      <c r="G26" s="15"/>
+      <c r="A26" s="17"/>
+      <c r="B26" s="65"/>
+      <c r="G26" s="17"/>
     </row>
     <row r="27">
-      <c r="B27" s="63"/>
-      <c r="G27" s="15"/>
+      <c r="B27" s="65"/>
+      <c r="G27" s="17"/>
     </row>
     <row r="28">
-      <c r="A28" s="15"/>
-      <c r="B28" s="63"/>
-      <c r="G28" s="15"/>
-      <c r="J28" s="12"/>
-      <c r="K28" s="36"/>
-      <c r="L28" s="36"/>
-      <c r="M28" s="36"/>
-      <c r="N28" s="36"/>
-      <c r="O28" s="36"/>
-      <c r="P28" s="36"/>
-      <c r="Q28" s="36"/>
-      <c r="R28" s="36"/>
-      <c r="S28" s="36"/>
+      <c r="A28" s="17"/>
+      <c r="B28" s="65"/>
+      <c r="G28" s="17"/>
+      <c r="J28" s="14"/>
+      <c r="K28" s="38"/>
+      <c r="L28" s="38"/>
+      <c r="M28" s="38"/>
+      <c r="N28" s="38"/>
+      <c r="O28" s="38"/>
+      <c r="P28" s="38"/>
+      <c r="Q28" s="38"/>
+      <c r="R28" s="38"/>
+      <c r="S28" s="38"/>
     </row>
     <row r="29">
-      <c r="F29" s="70" t="s">
+      <c r="F29" s="72" t="s">
         <v>74</v>
       </c>
-      <c r="G29" s="71"/>
-      <c r="H29" s="71"/>
-      <c r="I29" s="71"/>
-      <c r="J29" s="50"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
-      <c r="M29" s="12"/>
-      <c r="N29" s="12"/>
-      <c r="O29" s="12"/>
-      <c r="P29" s="12"/>
-      <c r="Q29" s="12"/>
-      <c r="R29" s="12"/>
-      <c r="S29" s="12"/>
-      <c r="T29" s="12"/>
-      <c r="U29" s="12"/>
+      <c r="G29" s="73"/>
+      <c r="H29" s="73"/>
+      <c r="I29" s="73"/>
+      <c r="J29" s="52"/>
+      <c r="K29" s="14"/>
+      <c r="L29" s="14"/>
+      <c r="M29" s="14"/>
+      <c r="N29" s="14"/>
+      <c r="O29" s="14"/>
+      <c r="P29" s="14"/>
+      <c r="Q29" s="14"/>
+      <c r="R29" s="14"/>
+      <c r="S29" s="14"/>
+      <c r="T29" s="14"/>
+      <c r="U29" s="14"/>
     </row>
     <row r="30">
-      <c r="A30" s="72"/>
-      <c r="B30" s="43"/>
-      <c r="C30" s="43"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="43"/>
-      <c r="F30" s="43"/>
-      <c r="G30" s="43"/>
-      <c r="H30" s="43"/>
-      <c r="I30" s="26"/>
-      <c r="J30" s="73"/>
-      <c r="K30" s="31"/>
-      <c r="L30" s="12"/>
-      <c r="M30" s="12"/>
-      <c r="N30" s="12"/>
-      <c r="O30" s="74"/>
-      <c r="P30" s="32"/>
-      <c r="Q30" s="32"/>
-      <c r="R30" s="32"/>
-      <c r="S30" s="32"/>
-      <c r="T30" s="32"/>
-      <c r="U30" s="32"/>
+      <c r="A30" s="74"/>
+      <c r="B30" s="45"/>
+      <c r="C30" s="45"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="45"/>
+      <c r="F30" s="45"/>
+      <c r="G30" s="45"/>
+      <c r="H30" s="45"/>
+      <c r="I30" s="28"/>
+      <c r="J30" s="75"/>
+      <c r="K30" s="33"/>
+      <c r="L30" s="14"/>
+      <c r="M30" s="14"/>
+      <c r="N30" s="14"/>
+      <c r="O30" s="76"/>
+      <c r="P30" s="34"/>
+      <c r="Q30" s="34"/>
+      <c r="R30" s="34"/>
+      <c r="S30" s="34"/>
+      <c r="T30" s="34"/>
+      <c r="U30" s="34"/>
     </row>
     <row r="31">
-      <c r="A31" s="75" t="s">
+      <c r="A31" s="77" t="s">
         <v>75</v>
       </c>
-      <c r="B31" s="76"/>
-      <c r="E31" s="75" t="s">
+      <c r="B31" s="78"/>
+      <c r="E31" s="77" t="s">
         <v>76</v>
       </c>
-      <c r="F31" s="76"/>
-      <c r="I31" s="46"/>
-      <c r="J31" s="73"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="12"/>
-      <c r="M31" s="12"/>
-      <c r="N31" s="12"/>
-      <c r="O31" s="74"/>
-      <c r="P31" s="32"/>
-      <c r="Q31" s="32"/>
-      <c r="R31" s="32"/>
-      <c r="S31" s="32"/>
-      <c r="T31" s="32"/>
-      <c r="U31" s="32"/>
+      <c r="F31" s="78"/>
+      <c r="I31" s="48"/>
+      <c r="J31" s="75"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
+      <c r="M31" s="14"/>
+      <c r="N31" s="14"/>
+      <c r="O31" s="76"/>
+      <c r="P31" s="34"/>
+      <c r="Q31" s="34"/>
+      <c r="R31" s="34"/>
+      <c r="S31" s="34"/>
+      <c r="T31" s="34"/>
+      <c r="U31" s="34"/>
     </row>
     <row r="32">
-      <c r="A32" s="44"/>
-      <c r="B32" s="21"/>
-      <c r="C32" s="21"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="21"/>
-      <c r="F32" s="21"/>
-      <c r="I32" s="46"/>
-      <c r="J32" s="53"/>
-      <c r="K32" s="21"/>
-      <c r="L32" s="21"/>
-      <c r="M32" s="21"/>
-      <c r="N32" s="21"/>
-      <c r="O32" s="77"/>
-      <c r="P32" s="21"/>
-      <c r="Q32" s="21"/>
-      <c r="S32" s="21"/>
+      <c r="A32" s="46"/>
+      <c r="B32" s="23"/>
+      <c r="C32" s="23"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="23"/>
+      <c r="I32" s="48"/>
+      <c r="J32" s="55"/>
+      <c r="K32" s="23"/>
+      <c r="L32" s="23"/>
+      <c r="M32" s="23"/>
+      <c r="N32" s="23"/>
+      <c r="O32" s="79"/>
+      <c r="P32" s="23"/>
+      <c r="Q32" s="23"/>
+      <c r="S32" s="23"/>
     </row>
     <row r="33">
-      <c r="A33" s="30"/>
-      <c r="B33" s="12"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="I33" s="46"/>
-      <c r="J33" s="53"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="12"/>
-      <c r="M33" s="12"/>
-      <c r="N33" s="12"/>
-      <c r="O33" s="31"/>
-      <c r="P33" s="12"/>
-      <c r="Q33" s="12"/>
-      <c r="R33" s="12"/>
-      <c r="S33" s="12"/>
+      <c r="A33" s="32"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="I33" s="48"/>
+      <c r="J33" s="55"/>
+      <c r="K33" s="14"/>
+      <c r="L33" s="14"/>
+      <c r="M33" s="14"/>
+      <c r="N33" s="14"/>
+      <c r="O33" s="33"/>
+      <c r="P33" s="14"/>
+      <c r="Q33" s="14"/>
+      <c r="R33" s="14"/>
+      <c r="S33" s="14"/>
     </row>
     <row r="34">
-      <c r="A34" s="30"/>
-      <c r="B34" s="12"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="50"/>
-      <c r="G34" s="78" t="s">
+      <c r="A34" s="32"/>
+      <c r="B34" s="14"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="52"/>
+      <c r="G34" s="80" t="s">
         <v>77</v>
       </c>
-      <c r="H34" s="79"/>
-      <c r="I34" s="46"/>
-      <c r="O34" s="15"/>
+      <c r="H34" s="81"/>
+      <c r="I34" s="48"/>
+      <c r="O34" s="17"/>
     </row>
     <row r="35">
-      <c r="A35" s="30"/>
-      <c r="B35" s="80" t="s">
-        <v>57</v>
-      </c>
-      <c r="C35" s="12"/>
-      <c r="D35" s="80" t="s">
+      <c r="A35" s="32"/>
+      <c r="B35" s="82" t="s">
+        <v>21</v>
+      </c>
+      <c r="C35" s="14"/>
+      <c r="D35" s="82" t="s">
         <v>78</v>
       </c>
-      <c r="E35" s="31"/>
-      <c r="F35" s="81"/>
-      <c r="G35" s="82" t="s">
+      <c r="E35" s="33"/>
+      <c r="F35" s="83"/>
+      <c r="G35" s="84" t="s">
         <v>79</v>
       </c>
-      <c r="H35" s="83"/>
-      <c r="I35" s="46"/>
-      <c r="O35" s="15"/>
+      <c r="H35" s="85"/>
+      <c r="I35" s="48"/>
+      <c r="O35" s="17"/>
     </row>
     <row r="36">
-      <c r="A36" s="30"/>
-      <c r="B36" s="12"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
-      <c r="E36" s="80" t="s">
+      <c r="A36" s="32"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="82" t="s">
         <v>80</v>
       </c>
-      <c r="F36" s="12"/>
-      <c r="I36" s="46"/>
-      <c r="O36" s="15"/>
+      <c r="F36" s="14"/>
+      <c r="I36" s="48"/>
+      <c r="O36" s="17"/>
     </row>
     <row r="37">
-      <c r="A37" s="30"/>
-      <c r="B37" s="12"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="12"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
-      <c r="G37" s="84" t="s">
+      <c r="A37" s="32"/>
+      <c r="B37" s="14"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="86" t="s">
         <v>81</v>
       </c>
-      <c r="H37" s="85"/>
-      <c r="I37" s="86"/>
-      <c r="K37" s="36"/>
-      <c r="L37" s="12"/>
-      <c r="O37" s="15"/>
+      <c r="H37" s="87"/>
+      <c r="I37" s="88"/>
+      <c r="K37" s="38"/>
+      <c r="L37" s="14"/>
+      <c r="O37" s="17"/>
     </row>
     <row r="38">
-      <c r="A38" s="30"/>
-      <c r="B38" s="12"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="12"/>
-      <c r="E38" s="12"/>
-      <c r="F38" s="12"/>
-      <c r="G38" s="76" t="s">
+      <c r="A38" s="32"/>
+      <c r="B38" s="14"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="78" t="s">
         <v>82</v>
       </c>
-      <c r="H38" s="76" t="s">
+      <c r="H38" s="78" t="s">
         <v>83</v>
       </c>
-      <c r="I38" s="76" t="s">
+      <c r="I38" s="78" t="s">
         <v>84</v>
       </c>
-      <c r="L38" s="53"/>
-      <c r="O38" s="15"/>
+      <c r="L38" s="55"/>
+      <c r="O38" s="17"/>
     </row>
     <row r="39">
-      <c r="A39" s="30"/>
-      <c r="B39" s="12"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="12"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="87">
+      <c r="A39" s="32"/>
+      <c r="B39" s="14"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="14"/>
+      <c r="G39" s="89">
         <v>0.0</v>
       </c>
-      <c r="H39" s="87">
+      <c r="H39" s="89">
         <v>0.0</v>
       </c>
-      <c r="I39" s="87">
+      <c r="I39" s="89">
         <v>0.0</v>
       </c>
-      <c r="L39" s="53"/>
-      <c r="O39" s="15"/>
+      <c r="L39" s="55"/>
+      <c r="O39" s="17"/>
     </row>
     <row r="40">
-      <c r="A40" s="30"/>
-      <c r="B40" s="12"/>
-      <c r="C40" s="80" t="s">
+      <c r="A40" s="32"/>
+      <c r="B40" s="14"/>
+      <c r="C40" s="82" t="s">
         <v>78</v>
       </c>
-      <c r="D40" s="12"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12"/>
-      <c r="G40" s="12"/>
-      <c r="H40" s="50"/>
-      <c r="I40" s="88"/>
-      <c r="J40" s="89"/>
-      <c r="K40" s="90"/>
-      <c r="L40" s="53"/>
-      <c r="O40" s="15"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="14"/>
+      <c r="H40" s="52"/>
+      <c r="I40" s="90"/>
+      <c r="J40" s="91"/>
+      <c r="K40" s="92"/>
+      <c r="L40" s="55"/>
+      <c r="O40" s="17"/>
     </row>
     <row r="41">
-      <c r="A41" s="30"/>
-      <c r="B41" s="12"/>
-      <c r="C41" s="12"/>
-      <c r="D41" s="12"/>
-      <c r="E41" s="12"/>
-      <c r="F41" s="12"/>
-      <c r="G41" s="12"/>
-      <c r="H41" s="12"/>
-      <c r="I41" s="91"/>
-      <c r="J41" s="92"/>
-      <c r="K41" s="21"/>
-      <c r="L41" s="12"/>
-      <c r="O41" s="15"/>
+      <c r="A41" s="32"/>
+      <c r="B41" s="14"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="14"/>
+      <c r="H41" s="14"/>
+      <c r="I41" s="93"/>
+      <c r="J41" s="94"/>
+      <c r="K41" s="23"/>
+      <c r="L41" s="14"/>
+      <c r="O41" s="17"/>
     </row>
     <row r="42">
-      <c r="A42" s="30"/>
-      <c r="B42" s="12"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="12"/>
-      <c r="E42" s="12"/>
-      <c r="F42" s="12"/>
-      <c r="G42" s="12"/>
-      <c r="H42" s="12"/>
-      <c r="I42" s="35"/>
-      <c r="J42" s="53"/>
-      <c r="K42" s="12"/>
-      <c r="L42" s="12"/>
-      <c r="O42" s="15"/>
+      <c r="A42" s="32"/>
+      <c r="B42" s="14"/>
+      <c r="C42" s="14"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="14"/>
+      <c r="H42" s="14"/>
+      <c r="I42" s="37"/>
+      <c r="J42" s="55"/>
+      <c r="K42" s="14"/>
+      <c r="L42" s="14"/>
+      <c r="O42" s="17"/>
     </row>
     <row r="43">
-      <c r="A43" s="30"/>
-      <c r="B43" s="12"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="12"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="12"/>
-      <c r="G43" s="12"/>
-      <c r="H43" s="12"/>
-      <c r="I43" s="35"/>
-      <c r="J43" s="53"/>
-      <c r="K43" s="12"/>
-      <c r="L43" s="12"/>
-      <c r="O43" s="15"/>
+      <c r="A43" s="32"/>
+      <c r="B43" s="14"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
+      <c r="H43" s="14"/>
+      <c r="I43" s="37"/>
+      <c r="J43" s="55"/>
+      <c r="K43" s="14"/>
+      <c r="L43" s="14"/>
+      <c r="O43" s="17"/>
     </row>
     <row r="44">
-      <c r="A44" s="30"/>
-      <c r="B44" s="12"/>
-      <c r="C44" s="36"/>
-      <c r="D44" s="36"/>
-      <c r="E44" s="12"/>
-      <c r="F44" s="12"/>
-      <c r="G44" s="12"/>
-      <c r="H44" s="12"/>
-      <c r="I44" s="35"/>
-      <c r="J44" s="53"/>
-      <c r="K44" s="12"/>
-      <c r="L44" s="12"/>
-      <c r="O44" s="15"/>
+      <c r="A44" s="32"/>
+      <c r="B44" s="14"/>
+      <c r="C44" s="38"/>
+      <c r="D44" s="38"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="14"/>
+      <c r="H44" s="14"/>
+      <c r="I44" s="37"/>
+      <c r="J44" s="55"/>
+      <c r="K44" s="14"/>
+      <c r="L44" s="14"/>
+      <c r="O44" s="17"/>
     </row>
     <row r="45">
-      <c r="A45" s="67"/>
-      <c r="B45" s="93"/>
-      <c r="C45" s="75" t="s">
+      <c r="A45" s="69"/>
+      <c r="B45" s="95"/>
+      <c r="C45" s="77" t="s">
         <v>85</v>
       </c>
-      <c r="D45" s="94"/>
-      <c r="E45" s="95"/>
-      <c r="F45" s="68"/>
-      <c r="G45" s="60"/>
-      <c r="H45" s="60"/>
-      <c r="I45" s="61"/>
-      <c r="O45" s="15"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="97"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="62"/>
+      <c r="H45" s="62"/>
+      <c r="I45" s="63"/>
+      <c r="O45" s="17"/>
     </row>
     <row r="46">
-      <c r="A46" s="21"/>
-      <c r="B46" s="21"/>
-      <c r="C46" s="21"/>
-      <c r="D46" s="21"/>
-      <c r="E46" s="21"/>
-      <c r="F46" s="21"/>
-      <c r="O46" s="63"/>
+      <c r="A46" s="23"/>
+      <c r="B46" s="23"/>
+      <c r="C46" s="23"/>
+      <c r="D46" s="23"/>
+      <c r="E46" s="23"/>
+      <c r="F46" s="23"/>
+      <c r="O46" s="65"/>
     </row>
     <row r="47">
-      <c r="A47" s="12"/>
-      <c r="B47" s="12"/>
-      <c r="C47" s="12"/>
-      <c r="D47" s="12"/>
-      <c r="E47" s="12"/>
-      <c r="F47" s="12"/>
-      <c r="O47" s="63"/>
+      <c r="A47" s="14"/>
+      <c r="B47" s="14"/>
+      <c r="C47" s="14"/>
+      <c r="D47" s="14"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="14"/>
+      <c r="O47" s="65"/>
     </row>
     <row r="48">
-      <c r="O48" s="63"/>
+      <c r="O48" s="65"/>
     </row>
     <row r="49">
-      <c r="O49" s="63"/>
+      <c r="O49" s="65"/>
     </row>
     <row r="50">
-      <c r="O50" s="63"/>
+      <c r="O50" s="65"/>
     </row>
     <row r="51">
-      <c r="O51" s="63"/>
+      <c r="O51" s="65"/>
     </row>
     <row r="52">
-      <c r="O52" s="63"/>
+      <c r="O52" s="65"/>
     </row>
     <row r="53">
-      <c r="O53" s="63"/>
+      <c r="O53" s="65"/>
     </row>
     <row r="54">
-      <c r="A54" s="3"/>
-      <c r="O54" s="63"/>
+      <c r="A54" s="7"/>
+      <c r="O54" s="65"/>
     </row>
     <row r="55">
-      <c r="A55" s="3"/>
-      <c r="O55" s="63"/>
+      <c r="A55" s="7"/>
+      <c r="O55" s="65"/>
     </row>
     <row r="56">
-      <c r="O56" s="63"/>
+      <c r="O56" s="65"/>
     </row>
     <row r="57">
-      <c r="O57" s="63"/>
+      <c r="O57" s="65"/>
     </row>
     <row r="58">
-      <c r="O58" s="63"/>
+      <c r="O58" s="65"/>
     </row>
     <row r="59">
-      <c r="O59" s="63"/>
+      <c r="O59" s="65"/>
     </row>
     <row r="60">
-      <c r="O60" s="63"/>
+      <c r="O60" s="65"/>
     </row>
     <row r="61">
-      <c r="O61" s="63"/>
+      <c r="O61" s="65"/>
     </row>
     <row r="62">
-      <c r="O62" s="63"/>
+      <c r="O62" s="65"/>
     </row>
     <row r="63">
-      <c r="O63" s="63"/>
+      <c r="O63" s="65"/>
     </row>
     <row r="64">
-      <c r="O64" s="63"/>
+      <c r="O64" s="65"/>
     </row>
     <row r="65">
-      <c r="O65" s="63"/>
+      <c r="O65" s="65"/>
     </row>
     <row r="66">
-      <c r="O66" s="63"/>
+      <c r="O66" s="65"/>
     </row>
     <row r="67">
-      <c r="O67" s="63"/>
+      <c r="O67" s="65"/>
     </row>
     <row r="68">
-      <c r="O68" s="63"/>
+      <c r="O68" s="65"/>
     </row>
     <row r="69">
-      <c r="O69" s="63"/>
+      <c r="O69" s="65"/>
     </row>
     <row r="70">
-      <c r="O70" s="63"/>
+      <c r="O70" s="65"/>
     </row>
     <row r="71">
-      <c r="O71" s="63"/>
+      <c r="O71" s="65"/>
     </row>
     <row r="72">
-      <c r="O72" s="63"/>
+      <c r="O72" s="65"/>
     </row>
     <row r="73">
-      <c r="O73" s="63"/>
+      <c r="O73" s="65"/>
     </row>
     <row r="74">
-      <c r="O74" s="63"/>
+      <c r="O74" s="65"/>
     </row>
     <row r="75">
-      <c r="O75" s="63"/>
+      <c r="O75" s="65"/>
     </row>
     <row r="76">
-      <c r="O76" s="63"/>
+      <c r="O76" s="65"/>
     </row>
     <row r="77">
-      <c r="O77" s="63"/>
+      <c r="O77" s="65"/>
     </row>
     <row r="78">
-      <c r="O78" s="63"/>
+      <c r="O78" s="65"/>
     </row>
     <row r="79">
-      <c r="O79" s="63"/>
+      <c r="O79" s="65"/>
     </row>
     <row r="80">
-      <c r="O80" s="63"/>
+      <c r="O80" s="65"/>
     </row>
     <row r="81">
-      <c r="O81" s="63"/>
+      <c r="O81" s="65"/>
     </row>
     <row r="82">
-      <c r="O82" s="63"/>
+      <c r="O82" s="65"/>
     </row>
     <row r="83">
-      <c r="O83" s="63"/>
+      <c r="O83" s="65"/>
     </row>
     <row r="84">
-      <c r="O84" s="63"/>
+      <c r="O84" s="65"/>
     </row>
     <row r="85">
-      <c r="O85" s="63"/>
+      <c r="O85" s="65"/>
     </row>
     <row r="86">
-      <c r="O86" s="63"/>
+      <c r="O86" s="65"/>
     </row>
     <row r="87">
-      <c r="O87" s="63"/>
+      <c r="O87" s="65"/>
     </row>
     <row r="88">
-      <c r="O88" s="63"/>
+      <c r="O88" s="65"/>
     </row>
     <row r="89">
-      <c r="O89" s="63"/>
+      <c r="O89" s="65"/>
     </row>
     <row r="90">
-      <c r="O90" s="63"/>
+      <c r="O90" s="65"/>
     </row>
     <row r="91">
-      <c r="O91" s="63"/>
+      <c r="O91" s="65"/>
     </row>
     <row r="92">
-      <c r="O92" s="63"/>
+      <c r="O92" s="65"/>
     </row>
     <row r="93">
-      <c r="O93" s="63"/>
+      <c r="O93" s="65"/>
     </row>
     <row r="94">
-      <c r="O94" s="63"/>
+      <c r="O94" s="65"/>
     </row>
     <row r="95">
-      <c r="O95" s="63"/>
+      <c r="O95" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3676,1134 +3733,1158 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="F1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6">
+        <v>0.7467939814814815</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D2" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="8"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
+      <c r="E2" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="O2" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="P2" s="8">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
+      <c r="A3" s="6"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
     </row>
     <row r="4">
-      <c r="A4" s="8"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
     </row>
     <row r="5">
-      <c r="A5" s="8"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
+      <c r="A5" s="6"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
     </row>
     <row r="6">
-      <c r="A6" s="8"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
-      <c r="P6" s="9"/>
+      <c r="A6" s="6"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="8"/>
     </row>
     <row r="7">
-      <c r="A7" s="8"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
-      <c r="P7" s="9"/>
+      <c r="A7" s="6"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
     </row>
     <row r="8">
-      <c r="A8" s="8"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="9"/>
-      <c r="O8" s="9"/>
-      <c r="P8" s="9"/>
+      <c r="A8" s="6"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
     </row>
     <row r="9">
-      <c r="A9" s="8"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="9"/>
+      <c r="A9" s="6"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
     </row>
     <row r="10">
-      <c r="A10" s="8"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
-      <c r="P10" s="9"/>
+      <c r="A10" s="6"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
     </row>
     <row r="11">
-      <c r="A11" s="8"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
-      <c r="P11" s="9"/>
+      <c r="A11" s="6"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
     </row>
     <row r="12">
-      <c r="A12" s="8"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
-      <c r="P12" s="9"/>
+      <c r="A12" s="6"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
     </row>
     <row r="13">
-      <c r="A13" s="8"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
-      <c r="P13" s="9"/>
+      <c r="A13" s="6"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
     </row>
     <row r="14">
-      <c r="A14" s="8"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
-      <c r="P14" s="9"/>
+      <c r="A14" s="6"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8"/>
     </row>
     <row r="15">
-      <c r="A15" s="8"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="9"/>
-      <c r="O15" s="9"/>
-      <c r="P15" s="9"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="8"/>
+      <c r="O15" s="8"/>
+      <c r="P15" s="8"/>
     </row>
     <row r="16">
-      <c r="A16" s="8"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="9"/>
-      <c r="P16" s="9"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8"/>
     </row>
     <row r="17">
-      <c r="A17" s="8"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
-      <c r="P17" s="9"/>
+      <c r="A17" s="6"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8"/>
+      <c r="P17" s="8"/>
     </row>
     <row r="18">
-      <c r="A18" s="8"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="9"/>
-      <c r="P18" s="9"/>
+      <c r="A18" s="6"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="8"/>
+      <c r="O18" s="8"/>
+      <c r="P18" s="8"/>
     </row>
     <row r="19">
-      <c r="A19" s="8"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="9"/>
-      <c r="O19" s="9"/>
-      <c r="P19" s="9"/>
+      <c r="A19" s="6"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="8"/>
+      <c r="P19" s="8"/>
     </row>
     <row r="20">
-      <c r="A20" s="8"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9"/>
-      <c r="P20" s="9"/>
+      <c r="A20" s="6"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="8"/>
+      <c r="P20" s="8"/>
     </row>
     <row r="21">
-      <c r="A21" s="8"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="9"/>
-      <c r="O21" s="9"/>
-      <c r="P21" s="9"/>
+      <c r="A21" s="6"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="8"/>
     </row>
     <row r="22">
-      <c r="A22" s="8"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="9"/>
-      <c r="O22" s="9"/>
-      <c r="P22" s="9"/>
+      <c r="A22" s="6"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
+      <c r="M22" s="7"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
+      <c r="P22" s="8"/>
     </row>
     <row r="23">
-      <c r="A23" s="8"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
-      <c r="N23" s="9"/>
-      <c r="O23" s="9"/>
-      <c r="P23" s="9"/>
+      <c r="A23" s="6"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="7"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="8"/>
+      <c r="P23" s="8"/>
     </row>
     <row r="24">
-      <c r="A24" s="8"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
-      <c r="N24" s="9"/>
-      <c r="O24" s="9"/>
-      <c r="P24" s="9"/>
+      <c r="A24" s="6"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
+      <c r="M24" s="7"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="8"/>
     </row>
     <row r="25">
-      <c r="A25" s="8"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="9"/>
-      <c r="O25" s="9"/>
-      <c r="P25" s="9"/>
+      <c r="A25" s="6"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="7"/>
+      <c r="M25" s="7"/>
+      <c r="N25" s="8"/>
+      <c r="O25" s="8"/>
+      <c r="P25" s="8"/>
     </row>
     <row r="26">
-      <c r="A26" s="8"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
-      <c r="N26" s="9"/>
-      <c r="O26" s="9"/>
-      <c r="P26" s="9"/>
+      <c r="A26" s="6"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="7"/>
+      <c r="L26" s="7"/>
+      <c r="M26" s="7"/>
+      <c r="N26" s="8"/>
+      <c r="O26" s="8"/>
+      <c r="P26" s="8"/>
     </row>
     <row r="27">
-      <c r="A27" s="8"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="9"/>
-      <c r="O27" s="9"/>
-      <c r="P27" s="9"/>
+      <c r="A27" s="6"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="7"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="7"/>
+      <c r="M27" s="7"/>
+      <c r="N27" s="8"/>
+      <c r="O27" s="8"/>
+      <c r="P27" s="8"/>
     </row>
     <row r="28">
-      <c r="A28" s="8"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
-      <c r="N28" s="9"/>
-      <c r="O28" s="9"/>
-      <c r="P28" s="9"/>
+      <c r="A28" s="6"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="7"/>
+      <c r="L28" s="7"/>
+      <c r="M28" s="7"/>
+      <c r="N28" s="8"/>
+      <c r="O28" s="8"/>
+      <c r="P28" s="8"/>
     </row>
     <row r="29">
-      <c r="A29" s="8"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3"/>
-      <c r="M29" s="3"/>
-      <c r="N29" s="9"/>
-      <c r="O29" s="9"/>
-      <c r="P29" s="9"/>
+      <c r="A29" s="6"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="7"/>
+      <c r="M29" s="7"/>
+      <c r="N29" s="8"/>
+      <c r="O29" s="8"/>
+      <c r="P29" s="8"/>
     </row>
     <row r="30">
-      <c r="A30" s="8"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
-      <c r="J30" s="3"/>
-      <c r="K30" s="3"/>
-      <c r="L30" s="3"/>
-      <c r="M30" s="3"/>
-      <c r="N30" s="9"/>
-      <c r="O30" s="9"/>
-      <c r="P30" s="9"/>
+      <c r="A30" s="6"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="7"/>
+      <c r="J30" s="7"/>
+      <c r="K30" s="7"/>
+      <c r="L30" s="7"/>
+      <c r="M30" s="7"/>
+      <c r="N30" s="8"/>
+      <c r="O30" s="8"/>
+      <c r="P30" s="8"/>
     </row>
     <row r="31">
-      <c r="A31" s="8"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-      <c r="N31" s="9"/>
-      <c r="O31" s="9"/>
-      <c r="P31" s="9"/>
+      <c r="A31" s="6"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7"/>
+      <c r="N31" s="8"/>
+      <c r="O31" s="8"/>
+      <c r="P31" s="8"/>
     </row>
     <row r="32">
-      <c r="A32" s="8"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
-      <c r="N32" s="9"/>
-      <c r="O32" s="9"/>
-      <c r="P32" s="9"/>
+      <c r="A32" s="6"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="F32" s="7"/>
+      <c r="H32" s="7"/>
+      <c r="I32" s="7"/>
+      <c r="N32" s="8"/>
+      <c r="O32" s="8"/>
+      <c r="P32" s="8"/>
     </row>
     <row r="33">
-      <c r="A33" s="8"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
-      <c r="N33" s="9"/>
-      <c r="O33" s="9"/>
-      <c r="P33" s="9"/>
+      <c r="A33" s="6"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="7"/>
+      <c r="N33" s="8"/>
+      <c r="O33" s="8"/>
+      <c r="P33" s="8"/>
     </row>
     <row r="34">
-      <c r="A34" s="8"/>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
-      <c r="N34" s="9"/>
-      <c r="O34" s="9"/>
-      <c r="P34" s="9"/>
+      <c r="A34" s="6"/>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="F34" s="7"/>
+      <c r="H34" s="7"/>
+      <c r="I34" s="7"/>
+      <c r="N34" s="8"/>
+      <c r="O34" s="8"/>
+      <c r="P34" s="8"/>
     </row>
     <row r="35">
-      <c r="A35" s="8"/>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
-      <c r="N35" s="9"/>
-      <c r="O35" s="9"/>
-      <c r="P35" s="9"/>
+      <c r="A35" s="6"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="F35" s="7"/>
+      <c r="H35" s="7"/>
+      <c r="I35" s="7"/>
+      <c r="N35" s="8"/>
+      <c r="O35" s="8"/>
+      <c r="P35" s="8"/>
     </row>
     <row r="36">
-      <c r="A36" s="8"/>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
-      <c r="N36" s="9"/>
-      <c r="O36" s="9"/>
-      <c r="P36" s="9"/>
+      <c r="A36" s="6"/>
+      <c r="B36" s="7"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="H36" s="7"/>
+      <c r="I36" s="7"/>
+      <c r="N36" s="8"/>
+      <c r="O36" s="8"/>
+      <c r="P36" s="8"/>
     </row>
     <row r="37">
-      <c r="A37" s="8"/>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
-      <c r="F37" s="3"/>
-      <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
-      <c r="N37" s="9"/>
-      <c r="O37" s="9"/>
-      <c r="P37" s="9"/>
+      <c r="A37" s="6"/>
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="H37" s="7"/>
+      <c r="I37" s="7"/>
+      <c r="N37" s="8"/>
+      <c r="O37" s="8"/>
+      <c r="P37" s="8"/>
     </row>
     <row r="38">
-      <c r="A38" s="8"/>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
-      <c r="F38" s="3"/>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
-      <c r="N38" s="9"/>
-      <c r="O38" s="9"/>
-      <c r="P38" s="9"/>
+      <c r="A38" s="6"/>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="H38" s="7"/>
+      <c r="I38" s="7"/>
+      <c r="N38" s="8"/>
+      <c r="O38" s="8"/>
+      <c r="P38" s="8"/>
     </row>
     <row r="39">
-      <c r="A39" s="8"/>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
-      <c r="N39" s="9"/>
-      <c r="O39" s="9"/>
-      <c r="P39" s="9"/>
+      <c r="A39" s="6"/>
+      <c r="B39" s="7"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="H39" s="7"/>
+      <c r="I39" s="7"/>
+      <c r="N39" s="8"/>
+      <c r="O39" s="8"/>
+      <c r="P39" s="8"/>
     </row>
     <row r="40">
-      <c r="A40" s="8"/>
-      <c r="B40" s="3"/>
-      <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
-      <c r="F40" s="3"/>
-      <c r="H40" s="3"/>
-      <c r="I40" s="3"/>
-      <c r="N40" s="9"/>
-      <c r="O40" s="9"/>
-      <c r="P40" s="9"/>
+      <c r="A40" s="6"/>
+      <c r="B40" s="7"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="F40" s="7"/>
+      <c r="H40" s="7"/>
+      <c r="I40" s="7"/>
+      <c r="N40" s="8"/>
+      <c r="O40" s="8"/>
+      <c r="P40" s="8"/>
     </row>
     <row r="41">
-      <c r="A41" s="8"/>
-      <c r="B41" s="3"/>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
-      <c r="F41" s="3"/>
-      <c r="H41" s="3"/>
-      <c r="I41" s="3"/>
-      <c r="N41" s="9"/>
-      <c r="O41" s="9"/>
-      <c r="P41" s="9"/>
+      <c r="A41" s="6"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
+      <c r="D41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="H41" s="7"/>
+      <c r="I41" s="7"/>
+      <c r="N41" s="8"/>
+      <c r="O41" s="8"/>
+      <c r="P41" s="8"/>
     </row>
     <row r="42">
-      <c r="A42" s="8"/>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
-      <c r="N42" s="9"/>
-      <c r="O42" s="9"/>
-      <c r="P42" s="9"/>
+      <c r="A42" s="6"/>
+      <c r="B42" s="7"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+      <c r="F42" s="7"/>
+      <c r="H42" s="7"/>
+      <c r="I42" s="7"/>
+      <c r="N42" s="8"/>
+      <c r="O42" s="8"/>
+      <c r="P42" s="8"/>
     </row>
     <row r="43">
-      <c r="A43" s="8"/>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
-      <c r="F43" s="3"/>
-      <c r="H43" s="3"/>
-      <c r="I43" s="3"/>
-      <c r="N43" s="9"/>
-      <c r="O43" s="9"/>
-      <c r="P43" s="9"/>
+      <c r="A43" s="6"/>
+      <c r="B43" s="7"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="7"/>
+      <c r="F43" s="7"/>
+      <c r="H43" s="7"/>
+      <c r="I43" s="7"/>
+      <c r="N43" s="8"/>
+      <c r="O43" s="8"/>
+      <c r="P43" s="8"/>
     </row>
     <row r="44">
-      <c r="A44" s="8"/>
-      <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
-      <c r="F44" s="3"/>
-      <c r="H44" s="3"/>
-      <c r="I44" s="3"/>
-      <c r="N44" s="9"/>
-      <c r="O44" s="9"/>
-      <c r="P44" s="9"/>
+      <c r="A44" s="6"/>
+      <c r="B44" s="7"/>
+      <c r="C44" s="7"/>
+      <c r="D44" s="7"/>
+      <c r="F44" s="7"/>
+      <c r="H44" s="7"/>
+      <c r="I44" s="7"/>
+      <c r="N44" s="8"/>
+      <c r="O44" s="8"/>
+      <c r="P44" s="8"/>
     </row>
     <row r="45">
-      <c r="A45" s="8"/>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-      <c r="F45" s="3"/>
-      <c r="H45" s="3"/>
-      <c r="I45" s="3"/>
-      <c r="N45" s="9"/>
-      <c r="O45" s="9"/>
-      <c r="P45" s="9"/>
+      <c r="A45" s="6"/>
+      <c r="B45" s="7"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="F45" s="7"/>
+      <c r="H45" s="7"/>
+      <c r="I45" s="7"/>
+      <c r="N45" s="8"/>
+      <c r="O45" s="8"/>
+      <c r="P45" s="8"/>
     </row>
     <row r="46">
-      <c r="A46" s="8"/>
-      <c r="B46" s="3"/>
-      <c r="C46" s="3"/>
-      <c r="D46" s="3"/>
-      <c r="F46" s="3"/>
-      <c r="H46" s="3"/>
-      <c r="I46" s="3"/>
-      <c r="N46" s="9"/>
-      <c r="O46" s="9"/>
-      <c r="P46" s="9"/>
+      <c r="A46" s="6"/>
+      <c r="B46" s="7"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="7"/>
+      <c r="F46" s="7"/>
+      <c r="H46" s="7"/>
+      <c r="I46" s="7"/>
+      <c r="N46" s="8"/>
+      <c r="O46" s="8"/>
+      <c r="P46" s="8"/>
     </row>
     <row r="47">
-      <c r="A47" s="8"/>
-      <c r="B47" s="3"/>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
-      <c r="F47" s="3"/>
-      <c r="H47" s="3"/>
-      <c r="I47" s="3"/>
-      <c r="N47" s="9"/>
-      <c r="O47" s="9"/>
-      <c r="P47" s="9"/>
+      <c r="A47" s="6"/>
+      <c r="B47" s="7"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7"/>
+      <c r="F47" s="7"/>
+      <c r="H47" s="7"/>
+      <c r="I47" s="7"/>
+      <c r="N47" s="8"/>
+      <c r="O47" s="8"/>
+      <c r="P47" s="8"/>
     </row>
     <row r="48">
-      <c r="A48" s="8"/>
-      <c r="B48" s="3"/>
-      <c r="C48" s="3"/>
-      <c r="D48" s="3"/>
-      <c r="F48" s="3"/>
-      <c r="H48" s="3"/>
-      <c r="I48" s="3"/>
-      <c r="N48" s="9"/>
-      <c r="O48" s="9"/>
-      <c r="P48" s="9"/>
+      <c r="A48" s="6"/>
+      <c r="B48" s="7"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
+      <c r="F48" s="7"/>
+      <c r="H48" s="7"/>
+      <c r="I48" s="7"/>
+      <c r="N48" s="8"/>
+      <c r="O48" s="8"/>
+      <c r="P48" s="8"/>
     </row>
     <row r="49">
-      <c r="A49" s="8"/>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-      <c r="F49" s="3"/>
-      <c r="H49" s="3"/>
-      <c r="I49" s="3"/>
-      <c r="N49" s="9"/>
-      <c r="O49" s="9"/>
-      <c r="P49" s="9"/>
+      <c r="A49" s="6"/>
+      <c r="B49" s="7"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="7"/>
+      <c r="F49" s="7"/>
+      <c r="H49" s="7"/>
+      <c r="I49" s="7"/>
+      <c r="N49" s="8"/>
+      <c r="O49" s="8"/>
+      <c r="P49" s="8"/>
     </row>
     <row r="50">
-      <c r="A50" s="8"/>
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
-      <c r="F50" s="3"/>
-      <c r="H50" s="3"/>
-      <c r="I50" s="3"/>
-      <c r="N50" s="9"/>
-      <c r="O50" s="9"/>
-      <c r="P50" s="9"/>
+      <c r="A50" s="6"/>
+      <c r="B50" s="7"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="7"/>
+      <c r="F50" s="7"/>
+      <c r="H50" s="7"/>
+      <c r="I50" s="7"/>
+      <c r="N50" s="8"/>
+      <c r="O50" s="8"/>
+      <c r="P50" s="8"/>
     </row>
     <row r="51">
-      <c r="A51" s="8"/>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
-      <c r="F51" s="3"/>
-      <c r="H51" s="3"/>
-      <c r="I51" s="3"/>
-      <c r="N51" s="9"/>
-      <c r="O51" s="9"/>
-      <c r="P51" s="9"/>
+      <c r="A51" s="6"/>
+      <c r="B51" s="7"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
+      <c r="F51" s="7"/>
+      <c r="H51" s="7"/>
+      <c r="I51" s="7"/>
+      <c r="N51" s="8"/>
+      <c r="O51" s="8"/>
+      <c r="P51" s="8"/>
     </row>
     <row r="52">
-      <c r="A52" s="8"/>
-      <c r="B52" s="3"/>
-      <c r="C52" s="3"/>
-      <c r="D52" s="3"/>
-      <c r="F52" s="3"/>
-      <c r="H52" s="3"/>
-      <c r="I52" s="3"/>
-      <c r="N52" s="9"/>
-      <c r="O52" s="9"/>
-      <c r="P52" s="9"/>
+      <c r="A52" s="6"/>
+      <c r="B52" s="7"/>
+      <c r="C52" s="7"/>
+      <c r="D52" s="7"/>
+      <c r="F52" s="7"/>
+      <c r="H52" s="7"/>
+      <c r="I52" s="7"/>
+      <c r="N52" s="8"/>
+      <c r="O52" s="8"/>
+      <c r="P52" s="8"/>
     </row>
     <row r="53">
-      <c r="A53" s="8"/>
-      <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
-      <c r="F53" s="3"/>
-      <c r="H53" s="3"/>
-      <c r="I53" s="3"/>
-      <c r="N53" s="9"/>
-      <c r="O53" s="9"/>
-      <c r="P53" s="9"/>
+      <c r="A53" s="6"/>
+      <c r="B53" s="7"/>
+      <c r="C53" s="7"/>
+      <c r="D53" s="7"/>
+      <c r="F53" s="7"/>
+      <c r="H53" s="7"/>
+      <c r="I53" s="7"/>
+      <c r="N53" s="8"/>
+      <c r="O53" s="8"/>
+      <c r="P53" s="8"/>
     </row>
     <row r="54">
-      <c r="A54" s="8"/>
-      <c r="B54" s="3"/>
-      <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
-      <c r="F54" s="3"/>
-      <c r="H54" s="3"/>
-      <c r="I54" s="3"/>
-      <c r="N54" s="9"/>
-      <c r="O54" s="9"/>
-      <c r="P54" s="9"/>
+      <c r="A54" s="6"/>
+      <c r="B54" s="7"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="7"/>
+      <c r="F54" s="7"/>
+      <c r="H54" s="7"/>
+      <c r="I54" s="7"/>
+      <c r="N54" s="8"/>
+      <c r="O54" s="8"/>
+      <c r="P54" s="8"/>
     </row>
     <row r="55">
-      <c r="A55" s="8"/>
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
-      <c r="F55" s="3"/>
-      <c r="H55" s="3"/>
-      <c r="I55" s="3"/>
-      <c r="N55" s="9"/>
-      <c r="O55" s="9"/>
-      <c r="P55" s="9"/>
+      <c r="A55" s="6"/>
+      <c r="B55" s="7"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+      <c r="F55" s="7"/>
+      <c r="H55" s="7"/>
+      <c r="I55" s="7"/>
+      <c r="N55" s="8"/>
+      <c r="O55" s="8"/>
+      <c r="P55" s="8"/>
     </row>
     <row r="56">
-      <c r="A56" s="8"/>
-      <c r="B56" s="3"/>
-      <c r="C56" s="3"/>
-      <c r="D56" s="3"/>
-      <c r="E56" s="3"/>
-      <c r="F56" s="3"/>
-      <c r="H56" s="3"/>
-      <c r="I56" s="3"/>
-      <c r="N56" s="9"/>
-      <c r="O56" s="9"/>
-      <c r="P56" s="9"/>
+      <c r="A56" s="6"/>
+      <c r="B56" s="7"/>
+      <c r="C56" s="7"/>
+      <c r="D56" s="7"/>
+      <c r="E56" s="7"/>
+      <c r="F56" s="7"/>
+      <c r="H56" s="7"/>
+      <c r="I56" s="7"/>
+      <c r="N56" s="8"/>
+      <c r="O56" s="8"/>
+      <c r="P56" s="8"/>
     </row>
     <row r="57">
-      <c r="A57" s="8"/>
-      <c r="B57" s="3"/>
-      <c r="C57" s="3"/>
-      <c r="D57" s="3"/>
-      <c r="E57" s="3"/>
-      <c r="F57" s="3"/>
-      <c r="H57" s="3"/>
-      <c r="I57" s="3"/>
-      <c r="N57" s="9"/>
-      <c r="O57" s="9"/>
-      <c r="P57" s="9"/>
+      <c r="A57" s="6"/>
+      <c r="B57" s="7"/>
+      <c r="C57" s="7"/>
+      <c r="D57" s="7"/>
+      <c r="E57" s="7"/>
+      <c r="F57" s="7"/>
+      <c r="H57" s="7"/>
+      <c r="I57" s="7"/>
+      <c r="N57" s="8"/>
+      <c r="O57" s="8"/>
+      <c r="P57" s="8"/>
     </row>
     <row r="58">
-      <c r="A58" s="8"/>
-      <c r="B58" s="3"/>
-      <c r="C58" s="3"/>
-      <c r="D58" s="3"/>
-      <c r="E58" s="3"/>
-      <c r="F58" s="3"/>
-      <c r="H58" s="3"/>
-      <c r="I58" s="3"/>
-      <c r="N58" s="9"/>
-      <c r="O58" s="9"/>
-      <c r="P58" s="9"/>
+      <c r="A58" s="6"/>
+      <c r="B58" s="7"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="7"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="7"/>
+      <c r="H58" s="7"/>
+      <c r="I58" s="7"/>
+      <c r="N58" s="8"/>
+      <c r="O58" s="8"/>
+      <c r="P58" s="8"/>
     </row>
     <row r="59">
-      <c r="A59" s="8"/>
-      <c r="B59" s="3"/>
-      <c r="C59" s="3"/>
-      <c r="D59" s="3"/>
-      <c r="E59" s="3"/>
-      <c r="F59" s="3"/>
-      <c r="H59" s="3"/>
-      <c r="I59" s="3"/>
-      <c r="N59" s="9"/>
-      <c r="O59" s="9"/>
-      <c r="P59" s="9"/>
+      <c r="A59" s="6"/>
+      <c r="B59" s="7"/>
+      <c r="C59" s="7"/>
+      <c r="D59" s="7"/>
+      <c r="E59" s="7"/>
+      <c r="F59" s="7"/>
+      <c r="H59" s="7"/>
+      <c r="I59" s="7"/>
+      <c r="N59" s="8"/>
+      <c r="O59" s="8"/>
+      <c r="P59" s="8"/>
     </row>
     <row r="60">
-      <c r="A60" s="8"/>
-      <c r="B60" s="3"/>
-      <c r="C60" s="3"/>
-      <c r="D60" s="3"/>
-      <c r="E60" s="3"/>
-      <c r="F60" s="3"/>
-      <c r="H60" s="3"/>
-      <c r="I60" s="3"/>
-      <c r="N60" s="9"/>
-      <c r="O60" s="9"/>
-      <c r="P60" s="9"/>
+      <c r="A60" s="6"/>
+      <c r="B60" s="7"/>
+      <c r="C60" s="7"/>
+      <c r="D60" s="7"/>
+      <c r="E60" s="7"/>
+      <c r="F60" s="7"/>
+      <c r="H60" s="7"/>
+      <c r="I60" s="7"/>
+      <c r="N60" s="8"/>
+      <c r="O60" s="8"/>
+      <c r="P60" s="8"/>
     </row>
     <row r="61">
-      <c r="A61" s="8"/>
-      <c r="B61" s="3"/>
-      <c r="C61" s="3"/>
-      <c r="D61" s="3"/>
-      <c r="E61" s="3"/>
-      <c r="F61" s="3"/>
-      <c r="H61" s="3"/>
-      <c r="I61" s="3"/>
-      <c r="N61" s="9"/>
-      <c r="O61" s="9"/>
-      <c r="P61" s="9"/>
+      <c r="A61" s="6"/>
+      <c r="B61" s="7"/>
+      <c r="C61" s="7"/>
+      <c r="D61" s="7"/>
+      <c r="E61" s="7"/>
+      <c r="F61" s="7"/>
+      <c r="H61" s="7"/>
+      <c r="I61" s="7"/>
+      <c r="N61" s="8"/>
+      <c r="O61" s="8"/>
+      <c r="P61" s="8"/>
     </row>
     <row r="62">
-      <c r="A62" s="8"/>
-      <c r="B62" s="3"/>
-      <c r="C62" s="3"/>
-      <c r="D62" s="3"/>
-      <c r="E62" s="3"/>
-      <c r="F62" s="3"/>
-      <c r="H62" s="3"/>
-      <c r="I62" s="3"/>
-      <c r="N62" s="9"/>
-      <c r="O62" s="9"/>
-      <c r="P62" s="9"/>
+      <c r="A62" s="6"/>
+      <c r="B62" s="7"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="7"/>
+      <c r="E62" s="7"/>
+      <c r="F62" s="7"/>
+      <c r="H62" s="7"/>
+      <c r="I62" s="7"/>
+      <c r="N62" s="8"/>
+      <c r="O62" s="8"/>
+      <c r="P62" s="8"/>
     </row>
     <row r="63">
-      <c r="A63" s="8"/>
-      <c r="B63" s="3"/>
-      <c r="C63" s="3"/>
-      <c r="D63" s="3"/>
-      <c r="E63" s="3"/>
-      <c r="F63" s="3"/>
-      <c r="H63" s="3"/>
-      <c r="I63" s="3"/>
-      <c r="N63" s="9"/>
-      <c r="O63" s="9"/>
-      <c r="P63" s="9"/>
+      <c r="A63" s="6"/>
+      <c r="B63" s="7"/>
+      <c r="C63" s="7"/>
+      <c r="D63" s="7"/>
+      <c r="E63" s="7"/>
+      <c r="F63" s="7"/>
+      <c r="H63" s="7"/>
+      <c r="I63" s="7"/>
+      <c r="N63" s="8"/>
+      <c r="O63" s="8"/>
+      <c r="P63" s="8"/>
     </row>
     <row r="64">
-      <c r="A64" s="8"/>
-      <c r="B64" s="3"/>
-      <c r="C64" s="3"/>
-      <c r="D64" s="3"/>
-      <c r="E64" s="3"/>
-      <c r="F64" s="3"/>
-      <c r="G64" s="3"/>
-      <c r="H64" s="3"/>
-      <c r="I64" s="3"/>
-      <c r="N64" s="9"/>
-      <c r="O64" s="9"/>
-      <c r="P64" s="9"/>
+      <c r="A64" s="6"/>
+      <c r="B64" s="7"/>
+      <c r="C64" s="7"/>
+      <c r="D64" s="7"/>
+      <c r="E64" s="7"/>
+      <c r="F64" s="7"/>
+      <c r="G64" s="7"/>
+      <c r="H64" s="7"/>
+      <c r="I64" s="7"/>
+      <c r="N64" s="8"/>
+      <c r="O64" s="8"/>
+      <c r="P64" s="8"/>
     </row>
     <row r="65">
-      <c r="A65" s="8"/>
-      <c r="B65" s="3"/>
-      <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
-      <c r="E65" s="3"/>
-      <c r="F65" s="3"/>
-      <c r="G65" s="3"/>
-      <c r="H65" s="3"/>
-      <c r="I65" s="3"/>
-      <c r="N65" s="9"/>
-      <c r="O65" s="9"/>
-      <c r="P65" s="9"/>
+      <c r="A65" s="6"/>
+      <c r="B65" s="7"/>
+      <c r="C65" s="7"/>
+      <c r="D65" s="7"/>
+      <c r="E65" s="7"/>
+      <c r="F65" s="7"/>
+      <c r="G65" s="7"/>
+      <c r="H65" s="7"/>
+      <c r="I65" s="7"/>
+      <c r="N65" s="8"/>
+      <c r="O65" s="8"/>
+      <c r="P65" s="8"/>
     </row>
     <row r="66">
-      <c r="A66" s="8"/>
-      <c r="B66" s="3"/>
-      <c r="C66" s="3"/>
-      <c r="D66" s="3"/>
-      <c r="E66" s="3"/>
-      <c r="F66" s="3"/>
-      <c r="G66" s="3"/>
-      <c r="H66" s="3"/>
-      <c r="I66" s="3"/>
-      <c r="N66" s="9"/>
-      <c r="O66" s="9"/>
-      <c r="P66" s="9"/>
+      <c r="A66" s="6"/>
+      <c r="B66" s="7"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="7"/>
+      <c r="E66" s="7"/>
+      <c r="F66" s="7"/>
+      <c r="G66" s="7"/>
+      <c r="H66" s="7"/>
+      <c r="I66" s="7"/>
+      <c r="N66" s="8"/>
+      <c r="O66" s="8"/>
+      <c r="P66" s="8"/>
     </row>
     <row r="67">
-      <c r="A67" s="8"/>
-      <c r="B67" s="3"/>
-      <c r="C67" s="3"/>
-      <c r="D67" s="3"/>
-      <c r="E67" s="3"/>
-      <c r="F67" s="3"/>
-      <c r="G67" s="3"/>
-      <c r="H67" s="3"/>
-      <c r="I67" s="3"/>
-      <c r="J67" s="3"/>
-      <c r="K67" s="3"/>
-      <c r="L67" s="3"/>
-      <c r="N67" s="9"/>
-      <c r="O67" s="9"/>
-      <c r="P67" s="9"/>
+      <c r="A67" s="6"/>
+      <c r="B67" s="7"/>
+      <c r="C67" s="7"/>
+      <c r="D67" s="7"/>
+      <c r="E67" s="7"/>
+      <c r="F67" s="7"/>
+      <c r="G67" s="7"/>
+      <c r="H67" s="7"/>
+      <c r="I67" s="7"/>
+      <c r="J67" s="7"/>
+      <c r="K67" s="7"/>
+      <c r="L67" s="7"/>
+      <c r="N67" s="8"/>
+      <c r="O67" s="8"/>
+      <c r="P67" s="8"/>
     </row>
     <row r="68">
-      <c r="A68" s="8"/>
-      <c r="B68" s="3"/>
-      <c r="C68" s="3"/>
-      <c r="D68" s="3"/>
-      <c r="E68" s="3"/>
-      <c r="F68" s="3"/>
-      <c r="G68" s="3"/>
-      <c r="H68" s="3"/>
-      <c r="I68" s="3"/>
-      <c r="J68" s="3"/>
-      <c r="K68" s="3"/>
-      <c r="L68" s="3"/>
-      <c r="N68" s="9"/>
-      <c r="O68" s="9"/>
-      <c r="P68" s="9"/>
+      <c r="A68" s="6"/>
+      <c r="B68" s="7"/>
+      <c r="C68" s="7"/>
+      <c r="D68" s="7"/>
+      <c r="E68" s="7"/>
+      <c r="F68" s="7"/>
+      <c r="G68" s="7"/>
+      <c r="H68" s="7"/>
+      <c r="I68" s="7"/>
+      <c r="J68" s="7"/>
+      <c r="K68" s="7"/>
+      <c r="L68" s="7"/>
+      <c r="N68" s="8"/>
+      <c r="O68" s="8"/>
+      <c r="P68" s="8"/>
     </row>
     <row r="69">
-      <c r="A69" s="8"/>
-      <c r="B69" s="3"/>
-      <c r="C69" s="3"/>
-      <c r="D69" s="3"/>
-      <c r="E69" s="3"/>
-      <c r="F69" s="3"/>
-      <c r="G69" s="3"/>
-      <c r="H69" s="3"/>
-      <c r="I69" s="3"/>
-      <c r="J69" s="3"/>
-      <c r="K69" s="3"/>
-      <c r="L69" s="3"/>
-      <c r="M69" s="3"/>
-      <c r="N69" s="9"/>
-      <c r="O69" s="9"/>
-      <c r="P69" s="9"/>
+      <c r="A69" s="6"/>
+      <c r="B69" s="7"/>
+      <c r="C69" s="7"/>
+      <c r="D69" s="7"/>
+      <c r="E69" s="7"/>
+      <c r="F69" s="7"/>
+      <c r="G69" s="7"/>
+      <c r="H69" s="7"/>
+      <c r="I69" s="7"/>
+      <c r="J69" s="7"/>
+      <c r="K69" s="7"/>
+      <c r="L69" s="7"/>
+      <c r="M69" s="7"/>
+      <c r="N69" s="8"/>
+      <c r="O69" s="8"/>
+      <c r="P69" s="8"/>
     </row>
     <row r="70">
-      <c r="A70" s="8"/>
-      <c r="B70" s="3"/>
-      <c r="C70" s="3"/>
-      <c r="D70" s="3"/>
-      <c r="E70" s="3"/>
-      <c r="F70" s="3"/>
-      <c r="G70" s="3"/>
-      <c r="H70" s="3"/>
-      <c r="I70" s="3"/>
-      <c r="N70" s="9"/>
-      <c r="O70" s="9"/>
-      <c r="P70" s="9"/>
+      <c r="A70" s="6"/>
+      <c r="B70" s="7"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="7"/>
+      <c r="E70" s="7"/>
+      <c r="F70" s="7"/>
+      <c r="G70" s="7"/>
+      <c r="H70" s="7"/>
+      <c r="I70" s="7"/>
+      <c r="N70" s="8"/>
+      <c r="O70" s="8"/>
+      <c r="P70" s="8"/>
     </row>
     <row r="71">
-      <c r="A71" s="8"/>
-      <c r="B71" s="3"/>
-      <c r="C71" s="3"/>
-      <c r="D71" s="3"/>
-      <c r="E71" s="3"/>
-      <c r="F71" s="3"/>
-      <c r="H71" s="3"/>
-      <c r="I71" s="3"/>
-      <c r="N71" s="9"/>
-      <c r="O71" s="9"/>
-      <c r="P71" s="9"/>
+      <c r="A71" s="6"/>
+      <c r="B71" s="7"/>
+      <c r="C71" s="7"/>
+      <c r="D71" s="7"/>
+      <c r="E71" s="7"/>
+      <c r="F71" s="7"/>
+      <c r="H71" s="7"/>
+      <c r="I71" s="7"/>
+      <c r="N71" s="8"/>
+      <c r="O71" s="8"/>
+      <c r="P71" s="8"/>
     </row>
     <row r="72">
-      <c r="A72" s="8"/>
-      <c r="B72" s="3"/>
-      <c r="C72" s="3"/>
-      <c r="D72" s="3"/>
-      <c r="E72" s="3"/>
-      <c r="F72" s="3"/>
-      <c r="H72" s="3"/>
-      <c r="I72" s="3"/>
-      <c r="N72" s="9"/>
-      <c r="O72" s="9"/>
-      <c r="P72" s="9"/>
+      <c r="A72" s="6"/>
+      <c r="B72" s="7"/>
+      <c r="C72" s="7"/>
+      <c r="D72" s="7"/>
+      <c r="E72" s="7"/>
+      <c r="F72" s="7"/>
+      <c r="H72" s="7"/>
+      <c r="I72" s="7"/>
+      <c r="N72" s="8"/>
+      <c r="O72" s="8"/>
+      <c r="P72" s="8"/>
     </row>
     <row r="73">
-      <c r="A73" s="8"/>
-      <c r="B73" s="3"/>
-      <c r="C73" s="3"/>
-      <c r="D73" s="3"/>
-      <c r="F73" s="3"/>
-      <c r="H73" s="3"/>
-      <c r="I73" s="3"/>
-      <c r="N73" s="9"/>
-      <c r="O73" s="9"/>
-      <c r="P73" s="9"/>
+      <c r="A73" s="6"/>
+      <c r="B73" s="7"/>
+      <c r="C73" s="7"/>
+      <c r="D73" s="7"/>
+      <c r="F73" s="7"/>
+      <c r="H73" s="7"/>
+      <c r="I73" s="7"/>
+      <c r="N73" s="8"/>
+      <c r="O73" s="8"/>
+      <c r="P73" s="8"/>
     </row>
     <row r="74">
-      <c r="A74" s="8"/>
-      <c r="B74" s="3"/>
-      <c r="C74" s="3"/>
-      <c r="D74" s="3"/>
-      <c r="F74" s="3"/>
-      <c r="H74" s="3"/>
-      <c r="I74" s="3"/>
-      <c r="N74" s="9"/>
-      <c r="O74" s="9"/>
-      <c r="P74" s="9"/>
+      <c r="A74" s="6"/>
+      <c r="B74" s="7"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="7"/>
+      <c r="F74" s="7"/>
+      <c r="H74" s="7"/>
+      <c r="I74" s="7"/>
+      <c r="N74" s="8"/>
+      <c r="O74" s="8"/>
+      <c r="P74" s="8"/>
     </row>
     <row r="75">
-      <c r="A75" s="8"/>
-      <c r="B75" s="3"/>
-      <c r="C75" s="3"/>
-      <c r="D75" s="3"/>
-      <c r="F75" s="3"/>
-      <c r="H75" s="3"/>
-      <c r="I75" s="3"/>
-      <c r="N75" s="9"/>
-      <c r="O75" s="9"/>
-      <c r="P75" s="9"/>
+      <c r="A75" s="6"/>
+      <c r="B75" s="7"/>
+      <c r="C75" s="7"/>
+      <c r="D75" s="7"/>
+      <c r="F75" s="7"/>
+      <c r="H75" s="7"/>
+      <c r="I75" s="7"/>
+      <c r="N75" s="8"/>
+      <c r="O75" s="8"/>
+      <c r="P75" s="8"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/Ciclodeinstruccion (2).xlsx
+++ b/Ciclodeinstruccion (2).xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="135">
   <si>
     <t>Intrucciones</t>
   </si>
@@ -28,6 +28,9 @@
     <t>Acción Realizada</t>
   </si>
   <si>
+    <t>LD AX, 0EH</t>
+  </si>
+  <si>
     <t>PC</t>
   </si>
   <si>
@@ -37,18 +40,21 @@
     <t>MAR</t>
   </si>
   <si>
+    <t>LD BX, 0FH</t>
+  </si>
+  <si>
+    <t>MDR</t>
+  </si>
+  <si>
+    <t>AX</t>
+  </si>
+  <si>
+    <t>BX</t>
+  </si>
+  <si>
     <t>MOV AX, 00H</t>
   </si>
   <si>
-    <t>MDR</t>
-  </si>
-  <si>
-    <t>AX</t>
-  </si>
-  <si>
-    <t>BX</t>
-  </si>
-  <si>
     <t>ALU Operando 1</t>
   </si>
   <si>
@@ -67,81 +73,207 @@
     <t>CF (Carry)</t>
   </si>
   <si>
+    <t>SF (Sign)</t>
+  </si>
+  <si>
+    <t>MOV AX, 03H</t>
+  </si>
+  <si>
+    <t>MOV AX, 0AH</t>
+  </si>
+  <si>
+    <t>ADD AX, BX</t>
+  </si>
+  <si>
     <t>MOV BX, 04H</t>
   </si>
   <si>
-    <t>SF (Sign)</t>
+    <t>INC AX</t>
   </si>
   <si>
     <t>READY</t>
   </si>
   <si>
-    <t>Programa cargado desde la hoja 'Programas'.</t>
+    <t>MOV BX, 08H</t>
+  </si>
+  <si>
+    <t>Programa cargado en RAM y Pila de Instrucciones.</t>
+  </si>
+  <si>
+    <t>LD BX, 10H</t>
   </si>
   <si>
     <t>00H</t>
   </si>
   <si>
-    <t>MOV AX, 03H</t>
-  </si>
-  <si>
-    <t>MOV AX, 0AH</t>
+    <t>JC 0AH</t>
   </si>
   <si>
     <t>ADD AX, 03H</t>
   </si>
   <si>
-    <t>INC AX</t>
-  </si>
-  <si>
-    <t>MOV BX, 08H</t>
-  </si>
-  <si>
-    <t>LD BX, 10H</t>
+    <t>CMP AX, 05H</t>
+  </si>
+  <si>
+    <t>CMP AX, BX</t>
+  </si>
+  <si>
+    <t>ST 0EH, BX</t>
   </si>
   <si>
     <t>DEC BX</t>
   </si>
   <si>
-    <t>CMP AX, 05H</t>
-  </si>
-  <si>
-    <t>CMP AX, BX</t>
+    <t>JNZ 01H</t>
+  </si>
+  <si>
+    <t>ST 20H, AX</t>
+  </si>
+  <si>
+    <t>JZ 06H</t>
+  </si>
+  <si>
+    <t>FETCH_1</t>
+  </si>
+  <si>
+    <t>ST 0FH, AX</t>
+  </si>
+  <si>
+    <t>Paso del PC (00H) al registro de direcciones MAR</t>
   </si>
   <si>
     <t>JNZ 02H</t>
   </si>
   <si>
-    <t>JNZ 01H</t>
-  </si>
-  <si>
-    <t>ST 20H, AX</t>
-  </si>
-  <si>
-    <t>JZ 06H</t>
-  </si>
-  <si>
     <t>HLT</t>
   </si>
   <si>
     <t>ST 30H, 00H</t>
   </si>
   <si>
+    <t>JMP 00H</t>
+  </si>
+  <si>
+    <t>FETCH_2</t>
+  </si>
+  <si>
+    <t>Lectura de RAM en dirección 00H: Dato obtenido LD AX, 0EH</t>
+  </si>
+  <si>
+    <t>NOP</t>
+  </si>
+  <si>
+    <t>ST 30H, FFH</t>
+  </si>
+  <si>
+    <t>FETCH_3</t>
+  </si>
+  <si>
+    <t>Carga de instrucción al registro IR y avance del contador de programa PC</t>
+  </si>
+  <si>
+    <t>01H</t>
+  </si>
+  <si>
+    <t>DECODE</t>
+  </si>
+  <si>
+    <t>Decodificación: Operación LD sobre destino AX con origen 0EH</t>
+  </si>
+  <si>
     <t>Estado</t>
   </si>
   <si>
-    <t>ST 30H, FFH</t>
+    <t>STORE</t>
+  </si>
+  <si>
+    <t>STORE: Resultado guardado y Banderas actualizadas</t>
+  </si>
+  <si>
+    <t>0EH</t>
+  </si>
+  <si>
+    <t>EXECUTE: LD completado</t>
+  </si>
+  <si>
+    <t>Paso del PC (01H) al registro de direcciones MAR</t>
+  </si>
+  <si>
+    <t>Lectura de RAM en dirección 01H: Dato obtenido LD BX, 0FH</t>
+  </si>
+  <si>
+    <t>02H</t>
+  </si>
+  <si>
+    <t>Decodificación: Operación LD sobre destino BX con origen 0FH</t>
+  </si>
+  <si>
+    <t>EXECUTE</t>
+  </si>
+  <si>
+    <t>0FH</t>
+  </si>
+  <si>
+    <t>Paso del PC (02H) al registro de direcciones MAR</t>
   </si>
   <si>
     <t>CPU:</t>
   </si>
   <si>
+    <t>Lectura de RAM en dirección 02H: Dato obtenido ADD AX, BX</t>
+  </si>
+  <si>
+    <t>03H</t>
+  </si>
+  <si>
+    <t>Decodificación: Operación ADD sobre destino AX con origen BX</t>
+  </si>
+  <si>
+    <t>EXECUTE: ADD completado</t>
+  </si>
+  <si>
+    <t>Pila de Instrucciones</t>
+  </si>
+  <si>
+    <t>+</t>
+  </si>
+  <si>
+    <t>🔄 Formato RAM cambiado a DEC</t>
+  </si>
+  <si>
+    <t>Paso del PC (03H) al registro de direcciones MAR</t>
+  </si>
+  <si>
+    <t>Lectura de RAM en dirección 03H: Dato obtenido JC 0AH</t>
+  </si>
+  <si>
+    <t>04H</t>
+  </si>
+  <si>
+    <t>00H: LD AX, 0EH</t>
+  </si>
+  <si>
+    <t>Decodificación: Operación JC sobre destino 0AH con origen Ninguno</t>
+  </si>
+  <si>
+    <t>01H: LD BX, 0FH</t>
+  </si>
+  <si>
     <t>RAM</t>
   </si>
   <si>
+    <t>02H: ADD AX, BX</t>
+  </si>
+  <si>
     <t>Formato:</t>
   </si>
   <si>
+    <t>03H: JC 0AH</t>
+  </si>
+  <si>
+    <t>04H: ST 0EH, BX</t>
+  </si>
+  <si>
     <t>"+0"</t>
   </si>
   <si>
@@ -190,18 +322,36 @@
     <t>"+F</t>
   </si>
   <si>
+    <t>05H: ST 0FH, AX</t>
+  </si>
+  <si>
+    <t>06H: JMP 00H</t>
+  </si>
+  <si>
     <t>10H</t>
   </si>
   <si>
+    <t>07H: NOP</t>
+  </si>
+  <si>
     <t>20H</t>
   </si>
   <si>
+    <t>08H: NOP</t>
+  </si>
+  <si>
     <t>30H</t>
   </si>
   <si>
+    <t>09H: NOP</t>
+  </si>
+  <si>
     <t>40H</t>
   </si>
   <si>
+    <t>0AH: HLT</t>
+  </si>
+  <si>
     <t>50H</t>
   </si>
   <si>
@@ -248,9 +398,6 @@
   </si>
   <si>
     <t>Simbolo</t>
-  </si>
-  <si>
-    <t>04H</t>
   </si>
   <si>
     <t>de Operacion</t>
@@ -278,7 +425,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -298,6 +445,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="22.0"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -328,7 +482,6 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
-    <font/>
     <font>
       <b/>
       <i/>
@@ -397,6 +550,7 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font/>
     <font>
       <b/>
       <sz val="19.0"/>
@@ -405,7 +559,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -438,8 +592,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA4C2F4"/>
+        <bgColor rgb="FFA4C2F4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD9EAD3"/>
         <bgColor rgb="FFD9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB3B"/>
+        <bgColor rgb="FFFFEB3B"/>
       </patternFill>
     </fill>
     <fill>
@@ -467,7 +633,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="41">
+  <borders count="42">
     <border/>
     <border>
       <left style="thin">
@@ -506,6 +672,17 @@
       </bottom>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+    </border>
+    <border>
       <right style="thin">
         <color rgb="FFFFFFFF"/>
       </right>
@@ -531,6 +708,27 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFFFFFFF"/>
       </left>
       <right style="thin">
@@ -546,14 +744,21 @@
       </left>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+    </border>
+    <border>
       <right style="thin">
         <color rgb="FFFFFFFF"/>
       </right>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
       <right style="thin">
         <color rgb="FFFFFFFF"/>
       </right>
@@ -579,14 +784,6 @@
       </bottom>
     </border>
     <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFFFFFFF"/>
       </left>
@@ -609,20 +806,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFFFFFFF"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FFFFFFFF"/>
       </left>
       <right style="thin">
@@ -637,7 +820,7 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
         <color rgb="FFFFFFFF"/>
@@ -645,6 +828,9 @@
       <top style="thin">
         <color rgb="FFFFFFFF"/>
       </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
     </border>
     <border>
       <left style="thin">
@@ -661,24 +847,22 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <top style="thin">
+      <bottom style="thin">
         <color rgb="FF000000"/>
-      </top>
+      </bottom>
     </border>
     <border>
-      <top style="thin">
+      <bottom style="thin">
         <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
+      </bottom>
     </border>
     <border>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
     </border>
     <border>
       <left style="thin">
@@ -698,27 +882,6 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -796,6 +959,20 @@
       </bottom>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+    </border>
+    <border>
       <top style="thin">
         <color rgb="FFFFFFFF"/>
       </top>
@@ -862,7 +1039,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="110">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -873,12 +1050,16 @@
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="21" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -888,45 +1069,82 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="3" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="3" fillId="5" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="4" fillId="5" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="5" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="6" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="9" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="10" fillId="6" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="7" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="8" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf quotePrefix="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="9" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="10" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="2" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="11" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="12" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="13" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="14" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="15" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="16" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="12" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="13" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="14" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="15" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="16" fillId="7" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="17" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="10" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="18" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="19" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="20" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -936,70 +1154,81 @@
     <xf borderId="3" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="17" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="18" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="21" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="13" fillId="8" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="19" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="22" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="6" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="23" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="13" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="20" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="21" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="22" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="8" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="9" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="13" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="23" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="14" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="24" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="25" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="26" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="3" fillId="2" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="18" fillId="2" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="4" fillId="2" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="3" fillId="2" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="24" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="27" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="23" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="14" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="25" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="28" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="23" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="14" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="26" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="24" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="27" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="27" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="28" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="25" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="25" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="26" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="29" fillId="0" fontId="13" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="30" fillId="0" fontId="13" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="31" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="32" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="33" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="34" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="9" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="11" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="9" fontId="3" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="10" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="11" fontId="3" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="35" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="36" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="4" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -1008,41 +1237,41 @@
     <xf borderId="1" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="11" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="29" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf quotePrefix="1" borderId="29" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="24" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="7" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="27" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="9" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="36" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="10" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="37" fillId="0" fontId="19" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="12" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="18" fillId="7" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="37" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="9" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="38" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="38" fillId="0" fontId="17" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="15" fillId="0" fontId="17" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="17" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="38" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="15" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="39" fillId="0" fontId="17" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="20" fillId="0" fontId="17" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="11" fillId="0" fontId="17" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="39" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="20" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="40" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="40" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="41" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -2113,6 +2342,153 @@
     </xdr:sp>
     <xdr:clientData fLocksWithSheet="0"/>
   </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>295275</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="704850"/>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="2" name="Shape 2" title="Dibujo"/>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="3723050" y="4363450"/>
+          <a:ext cx="654000" cy="1000500"/>
+          <a:chOff x="3723050" y="4363450"/>
+          <a:chExt cx="654000" cy="1000500"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp>
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="21" name="Shape 21"/>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="3723050" y="4363450"/>
+            <a:ext cx="654000" cy="1000500"/>
+          </a:xfrm>
+          <a:prstGeom prst="straightConnector1">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln cap="flat" cmpd="sng" w="9525">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd len="med" w="med" type="none"/>
+            <a:tailEnd len="med" w="med" type="triangle"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>238125</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="981075" cy="733425"/>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="2" name="Shape 2" title="Dibujo"/>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="1018600" y="2808100"/>
+          <a:ext cx="1040100" cy="802500"/>
+          <a:chOff x="1018600" y="2808100"/>
+          <a:chExt cx="1040100" cy="802500"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp>
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="22" name="Shape 22"/>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="1018600" y="2808100"/>
+            <a:ext cx="1040100" cy="802500"/>
+          </a:xfrm>
+          <a:prstGeom prst="straightConnector1">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln cap="flat" cmpd="sng" w="9525">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd len="med" w="med" type="none"/>
+            <a:tailEnd len="med" w="med" type="triangle"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>581025</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="47625" cy="600075"/>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="2" name="Shape 2" title="Dibujo"/>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="3188075" y="3382675"/>
+          <a:ext cx="29700" cy="582000"/>
+          <a:chOff x="3188075" y="3382675"/>
+          <a:chExt cx="29700" cy="582000"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp>
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="23" name="Shape 23"/>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="3188075" y="3382675"/>
+            <a:ext cx="29700" cy="582000"/>
+          </a:xfrm>
+          <a:prstGeom prst="straightConnector1">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln cap="flat" cmpd="sng" w="9525">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd len="med" w="med" type="none"/>
+            <a:tailEnd len="med" w="med" type="triangle"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2337,170 +2713,199 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="5" t="s">
-        <v>23</v>
+        <v>8</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="6" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="K4" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="5" t="s">
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="5" t="s">
-        <v>27</v>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="6" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="5" t="s">
-        <v>30</v>
+      <c r="H5" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="6" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="P6" s="9"/>
-      <c r="Q6" s="9"/>
-      <c r="R6" s="5" t="s">
         <v>34</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="6" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="P7" s="9"/>
-      <c r="Q7" s="9"/>
-      <c r="R7" s="5" t="s">
-        <v>36</v>
+        <v>40</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="6" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
-      <c r="N8" s="9"/>
-      <c r="O8" s="9"/>
-      <c r="P8" s="9"/>
-      <c r="Q8" s="9"/>
-      <c r="R8" s="5" t="s">
-        <v>35</v>
+        <v>45</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="6" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="9"/>
-      <c r="Q9" s="9"/>
-      <c r="R9" s="5" t="s">
-        <v>38</v>
+      <c r="A9" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="6" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
-      <c r="P10" s="9"/>
-      <c r="Q10" s="9"/>
-      <c r="R10" s="5" t="s">
-        <v>35</v>
+      <c r="A10" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="7"/>
+      <c r="P10" s="7"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="6" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4"/>
+      <c r="A11" s="5" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="4"/>
+      <c r="A12" s="5" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="12"/>
+      <c r="A13" s="11"/>
     </row>
     <row r="14">
-      <c r="A14" s="12"/>
+      <c r="A14" s="11"/>
     </row>
     <row r="15">
-      <c r="A15" s="12"/>
+      <c r="A15" s="11"/>
     </row>
     <row r="16">
-      <c r="A16" s="12"/>
+      <c r="A16" s="11"/>
     </row>
     <row r="17">
-      <c r="A17" s="12"/>
+      <c r="A17" s="11"/>
     </row>
     <row r="18">
-      <c r="A18" s="12"/>
+      <c r="A18" s="11"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -2516,8 +2921,8 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="s">
-        <v>37</v>
+      <c r="A1" s="12" t="s">
+        <v>55</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="14"/>
@@ -2526,85 +2931,105 @@
       <c r="F1" s="15"/>
       <c r="G1" s="16"/>
       <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
       <c r="L1" s="16"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
+      <c r="Q1" s="18"/>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="18"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="22"/>
+      <c r="A2" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="19"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="J2" s="25"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="27"/>
     </row>
     <row r="3">
-      <c r="A3" s="23"/>
-      <c r="B3" s="23"/>
+      <c r="A3" s="28"/>
+      <c r="B3" s="28"/>
       <c r="C3" s="14"/>
       <c r="D3" s="14"/>
-      <c r="E3" s="24"/>
-      <c r="L3" s="25"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="J3" s="32"/>
+      <c r="K3" s="33"/>
+      <c r="L3" s="34"/>
     </row>
     <row r="4">
-      <c r="E4" s="24"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="N4" s="27"/>
-      <c r="O4" s="27"/>
-      <c r="P4" s="27"/>
-      <c r="Q4" s="27"/>
-      <c r="R4" s="27"/>
-      <c r="S4" s="27"/>
-      <c r="T4" s="27"/>
-      <c r="U4" s="27"/>
-      <c r="V4" s="27"/>
-      <c r="W4" s="27"/>
-      <c r="X4" s="27"/>
-      <c r="Y4" s="27"/>
-      <c r="Z4" s="27"/>
-      <c r="AA4" s="27"/>
-      <c r="AB4" s="27"/>
-      <c r="AC4" s="27"/>
-      <c r="AD4" s="27"/>
-      <c r="AE4" s="28"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="J4" s="32"/>
+      <c r="K4" s="33"/>
+      <c r="L4" s="34"/>
+      <c r="M4" s="35" t="s">
+        <v>81</v>
+      </c>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
+      <c r="S4" s="36"/>
+      <c r="T4" s="36"/>
+      <c r="U4" s="36"/>
+      <c r="V4" s="36"/>
+      <c r="W4" s="36"/>
+      <c r="X4" s="36"/>
+      <c r="Y4" s="36"/>
+      <c r="Z4" s="36"/>
+      <c r="AA4" s="36"/>
+      <c r="AB4" s="36"/>
+      <c r="AC4" s="36"/>
+      <c r="AD4" s="36"/>
+      <c r="AE4" s="37"/>
     </row>
     <row r="5">
-      <c r="E5" s="29"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="30"/>
-      <c r="J5" s="30"/>
-      <c r="K5" s="30"/>
-      <c r="L5" s="31"/>
-      <c r="M5" s="32"/>
-      <c r="O5" s="33" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q5" s="34"/>
-      <c r="R5" s="35"/>
-      <c r="S5" s="36"/>
-      <c r="T5" s="35"/>
-      <c r="U5" s="34"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="J5" s="32"/>
+      <c r="K5" s="33"/>
+      <c r="L5" s="40"/>
+      <c r="M5" s="41"/>
+      <c r="O5" s="42" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q5" s="43"/>
+      <c r="R5" s="44"/>
+      <c r="S5" s="45"/>
+      <c r="T5" s="44"/>
+      <c r="U5" s="43"/>
       <c r="V5" s="14"/>
       <c r="W5" s="14"/>
       <c r="X5" s="14"/>
@@ -2613,12 +3038,17 @@
       <c r="AA5" s="14"/>
       <c r="AB5" s="14"/>
       <c r="AC5" s="14"/>
-      <c r="AE5" s="37"/>
+      <c r="AE5" s="46"/>
     </row>
     <row r="6">
-      <c r="M6" s="32"/>
+      <c r="I6" s="47" t="s">
+        <v>84</v>
+      </c>
+      <c r="J6" s="32"/>
+      <c r="K6" s="33"/>
+      <c r="M6" s="48"/>
       <c r="N6" s="14"/>
-      <c r="O6" s="38"/>
+      <c r="O6" s="49"/>
       <c r="P6" s="14"/>
       <c r="Q6" s="14"/>
       <c r="R6" s="14"/>
@@ -2634,555 +3064,631 @@
       <c r="AB6" s="14"/>
       <c r="AC6" s="14"/>
       <c r="AD6" s="14"/>
-      <c r="AE6" s="37"/>
+      <c r="AE6" s="46"/>
     </row>
     <row r="7">
-      <c r="M7" s="32"/>
-      <c r="N7" s="39"/>
-      <c r="O7" s="40" t="s">
-        <v>42</v>
-      </c>
-      <c r="P7" s="40" t="s">
+      <c r="I7" s="31" t="s">
+        <v>85</v>
+      </c>
+      <c r="J7" s="32"/>
+      <c r="K7" s="33"/>
+      <c r="M7" s="48"/>
+      <c r="N7" s="50"/>
+      <c r="O7" s="51" t="s">
+        <v>86</v>
+      </c>
+      <c r="P7" s="51" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q7" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="R7" s="51" t="s">
+        <v>89</v>
+      </c>
+      <c r="S7" s="51" t="s">
+        <v>90</v>
+      </c>
+      <c r="T7" s="51" t="s">
+        <v>91</v>
+      </c>
+      <c r="U7" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="V7" s="51" t="s">
+        <v>93</v>
+      </c>
+      <c r="W7" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="X7" s="51" t="s">
+        <v>95</v>
+      </c>
+      <c r="Y7" s="51" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z7" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="AA7" s="51" t="s">
+        <v>98</v>
+      </c>
+      <c r="AB7" s="51" t="s">
+        <v>99</v>
+      </c>
+      <c r="AC7" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="AD7" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="AE7" s="46"/>
+    </row>
+    <row r="8">
+      <c r="I8" s="31" t="s">
+        <v>102</v>
+      </c>
+      <c r="J8" s="32"/>
+      <c r="K8" s="33"/>
+      <c r="M8" s="52"/>
+      <c r="N8" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="O8" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="P8" s="53" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q8" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="R8" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="S8" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="T8" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="U8" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="V8" s="53" t="s">
+        <v>48</v>
+      </c>
+      <c r="W8" s="53" t="s">
+        <v>48</v>
+      </c>
+      <c r="X8" s="53" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y8" s="53" t="s">
         <v>43</v>
       </c>
-      <c r="Q7" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="R7" s="40" t="s">
-        <v>45</v>
-      </c>
-      <c r="S7" s="40" t="s">
-        <v>46</v>
-      </c>
-      <c r="T7" s="40" t="s">
-        <v>47</v>
-      </c>
-      <c r="U7" s="40" t="s">
-        <v>48</v>
-      </c>
-      <c r="V7" s="40" t="s">
-        <v>49</v>
-      </c>
-      <c r="W7" s="40" t="s">
-        <v>50</v>
-      </c>
-      <c r="X7" s="40" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y7" s="40" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z7" s="40" t="s">
-        <v>53</v>
-      </c>
-      <c r="AA7" s="40" t="s">
-        <v>54</v>
-      </c>
-      <c r="AB7" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="AC7" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="AD7" s="40" t="s">
-        <v>57</v>
-      </c>
-      <c r="AE7" s="37"/>
-    </row>
-    <row r="8">
-      <c r="M8" s="41"/>
-      <c r="N8" s="40" t="s">
-        <v>21</v>
-      </c>
-      <c r="O8" s="42" t="s">
+      <c r="Z8" s="54"/>
+      <c r="AA8" s="54"/>
+      <c r="AB8" s="54"/>
+      <c r="AC8" s="53">
+        <v>0.0</v>
+      </c>
+      <c r="AD8" s="53">
+        <v>1.0</v>
+      </c>
+      <c r="AE8" s="46"/>
+    </row>
+    <row r="9">
+      <c r="I9" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="J9" s="32"/>
+      <c r="K9" s="33"/>
+      <c r="M9" s="48"/>
+      <c r="N9" s="51" t="s">
+        <v>104</v>
+      </c>
+      <c r="O9" s="54"/>
+      <c r="P9" s="54"/>
+      <c r="Q9" s="54"/>
+      <c r="R9" s="54"/>
+      <c r="S9" s="54"/>
+      <c r="T9" s="54"/>
+      <c r="U9" s="54"/>
+      <c r="V9" s="54"/>
+      <c r="W9" s="54"/>
+      <c r="X9" s="54"/>
+      <c r="Y9" s="54"/>
+      <c r="Z9" s="54"/>
+      <c r="AA9" s="54"/>
+      <c r="AB9" s="54"/>
+      <c r="AC9" s="54"/>
+      <c r="AD9" s="54"/>
+      <c r="AE9" s="46"/>
+    </row>
+    <row r="10">
+      <c r="I10" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="J10" s="32"/>
+      <c r="K10" s="33"/>
+      <c r="M10" s="48"/>
+      <c r="N10" s="51" t="s">
+        <v>106</v>
+      </c>
+      <c r="O10" s="53"/>
+      <c r="P10" s="53"/>
+      <c r="Q10" s="53"/>
+      <c r="R10" s="54"/>
+      <c r="S10" s="54"/>
+      <c r="T10" s="54"/>
+      <c r="U10" s="54"/>
+      <c r="V10" s="54"/>
+      <c r="W10" s="54"/>
+      <c r="X10" s="54"/>
+      <c r="Y10" s="54"/>
+      <c r="Z10" s="54"/>
+      <c r="AA10" s="54"/>
+      <c r="AB10" s="54"/>
+      <c r="AC10" s="54"/>
+      <c r="AD10" s="54"/>
+      <c r="AE10" s="46"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="55"/>
+      <c r="B11" s="56"/>
+      <c r="C11" s="56"/>
+      <c r="D11" s="56"/>
+      <c r="E11" s="56"/>
+      <c r="F11" s="37"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="J11" s="32"/>
+      <c r="K11" s="33"/>
+      <c r="M11" s="48"/>
+      <c r="N11" s="51" t="s">
+        <v>108</v>
+      </c>
+      <c r="O11" s="54"/>
+      <c r="P11" s="54"/>
+      <c r="Q11" s="54"/>
+      <c r="R11" s="54"/>
+      <c r="S11" s="54"/>
+      <c r="T11" s="54"/>
+      <c r="U11" s="54"/>
+      <c r="V11" s="54"/>
+      <c r="W11" s="54"/>
+      <c r="X11" s="54"/>
+      <c r="Y11" s="54"/>
+      <c r="Z11" s="54"/>
+      <c r="AA11" s="54"/>
+      <c r="AB11" s="54"/>
+      <c r="AC11" s="54"/>
+      <c r="AD11" s="54"/>
+      <c r="AE11" s="46"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="57"/>
+      <c r="B12" s="58"/>
+      <c r="D12" s="58"/>
+      <c r="F12" s="59"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="J12" s="32"/>
+      <c r="K12" s="33"/>
+      <c r="M12" s="48"/>
+      <c r="N12" s="51" t="s">
+        <v>110</v>
+      </c>
+      <c r="O12" s="53"/>
+      <c r="P12" s="54"/>
+      <c r="Q12" s="54"/>
+      <c r="R12" s="54"/>
+      <c r="S12" s="54"/>
+      <c r="T12" s="54"/>
+      <c r="U12" s="54"/>
+      <c r="V12" s="54"/>
+      <c r="W12" s="54"/>
+      <c r="X12" s="54"/>
+      <c r="Y12" s="54"/>
+      <c r="Z12" s="54"/>
+      <c r="AA12" s="54"/>
+      <c r="AB12" s="54"/>
+      <c r="AC12" s="54"/>
+      <c r="AD12" s="54"/>
+      <c r="AE12" s="46"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="57"/>
+      <c r="F13" s="59"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="60" t="s">
+        <v>111</v>
+      </c>
+      <c r="J13" s="61"/>
+      <c r="K13" s="62"/>
+      <c r="M13" s="48"/>
+      <c r="N13" s="51" t="s">
+        <v>112</v>
+      </c>
+      <c r="O13" s="54"/>
+      <c r="P13" s="54"/>
+      <c r="Q13" s="54"/>
+      <c r="R13" s="54"/>
+      <c r="S13" s="54"/>
+      <c r="T13" s="54"/>
+      <c r="U13" s="54"/>
+      <c r="V13" s="54"/>
+      <c r="W13" s="54"/>
+      <c r="X13" s="54"/>
+      <c r="Y13" s="54"/>
+      <c r="Z13" s="54"/>
+      <c r="AA13" s="54"/>
+      <c r="AB13" s="54"/>
+      <c r="AC13" s="54"/>
+      <c r="AD13" s="54"/>
+      <c r="AE13" s="46"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="57"/>
+      <c r="F14" s="59"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="32"/>
+      <c r="J14" s="32"/>
+      <c r="K14" s="32"/>
+      <c r="M14" s="48"/>
+      <c r="N14" s="51" t="s">
+        <v>113</v>
+      </c>
+      <c r="O14" s="54"/>
+      <c r="P14" s="54"/>
+      <c r="Q14" s="54"/>
+      <c r="R14" s="54"/>
+      <c r="S14" s="54"/>
+      <c r="T14" s="54"/>
+      <c r="U14" s="54"/>
+      <c r="V14" s="54"/>
+      <c r="W14" s="54"/>
+      <c r="X14" s="54"/>
+      <c r="Y14" s="54"/>
+      <c r="Z14" s="54"/>
+      <c r="AA14" s="54"/>
+      <c r="AB14" s="54"/>
+      <c r="AC14" s="54"/>
+      <c r="AD14" s="54"/>
+      <c r="AE14" s="46"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="57"/>
+      <c r="B15" s="63" t="s">
+        <v>114</v>
+      </c>
+      <c r="C15" s="64"/>
+      <c r="D15" s="64"/>
+      <c r="E15" s="65"/>
+      <c r="F15" s="59"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="M15" s="48"/>
+      <c r="N15" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="O15" s="54"/>
+      <c r="P15" s="54"/>
+      <c r="Q15" s="54"/>
+      <c r="R15" s="54"/>
+      <c r="S15" s="54"/>
+      <c r="T15" s="54"/>
+      <c r="U15" s="54"/>
+      <c r="V15" s="54"/>
+      <c r="W15" s="54"/>
+      <c r="X15" s="54"/>
+      <c r="Y15" s="54"/>
+      <c r="Z15" s="54"/>
+      <c r="AA15" s="54"/>
+      <c r="AB15" s="54"/>
+      <c r="AC15" s="54"/>
+      <c r="AD15" s="54"/>
+      <c r="AE15" s="46"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="57"/>
+      <c r="B16" s="66"/>
+      <c r="C16" s="67" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16" s="68" t="s">
+        <v>5</v>
+      </c>
+      <c r="E16" s="41"/>
+      <c r="F16" s="59"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="32"/>
+      <c r="J16" s="32"/>
+      <c r="K16" s="32"/>
+      <c r="M16" s="48"/>
+      <c r="N16" s="69" t="s">
+        <v>116</v>
+      </c>
+      <c r="O16" s="54"/>
+      <c r="P16" s="54"/>
+      <c r="Q16" s="54"/>
+      <c r="R16" s="54"/>
+      <c r="S16" s="54"/>
+      <c r="T16" s="54"/>
+      <c r="U16" s="54"/>
+      <c r="V16" s="54"/>
+      <c r="W16" s="54"/>
+      <c r="X16" s="54"/>
+      <c r="Y16" s="54"/>
+      <c r="Z16" s="54"/>
+      <c r="AA16" s="54"/>
+      <c r="AB16" s="54"/>
+      <c r="AC16" s="54"/>
+      <c r="AD16" s="54"/>
+      <c r="AE16" s="46"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="57"/>
+      <c r="B17" s="66"/>
+      <c r="C17" s="67" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="68" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17" s="41"/>
+      <c r="F17" s="59"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="32"/>
+      <c r="J17" s="32"/>
+      <c r="K17" s="32"/>
+      <c r="M17" s="48"/>
+      <c r="N17" s="69" t="s">
+        <v>117</v>
+      </c>
+      <c r="O17" s="54"/>
+      <c r="P17" s="54"/>
+      <c r="Q17" s="54"/>
+      <c r="R17" s="54"/>
+      <c r="S17" s="54"/>
+      <c r="T17" s="54"/>
+      <c r="U17" s="54"/>
+      <c r="V17" s="54"/>
+      <c r="W17" s="54"/>
+      <c r="X17" s="54"/>
+      <c r="Y17" s="54"/>
+      <c r="Z17" s="54"/>
+      <c r="AA17" s="54"/>
+      <c r="AB17" s="54"/>
+      <c r="AC17" s="54"/>
+      <c r="AD17" s="54"/>
+      <c r="AE17" s="46"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="57"/>
+      <c r="B18" s="66"/>
+      <c r="C18" s="67" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="P8" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q8" s="42" t="s">
-        <v>24</v>
-      </c>
-      <c r="R8" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="S8" s="42" t="s">
-        <v>31</v>
-      </c>
-      <c r="T8" s="42" t="s">
-        <v>33</v>
-      </c>
-      <c r="U8" s="42" t="s">
-        <v>35</v>
-      </c>
-      <c r="V8" s="42"/>
-      <c r="W8" s="42"/>
-      <c r="X8" s="42"/>
-      <c r="Y8" s="42"/>
-      <c r="Z8" s="43"/>
-      <c r="AA8" s="43"/>
-      <c r="AB8" s="43"/>
-      <c r="AC8" s="43"/>
-      <c r="AD8" s="43"/>
-      <c r="AE8" s="37"/>
-    </row>
-    <row r="9">
-      <c r="M9" s="32"/>
-      <c r="N9" s="40" t="s">
-        <v>58</v>
-      </c>
-      <c r="O9" s="43"/>
-      <c r="P9" s="43"/>
-      <c r="Q9" s="43"/>
-      <c r="R9" s="43"/>
-      <c r="S9" s="43"/>
-      <c r="T9" s="43"/>
-      <c r="U9" s="43"/>
-      <c r="V9" s="43"/>
-      <c r="W9" s="43"/>
-      <c r="X9" s="43"/>
-      <c r="Y9" s="43"/>
-      <c r="Z9" s="43"/>
-      <c r="AA9" s="43"/>
-      <c r="AB9" s="43"/>
-      <c r="AC9" s="43"/>
-      <c r="AD9" s="43"/>
-      <c r="AE9" s="37"/>
-    </row>
-    <row r="10">
-      <c r="M10" s="32"/>
-      <c r="N10" s="40" t="s">
-        <v>59</v>
-      </c>
-      <c r="O10" s="42"/>
-      <c r="P10" s="42"/>
-      <c r="Q10" s="42"/>
-      <c r="R10" s="43"/>
-      <c r="S10" s="43"/>
-      <c r="T10" s="43"/>
-      <c r="U10" s="43"/>
-      <c r="V10" s="43"/>
-      <c r="W10" s="43"/>
-      <c r="X10" s="43"/>
-      <c r="Y10" s="43"/>
-      <c r="Z10" s="43"/>
-      <c r="AA10" s="43"/>
-      <c r="AB10" s="43"/>
-      <c r="AC10" s="43"/>
-      <c r="AD10" s="43"/>
-      <c r="AE10" s="37"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="44"/>
-      <c r="B11" s="45"/>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="45"/>
-      <c r="F11" s="28"/>
-      <c r="H11" s="7"/>
-      <c r="M11" s="32"/>
-      <c r="N11" s="40" t="s">
-        <v>60</v>
-      </c>
-      <c r="O11" s="43"/>
-      <c r="P11" s="43"/>
-      <c r="Q11" s="43"/>
-      <c r="R11" s="43"/>
-      <c r="S11" s="43"/>
-      <c r="T11" s="43"/>
-      <c r="U11" s="43"/>
-      <c r="V11" s="43"/>
-      <c r="W11" s="43"/>
-      <c r="X11" s="43"/>
-      <c r="Y11" s="43"/>
-      <c r="Z11" s="43"/>
-      <c r="AA11" s="43"/>
-      <c r="AB11" s="43"/>
-      <c r="AC11" s="43"/>
-      <c r="AD11" s="43"/>
-      <c r="AE11" s="37"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="46"/>
-      <c r="B12" s="47"/>
-      <c r="D12" s="47"/>
-      <c r="F12" s="48"/>
-      <c r="H12" s="7"/>
-      <c r="M12" s="32"/>
-      <c r="N12" s="40" t="s">
-        <v>61</v>
-      </c>
-      <c r="O12" s="42"/>
-      <c r="P12" s="43"/>
-      <c r="Q12" s="43"/>
-      <c r="R12" s="43"/>
-      <c r="S12" s="43"/>
-      <c r="T12" s="43"/>
-      <c r="U12" s="43"/>
-      <c r="V12" s="43"/>
-      <c r="W12" s="43"/>
-      <c r="X12" s="43"/>
-      <c r="Y12" s="43"/>
-      <c r="Z12" s="43"/>
-      <c r="AA12" s="43"/>
-      <c r="AB12" s="43"/>
-      <c r="AC12" s="43"/>
-      <c r="AD12" s="43"/>
-      <c r="AE12" s="37"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="46"/>
-      <c r="F13" s="48"/>
-      <c r="H13" s="7"/>
-      <c r="M13" s="32"/>
-      <c r="N13" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="O13" s="43"/>
-      <c r="P13" s="43"/>
-      <c r="Q13" s="43"/>
-      <c r="R13" s="43"/>
-      <c r="S13" s="43"/>
-      <c r="T13" s="43"/>
-      <c r="U13" s="43"/>
-      <c r="V13" s="43"/>
-      <c r="W13" s="43"/>
-      <c r="X13" s="43"/>
-      <c r="Y13" s="43"/>
-      <c r="Z13" s="43"/>
-      <c r="AA13" s="43"/>
-      <c r="AB13" s="43"/>
-      <c r="AC13" s="43"/>
-      <c r="AD13" s="43"/>
-      <c r="AE13" s="37"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="46"/>
-      <c r="F14" s="48"/>
-      <c r="H14" s="7"/>
-      <c r="M14" s="32"/>
-      <c r="N14" s="40" t="s">
-        <v>63</v>
-      </c>
-      <c r="O14" s="43"/>
-      <c r="P14" s="43"/>
-      <c r="Q14" s="43"/>
-      <c r="R14" s="43"/>
-      <c r="S14" s="43"/>
-      <c r="T14" s="43"/>
-      <c r="U14" s="43"/>
-      <c r="V14" s="43"/>
-      <c r="W14" s="43"/>
-      <c r="X14" s="43"/>
-      <c r="Y14" s="43"/>
-      <c r="Z14" s="43"/>
-      <c r="AA14" s="43"/>
-      <c r="AB14" s="43"/>
-      <c r="AC14" s="43"/>
-      <c r="AD14" s="43"/>
-      <c r="AE14" s="37"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="46"/>
-      <c r="B15" s="49" t="s">
-        <v>64</v>
-      </c>
-      <c r="C15" s="50"/>
-      <c r="D15" s="50"/>
-      <c r="E15" s="51"/>
-      <c r="F15" s="48"/>
-      <c r="H15" s="7"/>
-      <c r="M15" s="32"/>
-      <c r="N15" s="40" t="s">
-        <v>65</v>
-      </c>
-      <c r="O15" s="43"/>
-      <c r="P15" s="43"/>
-      <c r="Q15" s="43"/>
-      <c r="R15" s="43"/>
-      <c r="S15" s="43"/>
-      <c r="T15" s="43"/>
-      <c r="U15" s="43"/>
-      <c r="V15" s="43"/>
-      <c r="W15" s="43"/>
-      <c r="X15" s="43"/>
-      <c r="Y15" s="43"/>
-      <c r="Z15" s="43"/>
-      <c r="AA15" s="43"/>
-      <c r="AB15" s="43"/>
-      <c r="AC15" s="43"/>
-      <c r="AD15" s="43"/>
-      <c r="AE15" s="37"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="46"/>
-      <c r="B16" s="52"/>
-      <c r="C16" s="53" t="s">
-        <v>21</v>
-      </c>
-      <c r="D16" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="E16" s="55"/>
-      <c r="F16" s="48"/>
-      <c r="H16" s="7"/>
-      <c r="M16" s="32"/>
-      <c r="N16" s="56" t="s">
-        <v>66</v>
-      </c>
-      <c r="O16" s="43"/>
-      <c r="P16" s="43"/>
-      <c r="Q16" s="43"/>
-      <c r="R16" s="43"/>
-      <c r="S16" s="43"/>
-      <c r="T16" s="43"/>
-      <c r="U16" s="43"/>
-      <c r="V16" s="43"/>
-      <c r="W16" s="43"/>
-      <c r="X16" s="43"/>
-      <c r="Y16" s="43"/>
-      <c r="Z16" s="43"/>
-      <c r="AA16" s="43"/>
-      <c r="AB16" s="43"/>
-      <c r="AC16" s="43"/>
-      <c r="AD16" s="43"/>
-      <c r="AE16" s="37"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="46"/>
-      <c r="B17" s="52"/>
-      <c r="C17" s="53" t="s">
-        <v>21</v>
-      </c>
-      <c r="D17" s="54" t="s">
-        <v>5</v>
-      </c>
-      <c r="E17" s="55"/>
-      <c r="F17" s="48"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="M17" s="32"/>
-      <c r="N17" s="56" t="s">
-        <v>67</v>
-      </c>
-      <c r="O17" s="43"/>
-      <c r="P17" s="43"/>
-      <c r="Q17" s="43"/>
-      <c r="R17" s="43"/>
-      <c r="S17" s="43"/>
-      <c r="T17" s="43"/>
-      <c r="U17" s="43"/>
-      <c r="V17" s="43"/>
-      <c r="W17" s="43"/>
-      <c r="X17" s="43"/>
-      <c r="Y17" s="43"/>
-      <c r="Z17" s="43"/>
-      <c r="AA17" s="43"/>
-      <c r="AB17" s="43"/>
-      <c r="AC17" s="43"/>
-      <c r="AD17" s="43"/>
-      <c r="AE17" s="37"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="46"/>
-      <c r="B18" s="52"/>
-      <c r="C18" s="53" t="s">
-        <v>21</v>
-      </c>
-      <c r="D18" s="54" t="s">
-        <v>6</v>
-      </c>
-      <c r="E18" s="55"/>
-      <c r="F18" s="57"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="M18" s="32"/>
-      <c r="N18" s="56" t="s">
-        <v>68</v>
-      </c>
-      <c r="O18" s="43"/>
-      <c r="P18" s="43"/>
-      <c r="Q18" s="43"/>
-      <c r="R18" s="43"/>
-      <c r="S18" s="43"/>
-      <c r="T18" s="43"/>
-      <c r="U18" s="43"/>
-      <c r="V18" s="43"/>
-      <c r="W18" s="43"/>
-      <c r="X18" s="43"/>
-      <c r="Y18" s="43"/>
-      <c r="Z18" s="43"/>
-      <c r="AA18" s="43"/>
-      <c r="AB18" s="43"/>
-      <c r="AC18" s="43"/>
-      <c r="AD18" s="43"/>
-      <c r="AE18" s="37"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="32"/>
+      <c r="J18" s="32"/>
+      <c r="K18" s="32"/>
+      <c r="M18" s="48"/>
+      <c r="N18" s="69" t="s">
+        <v>118</v>
+      </c>
+      <c r="O18" s="54"/>
+      <c r="P18" s="54"/>
+      <c r="Q18" s="54"/>
+      <c r="R18" s="54"/>
+      <c r="S18" s="54"/>
+      <c r="T18" s="54"/>
+      <c r="U18" s="54"/>
+      <c r="V18" s="54"/>
+      <c r="W18" s="54"/>
+      <c r="X18" s="54"/>
+      <c r="Y18" s="54"/>
+      <c r="Z18" s="54"/>
+      <c r="AA18" s="54"/>
+      <c r="AB18" s="54"/>
+      <c r="AC18" s="54"/>
+      <c r="AD18" s="54"/>
+      <c r="AE18" s="46"/>
     </row>
     <row r="19">
-      <c r="A19" s="46"/>
-      <c r="B19" s="52"/>
-      <c r="C19" s="53" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19" s="55"/>
-      <c r="F19" s="57"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="M19" s="32"/>
-      <c r="N19" s="56" t="s">
-        <v>69</v>
-      </c>
-      <c r="O19" s="43"/>
-      <c r="P19" s="43"/>
-      <c r="Q19" s="43"/>
-      <c r="R19" s="43"/>
-      <c r="S19" s="43"/>
-      <c r="T19" s="43"/>
-      <c r="U19" s="43"/>
-      <c r="V19" s="43"/>
-      <c r="W19" s="43"/>
-      <c r="X19" s="43"/>
-      <c r="Y19" s="43"/>
-      <c r="Z19" s="43"/>
-      <c r="AA19" s="43"/>
-      <c r="AB19" s="43"/>
-      <c r="AC19" s="43"/>
-      <c r="AD19" s="43"/>
-      <c r="AE19" s="37"/>
+      <c r="A19" s="57"/>
+      <c r="B19" s="66"/>
+      <c r="C19" s="67" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="41"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="32"/>
+      <c r="J19" s="32"/>
+      <c r="K19" s="32"/>
+      <c r="M19" s="48"/>
+      <c r="N19" s="69" t="s">
+        <v>119</v>
+      </c>
+      <c r="O19" s="54"/>
+      <c r="P19" s="54"/>
+      <c r="Q19" s="54"/>
+      <c r="R19" s="54"/>
+      <c r="S19" s="54"/>
+      <c r="T19" s="54"/>
+      <c r="U19" s="54"/>
+      <c r="V19" s="54"/>
+      <c r="W19" s="54"/>
+      <c r="X19" s="54"/>
+      <c r="Y19" s="54"/>
+      <c r="Z19" s="54"/>
+      <c r="AA19" s="54"/>
+      <c r="AB19" s="54"/>
+      <c r="AC19" s="54"/>
+      <c r="AD19" s="54"/>
+      <c r="AE19" s="46"/>
     </row>
     <row r="20">
-      <c r="A20" s="46"/>
+      <c r="A20" s="57"/>
       <c r="B20" s="14"/>
-      <c r="C20" s="53" t="s">
-        <v>21</v>
-      </c>
-      <c r="D20" s="58" t="s">
-        <v>9</v>
+      <c r="C20" s="67">
+        <v>1.0</v>
+      </c>
+      <c r="D20" s="71" t="s">
+        <v>10</v>
       </c>
       <c r="E20" s="14"/>
-      <c r="F20" s="59"/>
-      <c r="G20" s="17"/>
-      <c r="M20" s="32"/>
-      <c r="N20" s="56" t="s">
-        <v>70</v>
-      </c>
-      <c r="O20" s="43"/>
-      <c r="P20" s="43"/>
-      <c r="Q20" s="43"/>
-      <c r="R20" s="43"/>
-      <c r="S20" s="43"/>
-      <c r="T20" s="43"/>
-      <c r="U20" s="43"/>
-      <c r="V20" s="43"/>
-      <c r="W20" s="43"/>
-      <c r="X20" s="43"/>
-      <c r="Y20" s="43"/>
-      <c r="Z20" s="43"/>
-      <c r="AA20" s="43"/>
-      <c r="AB20" s="43"/>
-      <c r="AC20" s="43"/>
-      <c r="AD20" s="43"/>
-      <c r="AE20" s="37"/>
+      <c r="F20" s="72"/>
+      <c r="G20" s="18"/>
+      <c r="I20" s="32"/>
+      <c r="J20" s="32"/>
+      <c r="K20" s="32"/>
+      <c r="M20" s="48"/>
+      <c r="N20" s="69" t="s">
+        <v>120</v>
+      </c>
+      <c r="O20" s="54"/>
+      <c r="P20" s="54"/>
+      <c r="Q20" s="54"/>
+      <c r="R20" s="54"/>
+      <c r="S20" s="54"/>
+      <c r="T20" s="54"/>
+      <c r="U20" s="54"/>
+      <c r="V20" s="54"/>
+      <c r="W20" s="54"/>
+      <c r="X20" s="54"/>
+      <c r="Y20" s="54"/>
+      <c r="Z20" s="54"/>
+      <c r="AA20" s="54"/>
+      <c r="AB20" s="54"/>
+      <c r="AC20" s="54"/>
+      <c r="AD20" s="54"/>
+      <c r="AE20" s="46"/>
     </row>
     <row r="21">
-      <c r="A21" s="46"/>
-      <c r="C21" s="53" t="s">
-        <v>21</v>
-      </c>
-      <c r="D21" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" s="48"/>
-      <c r="G21" s="17"/>
-      <c r="M21" s="32"/>
-      <c r="N21" s="56" t="s">
-        <v>71</v>
-      </c>
-      <c r="O21" s="43"/>
-      <c r="P21" s="43"/>
-      <c r="Q21" s="43"/>
-      <c r="R21" s="43"/>
-      <c r="S21" s="43"/>
-      <c r="T21" s="43"/>
-      <c r="U21" s="43"/>
-      <c r="V21" s="43"/>
-      <c r="W21" s="43"/>
-      <c r="X21" s="43"/>
-      <c r="Y21" s="43"/>
-      <c r="Z21" s="43"/>
-      <c r="AA21" s="43"/>
-      <c r="AB21" s="43"/>
-      <c r="AC21" s="43"/>
-      <c r="AD21" s="43"/>
-      <c r="AE21" s="37"/>
+      <c r="A21" s="57"/>
+      <c r="C21" s="67">
+        <v>1.0</v>
+      </c>
+      <c r="D21" s="71" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="59"/>
+      <c r="G21" s="18"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
+      <c r="M21" s="48"/>
+      <c r="N21" s="69" t="s">
+        <v>121</v>
+      </c>
+      <c r="O21" s="54"/>
+      <c r="P21" s="54"/>
+      <c r="Q21" s="54"/>
+      <c r="R21" s="54"/>
+      <c r="S21" s="54"/>
+      <c r="T21" s="54"/>
+      <c r="U21" s="54"/>
+      <c r="V21" s="54"/>
+      <c r="W21" s="54"/>
+      <c r="X21" s="54"/>
+      <c r="Y21" s="54"/>
+      <c r="Z21" s="54"/>
+      <c r="AA21" s="54"/>
+      <c r="AB21" s="54"/>
+      <c r="AC21" s="54"/>
+      <c r="AD21" s="54"/>
+      <c r="AE21" s="46"/>
     </row>
     <row r="22">
-      <c r="A22" s="60"/>
-      <c r="B22" s="61"/>
-      <c r="C22" s="62"/>
-      <c r="D22" s="62"/>
-      <c r="E22" s="62"/>
-      <c r="F22" s="63"/>
-      <c r="G22" s="17"/>
-      <c r="M22" s="32"/>
-      <c r="N22" s="56" t="s">
-        <v>72</v>
-      </c>
-      <c r="O22" s="43"/>
-      <c r="P22" s="43"/>
-      <c r="Q22" s="43"/>
-      <c r="R22" s="43"/>
-      <c r="S22" s="43"/>
-      <c r="T22" s="43"/>
-      <c r="U22" s="43"/>
-      <c r="V22" s="43"/>
-      <c r="W22" s="43"/>
-      <c r="X22" s="43"/>
-      <c r="Y22" s="43"/>
-      <c r="Z22" s="43"/>
-      <c r="AA22" s="43"/>
-      <c r="AB22" s="43"/>
-      <c r="AC22" s="43"/>
-      <c r="AD22" s="64"/>
-      <c r="AE22" s="37"/>
+      <c r="A22" s="73"/>
+      <c r="B22" s="74"/>
+      <c r="C22" s="75"/>
+      <c r="D22" s="75"/>
+      <c r="E22" s="75"/>
+      <c r="F22" s="76"/>
+      <c r="G22" s="18"/>
+      <c r="I22" s="32"/>
+      <c r="J22" s="32"/>
+      <c r="K22" s="32"/>
+      <c r="M22" s="48"/>
+      <c r="N22" s="69" t="s">
+        <v>122</v>
+      </c>
+      <c r="O22" s="54"/>
+      <c r="P22" s="54"/>
+      <c r="Q22" s="54"/>
+      <c r="R22" s="54"/>
+      <c r="S22" s="54"/>
+      <c r="T22" s="54"/>
+      <c r="U22" s="54"/>
+      <c r="V22" s="54"/>
+      <c r="W22" s="54"/>
+      <c r="X22" s="54"/>
+      <c r="Y22" s="54"/>
+      <c r="Z22" s="54"/>
+      <c r="AA22" s="54"/>
+      <c r="AB22" s="54"/>
+      <c r="AC22" s="54"/>
+      <c r="AD22" s="77"/>
+      <c r="AE22" s="46"/>
     </row>
     <row r="23">
-      <c r="A23" s="17"/>
-      <c r="B23" s="65"/>
-      <c r="G23" s="17"/>
-      <c r="M23" s="32"/>
-      <c r="N23" s="56" t="s">
-        <v>73</v>
-      </c>
-      <c r="O23" s="43"/>
-      <c r="P23" s="43"/>
-      <c r="Q23" s="43"/>
-      <c r="R23" s="43"/>
-      <c r="S23" s="43"/>
-      <c r="T23" s="43"/>
-      <c r="U23" s="43"/>
-      <c r="V23" s="43"/>
-      <c r="W23" s="43"/>
-      <c r="X23" s="43"/>
-      <c r="Y23" s="43"/>
-      <c r="Z23" s="43"/>
-      <c r="AA23" s="43"/>
-      <c r="AB23" s="43"/>
-      <c r="AC23" s="66"/>
-      <c r="AD23" s="43"/>
-      <c r="AE23" s="67"/>
+      <c r="A23" s="18"/>
+      <c r="B23" s="78"/>
+      <c r="G23" s="18"/>
+      <c r="I23" s="32"/>
+      <c r="J23" s="32"/>
+      <c r="K23" s="32"/>
+      <c r="M23" s="48"/>
+      <c r="N23" s="69" t="s">
+        <v>123</v>
+      </c>
+      <c r="O23" s="54"/>
+      <c r="P23" s="54"/>
+      <c r="Q23" s="54"/>
+      <c r="R23" s="54"/>
+      <c r="S23" s="54"/>
+      <c r="T23" s="54"/>
+      <c r="U23" s="54"/>
+      <c r="V23" s="54"/>
+      <c r="W23" s="54"/>
+      <c r="X23" s="54"/>
+      <c r="Y23" s="54"/>
+      <c r="Z23" s="54"/>
+      <c r="AA23" s="54"/>
+      <c r="AB23" s="54"/>
+      <c r="AC23" s="79"/>
+      <c r="AD23" s="54"/>
+      <c r="AE23" s="80"/>
     </row>
     <row r="24">
-      <c r="A24" s="17"/>
-      <c r="B24" s="65"/>
-      <c r="G24" s="17"/>
-      <c r="M24" s="32"/>
+      <c r="A24" s="18"/>
+      <c r="B24" s="78"/>
+      <c r="G24" s="18"/>
+      <c r="I24" s="32"/>
+      <c r="J24" s="32"/>
+      <c r="K24" s="32"/>
+      <c r="M24" s="48"/>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
       <c r="P24" s="14"/>
@@ -3199,66 +3705,71 @@
       <c r="AA24" s="14"/>
       <c r="AB24" s="14"/>
       <c r="AC24" s="14"/>
-      <c r="AD24" s="23"/>
-      <c r="AE24" s="67"/>
+      <c r="AD24" s="28"/>
+      <c r="AE24" s="80"/>
     </row>
     <row r="25">
-      <c r="A25" s="17"/>
-      <c r="B25" s="65"/>
-      <c r="G25" s="17"/>
-      <c r="K25" s="68"/>
-      <c r="M25" s="69"/>
-      <c r="N25" s="62"/>
-      <c r="O25" s="62"/>
-      <c r="P25" s="62"/>
-      <c r="Q25" s="62"/>
-      <c r="R25" s="62"/>
-      <c r="S25" s="62"/>
-      <c r="T25" s="62"/>
-      <c r="U25" s="62"/>
-      <c r="V25" s="62"/>
-      <c r="W25" s="62"/>
-      <c r="X25" s="62"/>
-      <c r="Y25" s="62"/>
-      <c r="Z25" s="62"/>
-      <c r="AA25" s="62"/>
-      <c r="AB25" s="62"/>
-      <c r="AC25" s="62"/>
-      <c r="AD25" s="70"/>
-      <c r="AE25" s="71"/>
+      <c r="A25" s="18"/>
+      <c r="B25" s="78"/>
+      <c r="G25" s="18"/>
+      <c r="I25" s="32"/>
+      <c r="J25" s="32"/>
+      <c r="K25" s="32"/>
+      <c r="M25" s="81"/>
+      <c r="N25" s="75"/>
+      <c r="O25" s="75"/>
+      <c r="P25" s="75"/>
+      <c r="Q25" s="75"/>
+      <c r="R25" s="75"/>
+      <c r="S25" s="75"/>
+      <c r="T25" s="75"/>
+      <c r="U25" s="75"/>
+      <c r="V25" s="75"/>
+      <c r="W25" s="75"/>
+      <c r="X25" s="75"/>
+      <c r="Y25" s="75"/>
+      <c r="Z25" s="75"/>
+      <c r="AA25" s="75"/>
+      <c r="AB25" s="75"/>
+      <c r="AC25" s="75"/>
+      <c r="AD25" s="82"/>
+      <c r="AE25" s="83"/>
     </row>
     <row r="26">
-      <c r="A26" s="17"/>
-      <c r="B26" s="65"/>
-      <c r="G26" s="17"/>
+      <c r="A26" s="18"/>
+      <c r="B26" s="78"/>
+      <c r="G26" s="18"/>
+      <c r="I26" s="32"/>
+      <c r="J26" s="32"/>
+      <c r="K26" s="32"/>
     </row>
     <row r="27">
-      <c r="B27" s="65"/>
-      <c r="G27" s="17"/>
+      <c r="B27" s="78"/>
+      <c r="G27" s="18"/>
     </row>
     <row r="28">
-      <c r="A28" s="17"/>
-      <c r="B28" s="65"/>
-      <c r="G28" s="17"/>
+      <c r="A28" s="18"/>
+      <c r="B28" s="78"/>
+      <c r="G28" s="18"/>
       <c r="J28" s="14"/>
-      <c r="K28" s="38"/>
-      <c r="L28" s="38"/>
-      <c r="M28" s="38"/>
-      <c r="N28" s="38"/>
-      <c r="O28" s="38"/>
-      <c r="P28" s="38"/>
-      <c r="Q28" s="38"/>
-      <c r="R28" s="38"/>
-      <c r="S28" s="38"/>
+      <c r="K28" s="49"/>
+      <c r="L28" s="49"/>
+      <c r="M28" s="49"/>
+      <c r="N28" s="49"/>
+      <c r="O28" s="49"/>
+      <c r="P28" s="49"/>
+      <c r="Q28" s="49"/>
+      <c r="R28" s="49"/>
+      <c r="S28" s="49"/>
     </row>
     <row r="29">
-      <c r="F29" s="72" t="s">
-        <v>74</v>
-      </c>
-      <c r="G29" s="73"/>
-      <c r="H29" s="73"/>
-      <c r="I29" s="73"/>
-      <c r="J29" s="52"/>
+      <c r="F29" s="84" t="s">
+        <v>124</v>
+      </c>
+      <c r="G29" s="85"/>
+      <c r="H29" s="85"/>
+      <c r="I29" s="85"/>
+      <c r="J29" s="66"/>
       <c r="K29" s="14"/>
       <c r="L29" s="14"/>
       <c r="M29" s="14"/>
@@ -3272,205 +3783,211 @@
       <c r="U29" s="14"/>
     </row>
     <row r="30">
-      <c r="A30" s="74"/>
-      <c r="B30" s="45"/>
-      <c r="C30" s="45"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="45"/>
-      <c r="F30" s="45"/>
-      <c r="G30" s="45"/>
-      <c r="H30" s="45"/>
-      <c r="I30" s="28"/>
-      <c r="J30" s="75"/>
-      <c r="K30" s="33"/>
+      <c r="A30" s="86"/>
+      <c r="B30" s="56"/>
+      <c r="C30" s="56"/>
+      <c r="D30" s="36"/>
+      <c r="E30" s="56"/>
+      <c r="F30" s="56"/>
+      <c r="G30" s="56"/>
+      <c r="H30" s="56"/>
+      <c r="I30" s="37"/>
+      <c r="J30" s="87"/>
+      <c r="K30" s="42"/>
       <c r="L30" s="14"/>
       <c r="M30" s="14"/>
       <c r="N30" s="14"/>
-      <c r="O30" s="76"/>
-      <c r="P30" s="34"/>
-      <c r="Q30" s="34"/>
-      <c r="R30" s="34"/>
-      <c r="S30" s="34"/>
-      <c r="T30" s="34"/>
-      <c r="U30" s="34"/>
+      <c r="O30" s="88"/>
+      <c r="P30" s="43"/>
+      <c r="Q30" s="43"/>
+      <c r="R30" s="43"/>
+      <c r="S30" s="43"/>
+      <c r="T30" s="43"/>
+      <c r="U30" s="43"/>
     </row>
     <row r="31">
-      <c r="A31" s="77" t="s">
-        <v>75</v>
-      </c>
-      <c r="B31" s="78"/>
-      <c r="E31" s="77" t="s">
-        <v>76</v>
-      </c>
-      <c r="F31" s="78"/>
-      <c r="I31" s="48"/>
-      <c r="J31" s="75"/>
+      <c r="A31" s="89" t="s">
+        <v>125</v>
+      </c>
+      <c r="B31" s="90">
+        <v>0.0</v>
+      </c>
+      <c r="C31" s="28"/>
+      <c r="E31" s="89" t="s">
+        <v>126</v>
+      </c>
+      <c r="F31" s="90">
+        <v>1.0</v>
+      </c>
+      <c r="I31" s="59"/>
+      <c r="J31" s="87"/>
       <c r="K31" s="14"/>
       <c r="L31" s="14"/>
       <c r="M31" s="14"/>
       <c r="N31" s="14"/>
-      <c r="O31" s="76"/>
-      <c r="P31" s="34"/>
-      <c r="Q31" s="34"/>
-      <c r="R31" s="34"/>
-      <c r="S31" s="34"/>
-      <c r="T31" s="34"/>
-      <c r="U31" s="34"/>
+      <c r="O31" s="88"/>
+      <c r="P31" s="43"/>
+      <c r="Q31" s="43"/>
+      <c r="R31" s="43"/>
+      <c r="S31" s="43"/>
+      <c r="T31" s="43"/>
+      <c r="U31" s="43"/>
     </row>
     <row r="32">
-      <c r="A32" s="46"/>
-      <c r="B32" s="23"/>
-      <c r="C32" s="23"/>
+      <c r="A32" s="57"/>
+      <c r="B32" s="28"/>
       <c r="D32" s="14"/>
-      <c r="E32" s="23"/>
-      <c r="F32" s="23"/>
-      <c r="I32" s="48"/>
-      <c r="J32" s="55"/>
-      <c r="K32" s="23"/>
-      <c r="L32" s="23"/>
-      <c r="M32" s="23"/>
-      <c r="N32" s="23"/>
-      <c r="O32" s="79"/>
-      <c r="P32" s="23"/>
-      <c r="Q32" s="23"/>
-      <c r="S32" s="23"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="I32" s="59"/>
+      <c r="J32" s="41"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+      <c r="M32" s="28"/>
+      <c r="N32" s="28"/>
+      <c r="O32" s="91"/>
+      <c r="P32" s="28"/>
+      <c r="Q32" s="28"/>
+      <c r="S32" s="28"/>
     </row>
     <row r="33">
-      <c r="A33" s="32"/>
+      <c r="A33" s="48"/>
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
       <c r="D33" s="14"/>
       <c r="E33" s="14"/>
       <c r="F33" s="14"/>
-      <c r="I33" s="48"/>
-      <c r="J33" s="55"/>
+      <c r="I33" s="59"/>
+      <c r="J33" s="41"/>
       <c r="K33" s="14"/>
       <c r="L33" s="14"/>
       <c r="M33" s="14"/>
       <c r="N33" s="14"/>
-      <c r="O33" s="33"/>
+      <c r="O33" s="42"/>
       <c r="P33" s="14"/>
       <c r="Q33" s="14"/>
       <c r="R33" s="14"/>
       <c r="S33" s="14"/>
     </row>
     <row r="34">
-      <c r="A34" s="32"/>
+      <c r="A34" s="48"/>
       <c r="B34" s="14"/>
       <c r="C34" s="14"/>
       <c r="D34" s="14"/>
       <c r="E34" s="14"/>
-      <c r="F34" s="52"/>
-      <c r="G34" s="80" t="s">
+      <c r="F34" s="66"/>
+      <c r="G34" s="92" t="s">
+        <v>127</v>
+      </c>
+      <c r="H34" s="93" t="s">
+        <v>73</v>
+      </c>
+      <c r="I34" s="59"/>
+      <c r="O34" s="18"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="48"/>
+      <c r="B35" s="94" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35" s="14"/>
+      <c r="D35" s="94" t="s">
         <v>77</v>
       </c>
-      <c r="H34" s="81"/>
-      <c r="I34" s="48"/>
-      <c r="O34" s="17"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="32"/>
-      <c r="B35" s="82" t="s">
-        <v>21</v>
-      </c>
-      <c r="C35" s="14"/>
-      <c r="D35" s="82" t="s">
-        <v>78</v>
-      </c>
-      <c r="E35" s="33"/>
-      <c r="F35" s="83"/>
-      <c r="G35" s="84" t="s">
-        <v>79</v>
-      </c>
-      <c r="H35" s="85"/>
-      <c r="I35" s="48"/>
-      <c r="O35" s="17"/>
+      <c r="E35" s="42"/>
+      <c r="F35" s="95"/>
+      <c r="G35" s="96" t="s">
+        <v>128</v>
+      </c>
+      <c r="H35" s="97"/>
+      <c r="I35" s="59"/>
+      <c r="O35" s="18"/>
     </row>
     <row r="36">
-      <c r="A36" s="32"/>
+      <c r="A36" s="48"/>
       <c r="B36" s="14"/>
       <c r="C36" s="14"/>
       <c r="D36" s="14"/>
-      <c r="E36" s="82" t="s">
-        <v>80</v>
+      <c r="E36" s="94" t="s">
+        <v>129</v>
       </c>
       <c r="F36" s="14"/>
-      <c r="I36" s="48"/>
-      <c r="O36" s="17"/>
+      <c r="I36" s="59"/>
+      <c r="O36" s="18"/>
     </row>
     <row r="37">
-      <c r="A37" s="32"/>
+      <c r="A37" s="48"/>
       <c r="B37" s="14"/>
       <c r="C37" s="14"/>
       <c r="D37" s="14"/>
       <c r="E37" s="14"/>
       <c r="F37" s="14"/>
-      <c r="G37" s="86" t="s">
-        <v>81</v>
-      </c>
-      <c r="H37" s="87"/>
-      <c r="I37" s="88"/>
-      <c r="K37" s="38"/>
+      <c r="G37" s="98" t="s">
+        <v>130</v>
+      </c>
+      <c r="H37" s="99"/>
+      <c r="I37" s="100"/>
+      <c r="K37" s="49"/>
       <c r="L37" s="14"/>
-      <c r="O37" s="17"/>
+      <c r="O37" s="18"/>
     </row>
     <row r="38">
-      <c r="A38" s="32"/>
+      <c r="A38" s="48"/>
       <c r="B38" s="14"/>
       <c r="C38" s="14"/>
       <c r="D38" s="14"/>
       <c r="E38" s="14"/>
       <c r="F38" s="14"/>
-      <c r="G38" s="78" t="s">
-        <v>82</v>
-      </c>
-      <c r="H38" s="78" t="s">
-        <v>83</v>
-      </c>
-      <c r="I38" s="78" t="s">
-        <v>84</v>
-      </c>
-      <c r="L38" s="55"/>
-      <c r="O38" s="17"/>
+      <c r="G38" s="90" t="s">
+        <v>131</v>
+      </c>
+      <c r="H38" s="90" t="s">
+        <v>132</v>
+      </c>
+      <c r="I38" s="90" t="s">
+        <v>133</v>
+      </c>
+      <c r="L38" s="41"/>
+      <c r="O38" s="18"/>
     </row>
     <row r="39">
-      <c r="A39" s="32"/>
+      <c r="A39" s="48"/>
       <c r="B39" s="14"/>
       <c r="C39" s="14"/>
       <c r="D39" s="14"/>
       <c r="E39" s="14"/>
       <c r="F39" s="14"/>
-      <c r="G39" s="89">
-        <v>0.0</v>
-      </c>
-      <c r="H39" s="89">
-        <v>0.0</v>
-      </c>
-      <c r="I39" s="89">
-        <v>0.0</v>
-      </c>
-      <c r="L39" s="55"/>
-      <c r="O39" s="17"/>
+      <c r="G39" s="101">
+        <v>0.0</v>
+      </c>
+      <c r="H39" s="101">
+        <v>0.0</v>
+      </c>
+      <c r="I39" s="101">
+        <v>0.0</v>
+      </c>
+      <c r="L39" s="41"/>
+      <c r="O39" s="18"/>
     </row>
     <row r="40">
-      <c r="A40" s="32"/>
+      <c r="A40" s="48"/>
       <c r="B40" s="14"/>
-      <c r="C40" s="82" t="s">
-        <v>78</v>
+      <c r="C40" s="94" t="s">
+        <v>77</v>
       </c>
       <c r="D40" s="14"/>
       <c r="E40" s="14"/>
       <c r="F40" s="14"/>
       <c r="G40" s="14"/>
-      <c r="H40" s="52"/>
-      <c r="I40" s="90"/>
-      <c r="J40" s="91"/>
-      <c r="K40" s="92"/>
-      <c r="L40" s="55"/>
-      <c r="O40" s="17"/>
+      <c r="H40" s="66"/>
+      <c r="I40" s="102"/>
+      <c r="J40" s="103"/>
+      <c r="K40" s="104"/>
+      <c r="L40" s="41"/>
+      <c r="O40" s="18"/>
     </row>
     <row r="41">
-      <c r="A41" s="32"/>
+      <c r="A41" s="48"/>
       <c r="B41" s="14"/>
       <c r="C41" s="14"/>
       <c r="D41" s="14"/>
@@ -3478,14 +3995,14 @@
       <c r="F41" s="14"/>
       <c r="G41" s="14"/>
       <c r="H41" s="14"/>
-      <c r="I41" s="93"/>
-      <c r="J41" s="94"/>
-      <c r="K41" s="23"/>
+      <c r="I41" s="105"/>
+      <c r="J41" s="106"/>
+      <c r="K41" s="28"/>
       <c r="L41" s="14"/>
-      <c r="O41" s="17"/>
+      <c r="O41" s="18"/>
     </row>
     <row r="42">
-      <c r="A42" s="32"/>
+      <c r="A42" s="48"/>
       <c r="B42" s="14"/>
       <c r="C42" s="14"/>
       <c r="D42" s="14"/>
@@ -3493,14 +4010,14 @@
       <c r="F42" s="14"/>
       <c r="G42" s="14"/>
       <c r="H42" s="14"/>
-      <c r="I42" s="37"/>
-      <c r="J42" s="55"/>
+      <c r="I42" s="46"/>
+      <c r="J42" s="41"/>
       <c r="K42" s="14"/>
       <c r="L42" s="14"/>
-      <c r="O42" s="17"/>
+      <c r="O42" s="18"/>
     </row>
     <row r="43">
-      <c r="A43" s="32"/>
+      <c r="A43" s="48"/>
       <c r="B43" s="14"/>
       <c r="C43" s="14"/>
       <c r="D43" s="14"/>
@@ -3508,49 +4025,51 @@
       <c r="F43" s="14"/>
       <c r="G43" s="14"/>
       <c r="H43" s="14"/>
-      <c r="I43" s="37"/>
-      <c r="J43" s="55"/>
+      <c r="I43" s="46"/>
+      <c r="J43" s="41"/>
       <c r="K43" s="14"/>
       <c r="L43" s="14"/>
-      <c r="O43" s="17"/>
+      <c r="O43" s="18"/>
     </row>
     <row r="44">
-      <c r="A44" s="32"/>
+      <c r="A44" s="48"/>
       <c r="B44" s="14"/>
-      <c r="C44" s="38"/>
-      <c r="D44" s="38"/>
+      <c r="C44" s="49"/>
+      <c r="D44" s="49"/>
       <c r="E44" s="14"/>
       <c r="F44" s="14"/>
       <c r="G44" s="14"/>
       <c r="H44" s="14"/>
-      <c r="I44" s="37"/>
-      <c r="J44" s="55"/>
+      <c r="I44" s="46"/>
+      <c r="J44" s="41"/>
       <c r="K44" s="14"/>
       <c r="L44" s="14"/>
-      <c r="O44" s="17"/>
+      <c r="O44" s="18"/>
     </row>
     <row r="45">
-      <c r="A45" s="69"/>
-      <c r="B45" s="95"/>
-      <c r="C45" s="77" t="s">
-        <v>85</v>
-      </c>
-      <c r="D45" s="96"/>
-      <c r="E45" s="97"/>
-      <c r="F45" s="70"/>
-      <c r="G45" s="62"/>
-      <c r="H45" s="62"/>
-      <c r="I45" s="63"/>
-      <c r="O45" s="17"/>
+      <c r="A45" s="81"/>
+      <c r="B45" s="107"/>
+      <c r="C45" s="89" t="s">
+        <v>134</v>
+      </c>
+      <c r="D45" s="108">
+        <v>1.0</v>
+      </c>
+      <c r="E45" s="109"/>
+      <c r="F45" s="82"/>
+      <c r="G45" s="75"/>
+      <c r="H45" s="75"/>
+      <c r="I45" s="76"/>
+      <c r="O45" s="18"/>
     </row>
     <row r="46">
-      <c r="A46" s="23"/>
-      <c r="B46" s="23"/>
-      <c r="C46" s="23"/>
-      <c r="D46" s="23"/>
-      <c r="E46" s="23"/>
-      <c r="F46" s="23"/>
-      <c r="O46" s="65"/>
+      <c r="A46" s="28"/>
+      <c r="B46" s="28"/>
+      <c r="C46" s="28"/>
+      <c r="D46" s="28"/>
+      <c r="E46" s="28"/>
+      <c r="F46" s="28"/>
+      <c r="O46" s="78"/>
     </row>
     <row r="47">
       <c r="A47" s="14"/>
@@ -3559,157 +4078,156 @@
       <c r="D47" s="14"/>
       <c r="E47" s="14"/>
       <c r="F47" s="14"/>
-      <c r="O47" s="65"/>
+      <c r="O47" s="78"/>
     </row>
     <row r="48">
-      <c r="O48" s="65"/>
+      <c r="O48" s="78"/>
     </row>
     <row r="49">
-      <c r="O49" s="65"/>
+      <c r="O49" s="78"/>
     </row>
     <row r="50">
-      <c r="O50" s="65"/>
+      <c r="O50" s="78"/>
     </row>
     <row r="51">
-      <c r="O51" s="65"/>
+      <c r="O51" s="78"/>
     </row>
     <row r="52">
-      <c r="O52" s="65"/>
+      <c r="O52" s="78"/>
     </row>
     <row r="53">
-      <c r="O53" s="65"/>
+      <c r="O53" s="78"/>
     </row>
     <row r="54">
-      <c r="A54" s="7"/>
-      <c r="O54" s="65"/>
+      <c r="A54" s="9"/>
+      <c r="O54" s="78"/>
     </row>
     <row r="55">
-      <c r="A55" s="7"/>
-      <c r="O55" s="65"/>
+      <c r="A55" s="9"/>
+      <c r="O55" s="78"/>
     </row>
     <row r="56">
-      <c r="O56" s="65"/>
+      <c r="O56" s="78"/>
     </row>
     <row r="57">
-      <c r="O57" s="65"/>
+      <c r="O57" s="78"/>
     </row>
     <row r="58">
-      <c r="O58" s="65"/>
+      <c r="O58" s="78"/>
     </row>
     <row r="59">
-      <c r="O59" s="65"/>
+      <c r="O59" s="78"/>
     </row>
     <row r="60">
-      <c r="O60" s="65"/>
+      <c r="O60" s="78"/>
     </row>
     <row r="61">
-      <c r="O61" s="65"/>
+      <c r="O61" s="78"/>
     </row>
     <row r="62">
-      <c r="O62" s="65"/>
+      <c r="O62" s="78"/>
     </row>
     <row r="63">
-      <c r="O63" s="65"/>
+      <c r="O63" s="78"/>
     </row>
     <row r="64">
-      <c r="O64" s="65"/>
+      <c r="O64" s="78"/>
     </row>
     <row r="65">
-      <c r="O65" s="65"/>
+      <c r="O65" s="78"/>
     </row>
     <row r="66">
-      <c r="O66" s="65"/>
+      <c r="O66" s="78"/>
     </row>
     <row r="67">
-      <c r="O67" s="65"/>
+      <c r="O67" s="78"/>
     </row>
     <row r="68">
-      <c r="O68" s="65"/>
+      <c r="O68" s="78"/>
     </row>
     <row r="69">
-      <c r="O69" s="65"/>
+      <c r="O69" s="78"/>
     </row>
     <row r="70">
-      <c r="O70" s="65"/>
+      <c r="O70" s="78"/>
     </row>
     <row r="71">
-      <c r="O71" s="65"/>
+      <c r="O71" s="78"/>
     </row>
     <row r="72">
-      <c r="O72" s="65"/>
+      <c r="O72" s="78"/>
     </row>
     <row r="73">
-      <c r="O73" s="65"/>
+      <c r="O73" s="78"/>
     </row>
     <row r="74">
-      <c r="O74" s="65"/>
+      <c r="O74" s="78"/>
     </row>
     <row r="75">
-      <c r="O75" s="65"/>
+      <c r="O75" s="78"/>
     </row>
     <row r="76">
-      <c r="O76" s="65"/>
+      <c r="O76" s="78"/>
     </row>
     <row r="77">
-      <c r="O77" s="65"/>
+      <c r="O77" s="78"/>
     </row>
     <row r="78">
-      <c r="O78" s="65"/>
+      <c r="O78" s="78"/>
     </row>
     <row r="79">
-      <c r="O79" s="65"/>
+      <c r="O79" s="78"/>
     </row>
     <row r="80">
-      <c r="O80" s="65"/>
+      <c r="O80" s="78"/>
     </row>
     <row r="81">
-      <c r="O81" s="65"/>
+      <c r="O81" s="78"/>
     </row>
     <row r="82">
-      <c r="O82" s="65"/>
+      <c r="O82" s="78"/>
     </row>
     <row r="83">
-      <c r="O83" s="65"/>
+      <c r="O83" s="78"/>
     </row>
     <row r="84">
-      <c r="O84" s="65"/>
+      <c r="O84" s="78"/>
     </row>
     <row r="85">
-      <c r="O85" s="65"/>
+      <c r="O85" s="78"/>
     </row>
     <row r="86">
-      <c r="O86" s="65"/>
+      <c r="O86" s="78"/>
     </row>
     <row r="87">
-      <c r="O87" s="65"/>
+      <c r="O87" s="78"/>
     </row>
     <row r="88">
-      <c r="O88" s="65"/>
+      <c r="O88" s="78"/>
     </row>
     <row r="89">
-      <c r="O89" s="65"/>
+      <c r="O89" s="78"/>
     </row>
     <row r="90">
-      <c r="O90" s="65"/>
+      <c r="O90" s="78"/>
     </row>
     <row r="91">
-      <c r="O91" s="65"/>
+      <c r="O91" s="78"/>
     </row>
     <row r="92">
-      <c r="O92" s="65"/>
+      <c r="O92" s="78"/>
     </row>
     <row r="93">
-      <c r="O93" s="65"/>
+      <c r="O93" s="78"/>
     </row>
     <row r="94">
-      <c r="O94" s="65"/>
+      <c r="O94" s="78"/>
     </row>
     <row r="95">
-      <c r="O95" s="65"/>
+      <c r="O95" s="78"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="E2:L5"/>
+  <mergeCells count="1">
     <mergeCell ref="H34:H35"/>
   </mergeCells>
   <printOptions gridLines="1" horizontalCentered="1"/>
@@ -3743,1148 +4261,1792 @@
         <v>3</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8">
+        <v>0.9866550925925925</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O2" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="P2" s="10">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8">
+        <v>0.9871296296296296</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="N3" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O3" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="P3" s="10">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8">
+        <v>0.9881365740740741</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="2" t="s">
+      <c r="H4" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="N4" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O4" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="P4" s="10">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8">
+        <v>0.9881828703703703</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="N5" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O5" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="P5" s="10">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8">
+        <v>0.9881944444444445</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O6" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="P6" s="10">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8">
+        <v>0.9882638888888889</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G7" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O7" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="P7" s="10">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8">
+        <v>0.988275462962963</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G8" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="H8" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O8" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="P8" s="10">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8">
+        <v>0.9883449074074074</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="H9" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O9" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="P9" s="10">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8">
+        <v>0.9883796296296297</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6">
-        <v>0.7467939814814815</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="N2" s="8">
-        <v>0.0</v>
-      </c>
-      <c r="O2" s="8">
-        <v>0.0</v>
-      </c>
-      <c r="P2" s="8">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="6"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="8"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="6"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="N5" s="8"/>
-      <c r="O5" s="8"/>
-      <c r="P5" s="8"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="6"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="8"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="6"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="6"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="6"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
-      <c r="P9" s="8"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="6"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="8"/>
-      <c r="P10" s="8"/>
+      <c r="H10" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O10" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="P10" s="10">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="6"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="8"/>
-      <c r="O11" s="8"/>
-      <c r="P11" s="8"/>
+      <c r="A11" s="8">
+        <v>0.9884375</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="H11" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O11" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="P11" s="10">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="6"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="8"/>
+      <c r="A12" s="8">
+        <v>0.9884722222222222</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O12" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="P12" s="10">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="6"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="8"/>
-      <c r="O13" s="8"/>
-      <c r="P13" s="8"/>
+      <c r="A13" s="8">
+        <v>0.9885416666666667</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="H13" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="I13" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O13" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="P13" s="10">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="6"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="8"/>
-      <c r="O14" s="8"/>
-      <c r="P14" s="8"/>
+      <c r="A14" s="8">
+        <v>0.9885879629629629</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G14" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="H14" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="I14" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O14" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="P14" s="10">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="6"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="8"/>
-      <c r="O15" s="8"/>
-      <c r="P15" s="8"/>
+      <c r="A15" s="8">
+        <v>0.9886342592592593</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="G15" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="H15" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="I15" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O15" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="P15" s="10">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="6"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="8"/>
-      <c r="O16" s="8"/>
-      <c r="P16" s="8"/>
+      <c r="A16" s="8">
+        <v>0.9886805555555556</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="H16" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="I16" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O16" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="P16" s="10">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="6"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="8"/>
-      <c r="O17" s="8"/>
-      <c r="P17" s="8"/>
+      <c r="A17" s="8">
+        <v>0.988738425925926</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="H17" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="I17" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O17" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="P17" s="10">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="6"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="8"/>
-      <c r="O18" s="8"/>
-      <c r="P18" s="8"/>
+      <c r="A18" s="8">
+        <v>0.9888541666666667</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="H18" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="I18" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O18" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="P18" s="10">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="6"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="7"/>
-      <c r="N19" s="8"/>
-      <c r="O19" s="8"/>
-      <c r="P19" s="8"/>
+      <c r="A19" s="8">
+        <v>0.9889930555555555</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="I19" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="J19" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="K19" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="L19" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="M19" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="N19" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O19" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="P19" s="10">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="6"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7"/>
-      <c r="N20" s="8"/>
-      <c r="O20" s="8"/>
-      <c r="P20" s="8"/>
+      <c r="A20" s="8">
+        <v>0.9890509259259259</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="I20" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="J20" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="K20" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="L20" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="M20" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="N20" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O20" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="P20" s="10">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="6"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="7"/>
-      <c r="N21" s="8"/>
-      <c r="O21" s="8"/>
-      <c r="P21" s="8"/>
+      <c r="A21" s="8">
+        <v>0.9890972222222222</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="I21" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="J21" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="K21" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="L21" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="M21" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="N21" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O21" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="P21" s="10">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="6"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7"/>
-      <c r="N22" s="8"/>
-      <c r="O22" s="8"/>
-      <c r="P22" s="8"/>
+      <c r="A22" s="8">
+        <v>0.9891782407407408</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="H22" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="I22" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="J22" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="K22" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="L22" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="M22" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="N22" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O22" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="P22" s="10">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="6"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="7"/>
-      <c r="M23" s="7"/>
-      <c r="N23" s="8"/>
-      <c r="O23" s="8"/>
-      <c r="P23" s="8"/>
+      <c r="A23" s="8">
+        <v>0.989212962962963</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="H23" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="I23" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="J23" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="K23" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="L23" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="M23" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="N23" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O23" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="P23" s="10">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="6"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="8"/>
-      <c r="O24" s="8"/>
-      <c r="P24" s="8"/>
+      <c r="A24" s="8">
+        <v>0.9892824074074074</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="H24" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="I24" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="J24" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="K24" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="L24" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="M24" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="N24" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O24" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="P24" s="10">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="6"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="7"/>
-      <c r="M25" s="7"/>
-      <c r="N25" s="8"/>
-      <c r="O25" s="8"/>
-      <c r="P25" s="8"/>
+      <c r="A25" s="8">
+        <v>0.9893171296296296</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="H25" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="I25" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="J25" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="K25" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="L25" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="M25" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="N25" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O25" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="P25" s="10">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="6"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="7"/>
-      <c r="N26" s="8"/>
-      <c r="O26" s="8"/>
-      <c r="P26" s="8"/>
+      <c r="A26" s="8"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="10"/>
+      <c r="O26" s="10"/>
+      <c r="P26" s="10"/>
     </row>
     <row r="27">
-      <c r="A27" s="6"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="7"/>
-      <c r="M27" s="7"/>
-      <c r="N27" s="8"/>
-      <c r="O27" s="8"/>
-      <c r="P27" s="8"/>
+      <c r="A27" s="8"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
+      <c r="M27" s="9"/>
+      <c r="N27" s="10"/>
+      <c r="O27" s="10"/>
+      <c r="P27" s="10"/>
     </row>
     <row r="28">
-      <c r="A28" s="6"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7"/>
-      <c r="J28" s="7"/>
-      <c r="K28" s="7"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="7"/>
-      <c r="N28" s="8"/>
-      <c r="O28" s="8"/>
-      <c r="P28" s="8"/>
+      <c r="A28" s="8"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9"/>
+      <c r="M28" s="9"/>
+      <c r="N28" s="10"/>
+      <c r="O28" s="10"/>
+      <c r="P28" s="10"/>
     </row>
     <row r="29">
-      <c r="A29" s="6"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
-      <c r="L29" s="7"/>
-      <c r="M29" s="7"/>
-      <c r="N29" s="8"/>
-      <c r="O29" s="8"/>
-      <c r="P29" s="8"/>
+      <c r="A29" s="8"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="9"/>
+      <c r="M29" s="9"/>
+      <c r="N29" s="10"/>
+      <c r="O29" s="10"/>
+      <c r="P29" s="10"/>
     </row>
     <row r="30">
-      <c r="A30" s="6"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
-      <c r="I30" s="7"/>
-      <c r="J30" s="7"/>
-      <c r="K30" s="7"/>
-      <c r="L30" s="7"/>
-      <c r="M30" s="7"/>
-      <c r="N30" s="8"/>
-      <c r="O30" s="8"/>
-      <c r="P30" s="8"/>
+      <c r="A30" s="8"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
+      <c r="K30" s="9"/>
+      <c r="L30" s="9"/>
+      <c r="M30" s="9"/>
+      <c r="N30" s="10"/>
+      <c r="O30" s="10"/>
+      <c r="P30" s="10"/>
     </row>
     <row r="31">
-      <c r="A31" s="6"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
-      <c r="N31" s="8"/>
-      <c r="O31" s="8"/>
-      <c r="P31" s="8"/>
+      <c r="A31" s="8"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
+      <c r="K31" s="10"/>
+      <c r="L31" s="9"/>
+      <c r="M31" s="9"/>
+      <c r="N31" s="10"/>
+      <c r="O31" s="10"/>
+      <c r="P31" s="10"/>
     </row>
     <row r="32">
-      <c r="A32" s="6"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="H32" s="7"/>
-      <c r="I32" s="7"/>
-      <c r="N32" s="8"/>
-      <c r="O32" s="8"/>
-      <c r="P32" s="8"/>
+      <c r="A32" s="8"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="9"/>
+      <c r="K32" s="10"/>
+      <c r="L32" s="9"/>
+      <c r="M32" s="9"/>
+      <c r="N32" s="10"/>
+      <c r="O32" s="10"/>
+      <c r="P32" s="10"/>
     </row>
     <row r="33">
-      <c r="A33" s="6"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="H33" s="7"/>
-      <c r="I33" s="7"/>
-      <c r="N33" s="8"/>
-      <c r="O33" s="8"/>
-      <c r="P33" s="8"/>
+      <c r="A33" s="8"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="9"/>
+      <c r="K33" s="10"/>
+      <c r="L33" s="9"/>
+      <c r="M33" s="9"/>
+      <c r="N33" s="10"/>
+      <c r="O33" s="10"/>
+      <c r="P33" s="10"/>
     </row>
     <row r="34">
-      <c r="A34" s="6"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="H34" s="7"/>
-      <c r="I34" s="7"/>
-      <c r="N34" s="8"/>
-      <c r="O34" s="8"/>
-      <c r="P34" s="8"/>
+      <c r="A34" s="8"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="9"/>
+      <c r="K34" s="10"/>
+      <c r="L34" s="9"/>
+      <c r="M34" s="9"/>
+      <c r="N34" s="10"/>
+      <c r="O34" s="10"/>
+      <c r="P34" s="10"/>
     </row>
     <row r="35">
-      <c r="A35" s="6"/>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="H35" s="7"/>
-      <c r="I35" s="7"/>
-      <c r="N35" s="8"/>
-      <c r="O35" s="8"/>
-      <c r="P35" s="8"/>
+      <c r="A35" s="8"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
+      <c r="J35" s="9"/>
+      <c r="K35" s="10"/>
+      <c r="L35" s="9"/>
+      <c r="M35" s="9"/>
+      <c r="N35" s="10"/>
+      <c r="O35" s="10"/>
+      <c r="P35" s="10"/>
     </row>
     <row r="36">
-      <c r="A36" s="6"/>
-      <c r="B36" s="7"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="F36" s="7"/>
-      <c r="H36" s="7"/>
-      <c r="I36" s="7"/>
-      <c r="N36" s="8"/>
-      <c r="O36" s="8"/>
-      <c r="P36" s="8"/>
+      <c r="A36" s="8"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
+      <c r="I36" s="9"/>
+      <c r="J36" s="9"/>
+      <c r="K36" s="10"/>
+      <c r="L36" s="9"/>
+      <c r="M36" s="9"/>
+      <c r="N36" s="10"/>
+      <c r="O36" s="10"/>
+      <c r="P36" s="10"/>
     </row>
     <row r="37">
-      <c r="A37" s="6"/>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="H37" s="7"/>
-      <c r="I37" s="7"/>
-      <c r="N37" s="8"/>
-      <c r="O37" s="8"/>
-      <c r="P37" s="8"/>
+      <c r="A37" s="8"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+      <c r="N37" s="10"/>
+      <c r="O37" s="10"/>
+      <c r="P37" s="10"/>
     </row>
     <row r="38">
-      <c r="A38" s="6"/>
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="F38" s="7"/>
-      <c r="H38" s="7"/>
-      <c r="I38" s="7"/>
-      <c r="N38" s="8"/>
-      <c r="O38" s="8"/>
-      <c r="P38" s="8"/>
+      <c r="A38" s="8"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="F38" s="9"/>
+      <c r="H38" s="9"/>
+      <c r="I38" s="9"/>
+      <c r="N38" s="10"/>
+      <c r="O38" s="10"/>
+      <c r="P38" s="10"/>
     </row>
     <row r="39">
-      <c r="A39" s="6"/>
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="H39" s="7"/>
-      <c r="I39" s="7"/>
-      <c r="N39" s="8"/>
-      <c r="O39" s="8"/>
-      <c r="P39" s="8"/>
+      <c r="A39" s="8"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="F39" s="9"/>
+      <c r="H39" s="9"/>
+      <c r="I39" s="9"/>
+      <c r="N39" s="10"/>
+      <c r="O39" s="10"/>
+      <c r="P39" s="10"/>
     </row>
     <row r="40">
-      <c r="A40" s="6"/>
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="F40" s="7"/>
-      <c r="H40" s="7"/>
-      <c r="I40" s="7"/>
-      <c r="N40" s="8"/>
-      <c r="O40" s="8"/>
-      <c r="P40" s="8"/>
+      <c r="A40" s="8"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+      <c r="N40" s="10"/>
+      <c r="O40" s="10"/>
+      <c r="P40" s="10"/>
     </row>
     <row r="41">
-      <c r="A41" s="6"/>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="F41" s="7"/>
-      <c r="H41" s="7"/>
-      <c r="I41" s="7"/>
-      <c r="N41" s="8"/>
-      <c r="O41" s="8"/>
-      <c r="P41" s="8"/>
+      <c r="A41" s="8"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="F41" s="9"/>
+      <c r="H41" s="9"/>
+      <c r="I41" s="9"/>
+      <c r="N41" s="10"/>
+      <c r="O41" s="10"/>
+      <c r="P41" s="10"/>
     </row>
     <row r="42">
-      <c r="A42" s="6"/>
-      <c r="B42" s="7"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
-      <c r="F42" s="7"/>
-      <c r="H42" s="7"/>
-      <c r="I42" s="7"/>
-      <c r="N42" s="8"/>
-      <c r="O42" s="8"/>
-      <c r="P42" s="8"/>
+      <c r="A42" s="8"/>
+      <c r="B42" s="9"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="F42" s="9"/>
+      <c r="H42" s="9"/>
+      <c r="I42" s="9"/>
+      <c r="N42" s="10"/>
+      <c r="O42" s="10"/>
+      <c r="P42" s="10"/>
     </row>
     <row r="43">
-      <c r="A43" s="6"/>
-      <c r="B43" s="7"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
-      <c r="F43" s="7"/>
-      <c r="H43" s="7"/>
-      <c r="I43" s="7"/>
-      <c r="N43" s="8"/>
-      <c r="O43" s="8"/>
-      <c r="P43" s="8"/>
+      <c r="A43" s="8"/>
+      <c r="B43" s="9"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="F43" s="9"/>
+      <c r="H43" s="9"/>
+      <c r="I43" s="9"/>
+      <c r="N43" s="10"/>
+      <c r="O43" s="10"/>
+      <c r="P43" s="10"/>
     </row>
     <row r="44">
-      <c r="A44" s="6"/>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="F44" s="7"/>
-      <c r="H44" s="7"/>
-      <c r="I44" s="7"/>
-      <c r="N44" s="8"/>
-      <c r="O44" s="8"/>
-      <c r="P44" s="8"/>
+      <c r="A44" s="8"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+      <c r="F44" s="9"/>
+      <c r="H44" s="9"/>
+      <c r="I44" s="9"/>
+      <c r="N44" s="10"/>
+      <c r="O44" s="10"/>
+      <c r="P44" s="10"/>
     </row>
     <row r="45">
-      <c r="A45" s="6"/>
-      <c r="B45" s="7"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="7"/>
-      <c r="F45" s="7"/>
-      <c r="H45" s="7"/>
-      <c r="I45" s="7"/>
-      <c r="N45" s="8"/>
-      <c r="O45" s="8"/>
-      <c r="P45" s="8"/>
+      <c r="A45" s="8"/>
+      <c r="B45" s="9"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="F45" s="9"/>
+      <c r="H45" s="9"/>
+      <c r="I45" s="9"/>
+      <c r="N45" s="10"/>
+      <c r="O45" s="10"/>
+      <c r="P45" s="10"/>
     </row>
     <row r="46">
-      <c r="A46" s="6"/>
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="F46" s="7"/>
-      <c r="H46" s="7"/>
-      <c r="I46" s="7"/>
-      <c r="N46" s="8"/>
-      <c r="O46" s="8"/>
-      <c r="P46" s="8"/>
+      <c r="A46" s="8"/>
+      <c r="B46" s="9"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+      <c r="F46" s="9"/>
+      <c r="H46" s="9"/>
+      <c r="I46" s="9"/>
+      <c r="N46" s="10"/>
+      <c r="O46" s="10"/>
+      <c r="P46" s="10"/>
     </row>
     <row r="47">
-      <c r="A47" s="6"/>
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
-      <c r="F47" s="7"/>
-      <c r="H47" s="7"/>
-      <c r="I47" s="7"/>
-      <c r="N47" s="8"/>
-      <c r="O47" s="8"/>
-      <c r="P47" s="8"/>
+      <c r="A47" s="8"/>
+      <c r="B47" s="9"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="9"/>
+      <c r="F47" s="9"/>
+      <c r="H47" s="9"/>
+      <c r="I47" s="9"/>
+      <c r="N47" s="10"/>
+      <c r="O47" s="10"/>
+      <c r="P47" s="10"/>
     </row>
     <row r="48">
-      <c r="A48" s="6"/>
-      <c r="B48" s="7"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="F48" s="7"/>
-      <c r="H48" s="7"/>
-      <c r="I48" s="7"/>
-      <c r="N48" s="8"/>
-      <c r="O48" s="8"/>
-      <c r="P48" s="8"/>
+      <c r="A48" s="8"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="F48" s="9"/>
+      <c r="H48" s="9"/>
+      <c r="I48" s="9"/>
+      <c r="N48" s="10"/>
+      <c r="O48" s="10"/>
+      <c r="P48" s="10"/>
     </row>
     <row r="49">
-      <c r="A49" s="6"/>
-      <c r="B49" s="7"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="7"/>
-      <c r="F49" s="7"/>
-      <c r="H49" s="7"/>
-      <c r="I49" s="7"/>
-      <c r="N49" s="8"/>
-      <c r="O49" s="8"/>
-      <c r="P49" s="8"/>
+      <c r="A49" s="8"/>
+      <c r="B49" s="9"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="F49" s="9"/>
+      <c r="H49" s="9"/>
+      <c r="I49" s="9"/>
+      <c r="N49" s="10"/>
+      <c r="O49" s="10"/>
+      <c r="P49" s="10"/>
     </row>
     <row r="50">
-      <c r="A50" s="6"/>
-      <c r="B50" s="7"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
-      <c r="F50" s="7"/>
-      <c r="H50" s="7"/>
-      <c r="I50" s="7"/>
-      <c r="N50" s="8"/>
-      <c r="O50" s="8"/>
-      <c r="P50" s="8"/>
+      <c r="A50" s="8"/>
+      <c r="B50" s="9"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="9"/>
+      <c r="F50" s="9"/>
+      <c r="H50" s="9"/>
+      <c r="I50" s="9"/>
+      <c r="N50" s="10"/>
+      <c r="O50" s="10"/>
+      <c r="P50" s="10"/>
     </row>
     <row r="51">
-      <c r="A51" s="6"/>
-      <c r="B51" s="7"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
-      <c r="F51" s="7"/>
-      <c r="H51" s="7"/>
-      <c r="I51" s="7"/>
-      <c r="N51" s="8"/>
-      <c r="O51" s="8"/>
-      <c r="P51" s="8"/>
+      <c r="A51" s="8"/>
+      <c r="B51" s="9"/>
+      <c r="C51" s="9"/>
+      <c r="D51" s="9"/>
+      <c r="F51" s="9"/>
+      <c r="H51" s="9"/>
+      <c r="I51" s="9"/>
+      <c r="N51" s="10"/>
+      <c r="O51" s="10"/>
+      <c r="P51" s="10"/>
     </row>
     <row r="52">
-      <c r="A52" s="6"/>
-      <c r="B52" s="7"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
-      <c r="F52" s="7"/>
-      <c r="H52" s="7"/>
-      <c r="I52" s="7"/>
-      <c r="N52" s="8"/>
-      <c r="O52" s="8"/>
-      <c r="P52" s="8"/>
+      <c r="A52" s="8"/>
+      <c r="B52" s="9"/>
+      <c r="C52" s="9"/>
+      <c r="D52" s="9"/>
+      <c r="F52" s="9"/>
+      <c r="H52" s="9"/>
+      <c r="I52" s="9"/>
+      <c r="N52" s="10"/>
+      <c r="O52" s="10"/>
+      <c r="P52" s="10"/>
     </row>
     <row r="53">
-      <c r="A53" s="6"/>
-      <c r="B53" s="7"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="7"/>
-      <c r="F53" s="7"/>
-      <c r="H53" s="7"/>
-      <c r="I53" s="7"/>
-      <c r="N53" s="8"/>
-      <c r="O53" s="8"/>
-      <c r="P53" s="8"/>
+      <c r="A53" s="8"/>
+      <c r="B53" s="9"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="9"/>
+      <c r="F53" s="9"/>
+      <c r="H53" s="9"/>
+      <c r="I53" s="9"/>
+      <c r="N53" s="10"/>
+      <c r="O53" s="10"/>
+      <c r="P53" s="10"/>
     </row>
     <row r="54">
-      <c r="A54" s="6"/>
-      <c r="B54" s="7"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="F54" s="7"/>
-      <c r="H54" s="7"/>
-      <c r="I54" s="7"/>
-      <c r="N54" s="8"/>
-      <c r="O54" s="8"/>
-      <c r="P54" s="8"/>
+      <c r="A54" s="8"/>
+      <c r="B54" s="9"/>
+      <c r="C54" s="9"/>
+      <c r="D54" s="9"/>
+      <c r="F54" s="9"/>
+      <c r="H54" s="9"/>
+      <c r="I54" s="9"/>
+      <c r="N54" s="10"/>
+      <c r="O54" s="10"/>
+      <c r="P54" s="10"/>
     </row>
     <row r="55">
-      <c r="A55" s="6"/>
-      <c r="B55" s="7"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="7"/>
-      <c r="F55" s="7"/>
-      <c r="H55" s="7"/>
-      <c r="I55" s="7"/>
-      <c r="N55" s="8"/>
-      <c r="O55" s="8"/>
-      <c r="P55" s="8"/>
+      <c r="A55" s="8"/>
+      <c r="B55" s="9"/>
+      <c r="C55" s="9"/>
+      <c r="D55" s="9"/>
+      <c r="F55" s="9"/>
+      <c r="H55" s="9"/>
+      <c r="I55" s="9"/>
+      <c r="N55" s="10"/>
+      <c r="O55" s="10"/>
+      <c r="P55" s="10"/>
     </row>
     <row r="56">
-      <c r="A56" s="6"/>
-      <c r="B56" s="7"/>
-      <c r="C56" s="7"/>
-      <c r="D56" s="7"/>
-      <c r="E56" s="7"/>
-      <c r="F56" s="7"/>
-      <c r="H56" s="7"/>
-      <c r="I56" s="7"/>
-      <c r="N56" s="8"/>
-      <c r="O56" s="8"/>
-      <c r="P56" s="8"/>
+      <c r="A56" s="8"/>
+      <c r="B56" s="9"/>
+      <c r="C56" s="9"/>
+      <c r="D56" s="9"/>
+      <c r="E56" s="9"/>
+      <c r="F56" s="9"/>
+      <c r="H56" s="9"/>
+      <c r="I56" s="9"/>
+      <c r="N56" s="10"/>
+      <c r="O56" s="10"/>
+      <c r="P56" s="10"/>
     </row>
     <row r="57">
-      <c r="A57" s="6"/>
-      <c r="B57" s="7"/>
-      <c r="C57" s="7"/>
-      <c r="D57" s="7"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="7"/>
-      <c r="H57" s="7"/>
-      <c r="I57" s="7"/>
-      <c r="N57" s="8"/>
-      <c r="O57" s="8"/>
-      <c r="P57" s="8"/>
+      <c r="A57" s="8"/>
+      <c r="B57" s="9"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+      <c r="F57" s="9"/>
+      <c r="H57" s="9"/>
+      <c r="I57" s="9"/>
+      <c r="N57" s="10"/>
+      <c r="O57" s="10"/>
+      <c r="P57" s="10"/>
     </row>
     <row r="58">
-      <c r="A58" s="6"/>
-      <c r="B58" s="7"/>
-      <c r="C58" s="7"/>
-      <c r="D58" s="7"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="7"/>
-      <c r="H58" s="7"/>
-      <c r="I58" s="7"/>
-      <c r="N58" s="8"/>
-      <c r="O58" s="8"/>
-      <c r="P58" s="8"/>
+      <c r="A58" s="8"/>
+      <c r="B58" s="9"/>
+      <c r="C58" s="9"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="9"/>
+      <c r="F58" s="9"/>
+      <c r="H58" s="9"/>
+      <c r="I58" s="9"/>
+      <c r="N58" s="10"/>
+      <c r="O58" s="10"/>
+      <c r="P58" s="10"/>
     </row>
     <row r="59">
-      <c r="A59" s="6"/>
-      <c r="B59" s="7"/>
-      <c r="C59" s="7"/>
-      <c r="D59" s="7"/>
-      <c r="E59" s="7"/>
-      <c r="F59" s="7"/>
-      <c r="H59" s="7"/>
-      <c r="I59" s="7"/>
-      <c r="N59" s="8"/>
-      <c r="O59" s="8"/>
-      <c r="P59" s="8"/>
+      <c r="A59" s="8"/>
+      <c r="B59" s="9"/>
+      <c r="C59" s="9"/>
+      <c r="D59" s="9"/>
+      <c r="E59" s="9"/>
+      <c r="F59" s="9"/>
+      <c r="H59" s="9"/>
+      <c r="I59" s="9"/>
+      <c r="N59" s="10"/>
+      <c r="O59" s="10"/>
+      <c r="P59" s="10"/>
     </row>
     <row r="60">
-      <c r="A60" s="6"/>
-      <c r="B60" s="7"/>
-      <c r="C60" s="7"/>
-      <c r="D60" s="7"/>
-      <c r="E60" s="7"/>
-      <c r="F60" s="7"/>
-      <c r="H60" s="7"/>
-      <c r="I60" s="7"/>
-      <c r="N60" s="8"/>
-      <c r="O60" s="8"/>
-      <c r="P60" s="8"/>
+      <c r="A60" s="8"/>
+      <c r="B60" s="9"/>
+      <c r="C60" s="9"/>
+      <c r="D60" s="9"/>
+      <c r="E60" s="9"/>
+      <c r="F60" s="9"/>
+      <c r="H60" s="9"/>
+      <c r="I60" s="9"/>
+      <c r="N60" s="10"/>
+      <c r="O60" s="10"/>
+      <c r="P60" s="10"/>
     </row>
     <row r="61">
-      <c r="A61" s="6"/>
-      <c r="B61" s="7"/>
-      <c r="C61" s="7"/>
-      <c r="D61" s="7"/>
-      <c r="E61" s="7"/>
-      <c r="F61" s="7"/>
-      <c r="H61" s="7"/>
-      <c r="I61" s="7"/>
-      <c r="N61" s="8"/>
-      <c r="O61" s="8"/>
-      <c r="P61" s="8"/>
+      <c r="A61" s="8"/>
+      <c r="B61" s="9"/>
+      <c r="C61" s="9"/>
+      <c r="D61" s="9"/>
+      <c r="E61" s="9"/>
+      <c r="F61" s="9"/>
+      <c r="H61" s="9"/>
+      <c r="I61" s="9"/>
+      <c r="N61" s="10"/>
+      <c r="O61" s="10"/>
+      <c r="P61" s="10"/>
     </row>
     <row r="62">
-      <c r="A62" s="6"/>
-      <c r="B62" s="7"/>
-      <c r="C62" s="7"/>
-      <c r="D62" s="7"/>
-      <c r="E62" s="7"/>
-      <c r="F62" s="7"/>
-      <c r="H62" s="7"/>
-      <c r="I62" s="7"/>
-      <c r="N62" s="8"/>
-      <c r="O62" s="8"/>
-      <c r="P62" s="8"/>
+      <c r="A62" s="8"/>
+      <c r="B62" s="9"/>
+      <c r="C62" s="9"/>
+      <c r="D62" s="9"/>
+      <c r="E62" s="9"/>
+      <c r="F62" s="9"/>
+      <c r="H62" s="9"/>
+      <c r="I62" s="9"/>
+      <c r="N62" s="10"/>
+      <c r="O62" s="10"/>
+      <c r="P62" s="10"/>
     </row>
     <row r="63">
-      <c r="A63" s="6"/>
-      <c r="B63" s="7"/>
-      <c r="C63" s="7"/>
-      <c r="D63" s="7"/>
-      <c r="E63" s="7"/>
-      <c r="F63" s="7"/>
-      <c r="H63" s="7"/>
-      <c r="I63" s="7"/>
-      <c r="N63" s="8"/>
-      <c r="O63" s="8"/>
-      <c r="P63" s="8"/>
+      <c r="A63" s="8"/>
+      <c r="B63" s="9"/>
+      <c r="C63" s="9"/>
+      <c r="D63" s="9"/>
+      <c r="E63" s="9"/>
+      <c r="F63" s="9"/>
+      <c r="H63" s="9"/>
+      <c r="I63" s="9"/>
+      <c r="N63" s="10"/>
+      <c r="O63" s="10"/>
+      <c r="P63" s="10"/>
     </row>
     <row r="64">
-      <c r="A64" s="6"/>
-      <c r="B64" s="7"/>
-      <c r="C64" s="7"/>
-      <c r="D64" s="7"/>
-      <c r="E64" s="7"/>
-      <c r="F64" s="7"/>
-      <c r="G64" s="7"/>
-      <c r="H64" s="7"/>
-      <c r="I64" s="7"/>
-      <c r="N64" s="8"/>
-      <c r="O64" s="8"/>
-      <c r="P64" s="8"/>
+      <c r="A64" s="8"/>
+      <c r="B64" s="9"/>
+      <c r="C64" s="9"/>
+      <c r="D64" s="9"/>
+      <c r="E64" s="9"/>
+      <c r="F64" s="9"/>
+      <c r="G64" s="9"/>
+      <c r="H64" s="9"/>
+      <c r="I64" s="9"/>
+      <c r="N64" s="10"/>
+      <c r="O64" s="10"/>
+      <c r="P64" s="10"/>
     </row>
     <row r="65">
-      <c r="A65" s="6"/>
-      <c r="B65" s="7"/>
-      <c r="C65" s="7"/>
-      <c r="D65" s="7"/>
-      <c r="E65" s="7"/>
-      <c r="F65" s="7"/>
-      <c r="G65" s="7"/>
-      <c r="H65" s="7"/>
-      <c r="I65" s="7"/>
-      <c r="N65" s="8"/>
-      <c r="O65" s="8"/>
-      <c r="P65" s="8"/>
+      <c r="A65" s="8"/>
+      <c r="B65" s="9"/>
+      <c r="C65" s="9"/>
+      <c r="D65" s="9"/>
+      <c r="E65" s="9"/>
+      <c r="F65" s="9"/>
+      <c r="G65" s="9"/>
+      <c r="H65" s="9"/>
+      <c r="I65" s="9"/>
+      <c r="N65" s="10"/>
+      <c r="O65" s="10"/>
+      <c r="P65" s="10"/>
     </row>
     <row r="66">
-      <c r="A66" s="6"/>
-      <c r="B66" s="7"/>
-      <c r="C66" s="7"/>
-      <c r="D66" s="7"/>
-      <c r="E66" s="7"/>
-      <c r="F66" s="7"/>
-      <c r="G66" s="7"/>
-      <c r="H66" s="7"/>
-      <c r="I66" s="7"/>
-      <c r="N66" s="8"/>
-      <c r="O66" s="8"/>
-      <c r="P66" s="8"/>
+      <c r="A66" s="8"/>
+      <c r="B66" s="9"/>
+      <c r="C66" s="9"/>
+      <c r="D66" s="9"/>
+      <c r="E66" s="9"/>
+      <c r="F66" s="9"/>
+      <c r="G66" s="9"/>
+      <c r="H66" s="9"/>
+      <c r="I66" s="9"/>
+      <c r="N66" s="10"/>
+      <c r="O66" s="10"/>
+      <c r="P66" s="10"/>
     </row>
     <row r="67">
-      <c r="A67" s="6"/>
-      <c r="B67" s="7"/>
-      <c r="C67" s="7"/>
-      <c r="D67" s="7"/>
-      <c r="E67" s="7"/>
-      <c r="F67" s="7"/>
-      <c r="G67" s="7"/>
-      <c r="H67" s="7"/>
-      <c r="I67" s="7"/>
-      <c r="J67" s="7"/>
-      <c r="K67" s="7"/>
-      <c r="L67" s="7"/>
-      <c r="N67" s="8"/>
-      <c r="O67" s="8"/>
-      <c r="P67" s="8"/>
+      <c r="A67" s="8"/>
+      <c r="B67" s="9"/>
+      <c r="C67" s="9"/>
+      <c r="D67" s="9"/>
+      <c r="E67" s="9"/>
+      <c r="F67" s="9"/>
+      <c r="G67" s="9"/>
+      <c r="H67" s="9"/>
+      <c r="I67" s="9"/>
+      <c r="J67" s="9"/>
+      <c r="K67" s="9"/>
+      <c r="L67" s="9"/>
+      <c r="N67" s="10"/>
+      <c r="O67" s="10"/>
+      <c r="P67" s="10"/>
     </row>
     <row r="68">
-      <c r="A68" s="6"/>
-      <c r="B68" s="7"/>
-      <c r="C68" s="7"/>
-      <c r="D68" s="7"/>
-      <c r="E68" s="7"/>
-      <c r="F68" s="7"/>
-      <c r="G68" s="7"/>
-      <c r="H68" s="7"/>
-      <c r="I68" s="7"/>
-      <c r="J68" s="7"/>
-      <c r="K68" s="7"/>
-      <c r="L68" s="7"/>
-      <c r="N68" s="8"/>
-      <c r="O68" s="8"/>
-      <c r="P68" s="8"/>
+      <c r="A68" s="8"/>
+      <c r="B68" s="9"/>
+      <c r="C68" s="9"/>
+      <c r="D68" s="9"/>
+      <c r="E68" s="9"/>
+      <c r="F68" s="9"/>
+      <c r="G68" s="9"/>
+      <c r="H68" s="9"/>
+      <c r="I68" s="9"/>
+      <c r="J68" s="9"/>
+      <c r="K68" s="9"/>
+      <c r="L68" s="9"/>
+      <c r="N68" s="10"/>
+      <c r="O68" s="10"/>
+      <c r="P68" s="10"/>
     </row>
     <row r="69">
-      <c r="A69" s="6"/>
-      <c r="B69" s="7"/>
-      <c r="C69" s="7"/>
-      <c r="D69" s="7"/>
-      <c r="E69" s="7"/>
-      <c r="F69" s="7"/>
-      <c r="G69" s="7"/>
-      <c r="H69" s="7"/>
-      <c r="I69" s="7"/>
-      <c r="J69" s="7"/>
-      <c r="K69" s="7"/>
-      <c r="L69" s="7"/>
-      <c r="M69" s="7"/>
-      <c r="N69" s="8"/>
-      <c r="O69" s="8"/>
-      <c r="P69" s="8"/>
+      <c r="A69" s="8"/>
+      <c r="B69" s="9"/>
+      <c r="C69" s="9"/>
+      <c r="D69" s="9"/>
+      <c r="E69" s="9"/>
+      <c r="F69" s="9"/>
+      <c r="G69" s="9"/>
+      <c r="H69" s="9"/>
+      <c r="I69" s="9"/>
+      <c r="J69" s="9"/>
+      <c r="K69" s="9"/>
+      <c r="L69" s="9"/>
+      <c r="M69" s="9"/>
+      <c r="N69" s="10"/>
+      <c r="O69" s="10"/>
+      <c r="P69" s="10"/>
     </row>
     <row r="70">
-      <c r="A70" s="6"/>
-      <c r="B70" s="7"/>
-      <c r="C70" s="7"/>
-      <c r="D70" s="7"/>
-      <c r="E70" s="7"/>
-      <c r="F70" s="7"/>
-      <c r="G70" s="7"/>
-      <c r="H70" s="7"/>
-      <c r="I70" s="7"/>
-      <c r="N70" s="8"/>
-      <c r="O70" s="8"/>
-      <c r="P70" s="8"/>
+      <c r="A70" s="8"/>
+      <c r="B70" s="9"/>
+      <c r="C70" s="9"/>
+      <c r="D70" s="9"/>
+      <c r="E70" s="9"/>
+      <c r="F70" s="9"/>
+      <c r="G70" s="9"/>
+      <c r="H70" s="9"/>
+      <c r="I70" s="9"/>
+      <c r="N70" s="10"/>
+      <c r="O70" s="10"/>
+      <c r="P70" s="10"/>
     </row>
     <row r="71">
-      <c r="A71" s="6"/>
-      <c r="B71" s="7"/>
-      <c r="C71" s="7"/>
-      <c r="D71" s="7"/>
-      <c r="E71" s="7"/>
-      <c r="F71" s="7"/>
-      <c r="H71" s="7"/>
-      <c r="I71" s="7"/>
-      <c r="N71" s="8"/>
-      <c r="O71" s="8"/>
-      <c r="P71" s="8"/>
+      <c r="A71" s="8"/>
+      <c r="B71" s="9"/>
+      <c r="C71" s="9"/>
+      <c r="D71" s="9"/>
+      <c r="E71" s="9"/>
+      <c r="F71" s="9"/>
+      <c r="H71" s="9"/>
+      <c r="I71" s="9"/>
+      <c r="N71" s="10"/>
+      <c r="O71" s="10"/>
+      <c r="P71" s="10"/>
     </row>
     <row r="72">
-      <c r="A72" s="6"/>
-      <c r="B72" s="7"/>
-      <c r="C72" s="7"/>
-      <c r="D72" s="7"/>
-      <c r="E72" s="7"/>
-      <c r="F72" s="7"/>
-      <c r="H72" s="7"/>
-      <c r="I72" s="7"/>
-      <c r="N72" s="8"/>
-      <c r="O72" s="8"/>
-      <c r="P72" s="8"/>
+      <c r="A72" s="8"/>
+      <c r="B72" s="9"/>
+      <c r="C72" s="9"/>
+      <c r="D72" s="9"/>
+      <c r="E72" s="9"/>
+      <c r="F72" s="9"/>
+      <c r="H72" s="9"/>
+      <c r="I72" s="9"/>
+      <c r="N72" s="10"/>
+      <c r="O72" s="10"/>
+      <c r="P72" s="10"/>
     </row>
     <row r="73">
-      <c r="A73" s="6"/>
-      <c r="B73" s="7"/>
-      <c r="C73" s="7"/>
-      <c r="D73" s="7"/>
-      <c r="F73" s="7"/>
-      <c r="H73" s="7"/>
-      <c r="I73" s="7"/>
-      <c r="N73" s="8"/>
-      <c r="O73" s="8"/>
-      <c r="P73" s="8"/>
+      <c r="A73" s="8"/>
+      <c r="B73" s="9"/>
+      <c r="C73" s="9"/>
+      <c r="D73" s="9"/>
+      <c r="F73" s="9"/>
+      <c r="H73" s="9"/>
+      <c r="I73" s="9"/>
+      <c r="N73" s="10"/>
+      <c r="O73" s="10"/>
+      <c r="P73" s="10"/>
     </row>
     <row r="74">
-      <c r="A74" s="6"/>
-      <c r="B74" s="7"/>
-      <c r="C74" s="7"/>
-      <c r="D74" s="7"/>
-      <c r="F74" s="7"/>
-      <c r="H74" s="7"/>
-      <c r="I74" s="7"/>
-      <c r="N74" s="8"/>
-      <c r="O74" s="8"/>
-      <c r="P74" s="8"/>
+      <c r="A74" s="8"/>
+      <c r="B74" s="9"/>
+      <c r="C74" s="9"/>
+      <c r="D74" s="9"/>
+      <c r="F74" s="9"/>
+      <c r="H74" s="9"/>
+      <c r="I74" s="9"/>
+      <c r="N74" s="10"/>
+      <c r="O74" s="10"/>
+      <c r="P74" s="10"/>
     </row>
     <row r="75">
-      <c r="A75" s="6"/>
-      <c r="B75" s="7"/>
-      <c r="C75" s="7"/>
-      <c r="D75" s="7"/>
-      <c r="F75" s="7"/>
-      <c r="H75" s="7"/>
-      <c r="I75" s="7"/>
-      <c r="N75" s="8"/>
-      <c r="O75" s="8"/>
-      <c r="P75" s="8"/>
+      <c r="A75" s="8"/>
+      <c r="B75" s="9"/>
+      <c r="C75" s="9"/>
+      <c r="D75" s="9"/>
+      <c r="F75" s="9"/>
+      <c r="H75" s="9"/>
+      <c r="I75" s="9"/>
+      <c r="N75" s="10"/>
+      <c r="O75" s="10"/>
+      <c r="P75" s="10"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
